--- a/app/templates/informes/Informes agregado/P.fino/1-INF.-N-000-26-AG18-P.E.-FINO-V10.xlsx
+++ b/app/templates/informes/Informes agregado/P.fino/1-INF.-N-000-26-AG18-P.E.-FINO-V10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.2 Informe agregados\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\P.fino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CB2D3B-3272-4279-92E7-9294F8C80E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B5AAA4-C81B-4A94-BEFD-405087880263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="723" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="96" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="223">
   <si>
     <t>LABORATORIO DE ENSAYO DE MATERIALES</t>
   </si>
@@ -534,9 +534,6 @@
   </si>
   <si>
     <t>Resolucion</t>
-  </si>
-  <si>
-    <t>0.1</t>
   </si>
   <si>
     <t xml:space="preserve">Codigo </t>
@@ -2286,7 +2283,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="466">
+  <cellXfs count="468">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3619,6 +3616,14 @@
     </xf>
     <xf numFmtId="0" fontId="50" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5956,7 +5961,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6015,7 +6020,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6134,7 +6139,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6185,7 +6190,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6237,7 +6242,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6269,7 +6274,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -7919,20 +7924,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE1059-A774-42C5-B9E8-ED8B238CAF69}">
   <dimension ref="A1:M59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="310" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="310" customWidth="1"/>
     <col min="2" max="2" width="5" style="310" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="310" customWidth="1"/>
-    <col min="4" max="5" width="24.28515625" style="310" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="310" customWidth="1"/>
-    <col min="7" max="8" width="13.7109375" style="310" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" style="310" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" style="310" customWidth="1"/>
-    <col min="11" max="16384" width="10.28515625" style="310"/>
+    <col min="3" max="3" width="13.109375" style="310" customWidth="1"/>
+    <col min="4" max="5" width="24.33203125" style="310" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="310" customWidth="1"/>
+    <col min="7" max="8" width="13.6640625" style="310" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" style="310" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" style="310" customWidth="1"/>
+    <col min="11" max="16384" width="10.33203125" style="310"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="306"/>
       <c r="B1" s="307"/>
       <c r="C1" s="307"/>
@@ -7943,7 +7948,7 @@
       <c r="H1" s="308"/>
       <c r="I1" s="309"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="311"/>
       <c r="B2" s="312"/>
       <c r="C2" s="312"/>
@@ -7958,7 +7963,7 @@
       </c>
       <c r="M2" s="368"/>
     </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="311"/>
       <c r="B3" s="312"/>
       <c r="C3" s="312"/>
@@ -7973,7 +7978,7 @@
       </c>
       <c r="M3" s="369"/>
     </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="311"/>
       <c r="B4" s="312"/>
       <c r="C4" s="312"/>
@@ -7988,7 +7993,7 @@
       </c>
       <c r="M4" s="369"/>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="315"/>
       <c r="B5" s="316"/>
       <c r="C5" s="316"/>
@@ -8003,7 +8008,7 @@
       </c>
       <c r="M5" s="369"/>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="318"/>
       <c r="B6" s="318"/>
       <c r="C6" s="318"/>
@@ -8016,7 +8021,7 @@
       <c r="L6" s="370"/>
       <c r="M6" s="371"/>
     </row>
-    <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="389" t="s">
         <v>0</v>
       </c>
@@ -8029,13 +8034,13 @@
       <c r="H7" s="389"/>
       <c r="I7" s="389"/>
       <c r="L7" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M7" s="371"/>
     </row>
-    <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="390" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="390"/>
       <c r="C8" s="390"/>
@@ -8046,11 +8051,11 @@
       <c r="H8" s="390"/>
       <c r="I8" s="390"/>
       <c r="L8" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M8" s="372"/>
     </row>
-    <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="319"/>
       <c r="B9" s="319"/>
       <c r="C9" s="319"/>
@@ -8061,22 +8066,22 @@
       <c r="H9" s="319"/>
       <c r="I9" s="319"/>
       <c r="L9" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M9" s="371"/>
     </row>
-    <row r="10" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="320" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="320" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="320" t="s">
+      <c r="E10" s="320" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="320" t="s">
+      <c r="F10" s="391" t="s">
         <v>178</v>
-      </c>
-      <c r="F10" s="391" t="s">
-        <v>179</v>
       </c>
       <c r="G10" s="391"/>
       <c r="H10" s="321"/>
@@ -8085,7 +8090,7 @@
       <c r="L10" s="370"/>
       <c r="M10" s="371"/>
     </row>
-    <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="321"/>
       <c r="C11" s="363"/>
       <c r="D11" s="363"/>
@@ -8100,7 +8105,7 @@
       </c>
       <c r="M11" s="371"/>
     </row>
-    <row r="12" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="321"/>
       <c r="B12" s="321"/>
       <c r="C12" s="323"/>
@@ -8116,7 +8121,7 @@
       </c>
       <c r="M12" s="372"/>
     </row>
-    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="392" t="s">
         <v>10</v>
       </c>
@@ -8134,9 +8139,9 @@
       </c>
       <c r="M13" s="372"/>
     </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="395" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" s="396"/>
       <c r="C14" s="396"/>
@@ -8150,10 +8155,10 @@
       <c r="L14" s="370"/>
       <c r="M14" s="371"/>
     </row>
-    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="324"/>
       <c r="B15" s="325" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C15" s="326"/>
       <c r="D15" s="326"/>
@@ -8168,15 +8173,15 @@
       </c>
       <c r="M15" s="373"/>
     </row>
-    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="328"/>
       <c r="B16" s="329" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C16" s="330"/>
       <c r="D16" s="331"/>
       <c r="E16" s="329" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F16" s="330"/>
       <c r="G16" s="398"/>
@@ -8188,34 +8193,34 @@
       </c>
       <c r="M16" s="373"/>
     </row>
-    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="328"/>
       <c r="B17" s="329" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" s="330"/>
       <c r="D17" s="331"/>
       <c r="E17" s="329" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" s="398"/>
       <c r="H17" s="399"/>
       <c r="I17" s="332"/>
       <c r="J17" s="322"/>
       <c r="L17" s="42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M17" s="374"/>
     </row>
-    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="333"/>
       <c r="B18" s="329" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C18" s="329"/>
       <c r="D18" s="336"/>
       <c r="E18" s="329" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F18" s="330"/>
       <c r="G18" s="398"/>
@@ -8223,13 +8228,13 @@
       <c r="I18" s="334"/>
       <c r="J18" s="322"/>
     </row>
-    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="333"/>
       <c r="B19" s="329"/>
       <c r="C19" s="329"/>
       <c r="D19" s="329"/>
       <c r="E19" s="329" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F19" s="329"/>
       <c r="G19" s="398"/>
@@ -8237,10 +8242,10 @@
       <c r="I19" s="334"/>
       <c r="J19" s="322"/>
     </row>
-    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="333"/>
       <c r="B20" s="335" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C20" s="329"/>
       <c r="D20" s="329"/>
@@ -8251,10 +8256,10 @@
       <c r="I20" s="334"/>
       <c r="J20" s="322"/>
     </row>
-    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="333"/>
       <c r="B21" s="335" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C21" s="329"/>
       <c r="D21" s="329"/>
@@ -8265,7 +8270,7 @@
       <c r="I21" s="334"/>
       <c r="J21" s="322"/>
     </row>
-    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="333"/>
       <c r="B22" s="400" t="s">
         <v>19</v>
@@ -8277,13 +8282,13 @@
         <v>20</v>
       </c>
       <c r="G22" s="400" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H22" s="400"/>
       <c r="I22" s="334"/>
       <c r="J22" s="322"/>
     </row>
-    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="333"/>
       <c r="B23" s="284" t="s">
         <v>89</v>
@@ -8301,7 +8306,7 @@
       <c r="I23" s="334"/>
       <c r="J23" s="322"/>
     </row>
-    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="333"/>
       <c r="B24" s="284" t="s">
         <v>47</v>
@@ -8319,13 +8324,13 @@
       <c r="I24" s="339"/>
       <c r="J24" s="322"/>
     </row>
-    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="333"/>
       <c r="B25" s="284" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="285" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D25" s="337"/>
       <c r="E25" s="338"/>
@@ -8337,31 +8342,31 @@
       <c r="I25" s="339"/>
       <c r="J25" s="322"/>
     </row>
-    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="333"/>
       <c r="B26" s="284" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C26" s="285" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26" s="337"/>
       <c r="E26" s="338"/>
       <c r="F26" s="287" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="286"/>
-      <c r="H26" s="338"/>
+      <c r="G26" s="402"/>
+      <c r="H26" s="403"/>
       <c r="I26" s="339"/>
       <c r="J26" s="322"/>
     </row>
-    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="333"/>
       <c r="B27" s="284" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C27" s="285" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="337"/>
       <c r="E27" s="338"/>
@@ -8373,13 +8378,13 @@
       <c r="I27" s="339"/>
       <c r="J27" s="340"/>
     </row>
-    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="333"/>
       <c r="B28" s="284" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C28" s="285" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D28" s="337"/>
       <c r="E28" s="338"/>
@@ -8391,13 +8396,13 @@
       <c r="I28" s="339"/>
       <c r="J28" s="322"/>
     </row>
-    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="333"/>
       <c r="B29" s="284" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="285" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D29" s="337"/>
       <c r="E29" s="338"/>
@@ -8409,13 +8414,13 @@
       <c r="I29" s="339"/>
       <c r="J29" s="322"/>
     </row>
-    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="333"/>
       <c r="B30" s="284" t="s">
         <v>45</v>
       </c>
       <c r="C30" s="285" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D30" s="337"/>
       <c r="E30" s="338"/>
@@ -8427,13 +8432,13 @@
       <c r="I30" s="339"/>
       <c r="J30" s="322"/>
     </row>
-    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="333"/>
       <c r="B31" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="285" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D31" s="337"/>
       <c r="E31" s="338"/>
@@ -8445,13 +8450,13 @@
       <c r="I31" s="339"/>
       <c r="J31" s="322"/>
     </row>
-    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="333"/>
       <c r="B32" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="285" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D32" s="337"/>
       <c r="E32" s="338"/>
@@ -8463,13 +8468,13 @@
       <c r="I32" s="339"/>
       <c r="J32" s="322"/>
     </row>
-    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="333"/>
       <c r="B33" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="285" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D33" s="337"/>
       <c r="E33" s="338"/>
@@ -8481,13 +8486,13 @@
       <c r="I33" s="339"/>
       <c r="J33" s="322"/>
     </row>
-    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="341"/>
       <c r="B34" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="285" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D34" s="342"/>
       <c r="E34" s="343"/>
@@ -8499,7 +8504,7 @@
       <c r="I34" s="341"/>
       <c r="J34" s="322"/>
     </row>
-    <row r="35" spans="1:10" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="6.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="344"/>
       <c r="B35" s="345"/>
       <c r="C35" s="346"/>
@@ -8511,7 +8516,7 @@
       <c r="I35" s="348"/>
       <c r="J35" s="322"/>
     </row>
-    <row r="36" spans="1:10" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="6.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="349"/>
       <c r="B36" s="349"/>
       <c r="C36" s="350"/>
@@ -8523,7 +8528,7 @@
       <c r="I36" s="350"/>
       <c r="J36" s="322"/>
     </row>
-    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="351" t="s">
         <v>33</v>
       </c>
@@ -8531,54 +8536,54 @@
       <c r="G37" s="353"/>
       <c r="J37" s="322"/>
     </row>
-    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="354" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" s="86"/>
       <c r="G38" s="355"/>
       <c r="J38" s="322"/>
     </row>
-    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="352"/>
       <c r="B39" s="352"/>
       <c r="J39" s="322"/>
     </row>
-    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="356" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="387" t="s">
         <v>192</v>
-      </c>
-      <c r="E40" s="387" t="s">
-        <v>193</v>
       </c>
       <c r="F40" s="388"/>
       <c r="J40" s="322"/>
     </row>
-    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="357" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E41" s="384"/>
       <c r="F41" s="385"/>
       <c r="J41" s="322"/>
     </row>
-    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="357" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E42" s="384"/>
       <c r="F42" s="385"/>
       <c r="J42" s="322"/>
     </row>
-    <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="357" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E43" s="384"/>
       <c r="F43" s="385"/>
       <c r="J43" s="322"/>
     </row>
-    <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="357" t="s">
         <v>69</v>
       </c>
@@ -8586,23 +8591,23 @@
       <c r="F44" s="385"/>
       <c r="J44" s="322"/>
     </row>
-    <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="357" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E45" s="384"/>
       <c r="F45" s="385"/>
       <c r="J45" s="322"/>
     </row>
-    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="357" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E46" s="384"/>
       <c r="F46" s="385"/>
       <c r="J46" s="322"/>
     </row>
-    <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="358"/>
       <c r="B47" s="358"/>
       <c r="C47" s="352"/>
@@ -8611,9 +8616,9 @@
       <c r="F47" s="352"/>
       <c r="J47" s="322"/>
     </row>
-    <row r="48" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="359" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B48" s="358"/>
       <c r="C48" s="352"/>
@@ -8625,7 +8630,7 @@
       <c r="I48" s="360"/>
       <c r="J48" s="322"/>
     </row>
-    <row r="49" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="358"/>
       <c r="B49" s="358"/>
       <c r="C49" s="352"/>
@@ -8637,17 +8642,17 @@
       <c r="I49" s="352"/>
       <c r="J49" s="322"/>
     </row>
-    <row r="50" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="358"/>
       <c r="B50" s="358"/>
       <c r="J50" s="322"/>
     </row>
-    <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="358"/>
       <c r="B51" s="358"/>
       <c r="J51" s="322"/>
     </row>
-    <row r="52" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="358"/>
       <c r="B52" s="358"/>
       <c r="C52" s="352"/>
@@ -8659,7 +8664,7 @@
       <c r="I52" s="352"/>
       <c r="J52" s="322"/>
     </row>
-    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="386"/>
       <c r="D53" s="386"/>
       <c r="E53" s="386"/>
@@ -8669,7 +8674,7 @@
       <c r="I53" s="361"/>
       <c r="J53" s="322"/>
     </row>
-    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="362" t="s">
         <v>38</v>
       </c>
@@ -8683,14 +8688,14 @@
       <c r="I54" s="352"/>
       <c r="J54" s="322"/>
     </row>
-    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="362" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="362"/>
       <c r="C55" s="352"/>
       <c r="D55" s="382" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E55" s="382"/>
       <c r="F55" s="382"/>
@@ -8699,10 +8704,10 @@
       <c r="I55" s="382"/>
       <c r="J55" s="322"/>
     </row>
-    <row r="56" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="383" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" s="383"/>
       <c r="C57" s="383"/>
@@ -8713,15 +8718,15 @@
       <c r="H57" s="383"/>
       <c r="I57" s="383"/>
     </row>
-    <row r="58" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SanDugKjDcvX4yldhv/OOnHLKRvkB4OUwXOk/U85MYvcekrfWZkeZtLGTNLL4nt5uXIZDmSVAOY8ZFeARwEHSg==" saltValue="YQGDVirTjD+pRBdCn0P2sg==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="C12" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E11 C53 C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
@@ -8734,6 +8739,7 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G26:H26"/>
     <mergeCell ref="D55:I55"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="E41:F41"/>
@@ -8757,24 +8763,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:O50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="27" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" style="27" customWidth="1"/>
     <col min="2" max="2" width="2" style="27" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="27" customWidth="1"/>
-    <col min="4" max="4" width="1.140625" style="27" customWidth="1"/>
-    <col min="5" max="6" width="10.7109375" style="27" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="27" customWidth="1"/>
-    <col min="9" max="9" width="4.42578125" style="27" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="27" customWidth="1"/>
-    <col min="11" max="11" width="1.5703125" style="27" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="27" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="27" customWidth="1"/>
-    <col min="14" max="16384" width="10.28515625" style="27"/>
+    <col min="3" max="3" width="4.33203125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="1.109375" style="27" customWidth="1"/>
+    <col min="5" max="6" width="10.6640625" style="27" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" style="27" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" style="27" customWidth="1"/>
+    <col min="9" max="9" width="4.44140625" style="27" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="27" customWidth="1"/>
+    <col min="11" max="11" width="1.5546875" style="27" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="27" customWidth="1"/>
+    <col min="13" max="13" width="6.44140625" style="27" customWidth="1"/>
+    <col min="14" max="16384" width="10.33203125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -8785,7 +8791,7 @@
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36"/>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -8799,7 +8805,7 @@
       <c r="K2" s="38"/>
       <c r="L2" s="38"/>
     </row>
-    <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39"/>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -8813,56 +8819,56 @@
       <c r="K3" s="39"/>
       <c r="L3" s="39"/>
     </row>
-    <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="402" t="s">
+    <row r="4" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="404" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="402"/>
-      <c r="C4" s="402"/>
-      <c r="D4" s="402"/>
-      <c r="E4" s="402"/>
-      <c r="F4" s="402"/>
-      <c r="G4" s="402"/>
-      <c r="H4" s="402"/>
-      <c r="I4" s="402"/>
-      <c r="J4" s="402"/>
-      <c r="K4" s="402"/>
-      <c r="L4" s="402"/>
-    </row>
-    <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="409">
+      <c r="B4" s="404"/>
+      <c r="C4" s="404"/>
+      <c r="D4" s="404"/>
+      <c r="E4" s="404"/>
+      <c r="F4" s="404"/>
+      <c r="G4" s="404"/>
+      <c r="H4" s="404"/>
+      <c r="I4" s="404"/>
+      <c r="J4" s="404"/>
+      <c r="K4" s="404"/>
+      <c r="L4" s="404"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="411">
         <v>0</v>
       </c>
-      <c r="B5" s="409"/>
-      <c r="C5" s="409"/>
-      <c r="D5" s="409"/>
-      <c r="E5" s="409"/>
-      <c r="F5" s="409"/>
-      <c r="G5" s="409"/>
-      <c r="H5" s="409"/>
-      <c r="I5" s="409"/>
-      <c r="J5" s="409"/>
-      <c r="K5" s="409"/>
-      <c r="L5" s="409"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="411"/>
+      <c r="C5" s="411"/>
+      <c r="D5" s="411"/>
+      <c r="E5" s="411"/>
+      <c r="F5" s="411"/>
+      <c r="G5" s="411"/>
+      <c r="H5" s="411"/>
+      <c r="I5" s="411"/>
+      <c r="J5" s="411"/>
+      <c r="K5" s="411"/>
+      <c r="L5" s="411"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="190" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="413">
+      <c r="C7" s="415">
         <f>+FORMATO!M2</f>
         <v>0</v>
       </c>
-      <c r="D7" s="413"/>
-      <c r="E7" s="413"/>
-      <c r="F7" s="413"/>
-      <c r="G7" s="413"/>
-      <c r="H7" s="413"/>
-      <c r="I7" s="413"/>
+      <c r="D7" s="415"/>
+      <c r="E7" s="415"/>
+      <c r="F7" s="415"/>
+      <c r="G7" s="415"/>
+      <c r="H7" s="415"/>
+      <c r="I7" s="415"/>
       <c r="J7" s="42" t="s">
         <v>3</v>
       </c>
@@ -8873,25 +8879,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="190" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="413">
+      <c r="C8" s="415">
         <f>+FORMATO!M3</f>
         <v>0</v>
       </c>
-      <c r="D8" s="413"/>
-      <c r="E8" s="413"/>
-      <c r="F8" s="413"/>
-      <c r="G8" s="413"/>
-      <c r="H8" s="413"/>
-      <c r="I8" s="413"/>
+      <c r="D8" s="415"/>
+      <c r="E8" s="415"/>
+      <c r="F8" s="415"/>
+      <c r="G8" s="415"/>
+      <c r="H8" s="415"/>
+      <c r="I8" s="415"/>
       <c r="J8" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K8" s="40" t="s">
         <v>2</v>
@@ -8902,25 +8908,25 @@
       </c>
       <c r="M8" s="28"/>
     </row>
-    <row r="9" spans="1:13" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="190" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="413">
+      <c r="C9" s="415">
         <f>+FORMATO!M4</f>
         <v>0</v>
       </c>
-      <c r="D9" s="413"/>
-      <c r="E9" s="413"/>
-      <c r="F9" s="413"/>
-      <c r="G9" s="413"/>
-      <c r="H9" s="413"/>
-      <c r="I9" s="413"/>
+      <c r="D9" s="415"/>
+      <c r="E9" s="415"/>
+      <c r="F9" s="415"/>
+      <c r="G9" s="415"/>
+      <c r="H9" s="415"/>
+      <c r="I9" s="415"/>
       <c r="J9" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K9" s="40" t="s">
         <v>2</v>
@@ -8931,23 +8937,23 @@
       </c>
       <c r="M9" s="28"/>
     </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="190" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="413">
+      <c r="C10" s="415">
         <f>+FORMATO!M5</f>
         <v>0</v>
       </c>
-      <c r="D10" s="413"/>
-      <c r="E10" s="413"/>
-      <c r="F10" s="413"/>
-      <c r="G10" s="413"/>
-      <c r="H10" s="413"/>
-      <c r="I10" s="413"/>
+      <c r="D10" s="415"/>
+      <c r="E10" s="415"/>
+      <c r="F10" s="415"/>
+      <c r="G10" s="415"/>
+      <c r="H10" s="415"/>
+      <c r="I10" s="415"/>
       <c r="J10" s="381" t="s">
         <v>7</v>
       </c>
@@ -8960,7 +8966,7 @@
       </c>
       <c r="M10" s="28"/>
     </row>
-    <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="177" t="s">
         <v>9</v>
       </c>
@@ -8977,7 +8983,7 @@
       <c r="L11" s="29"/>
       <c r="M11" s="28"/>
     </row>
-    <row r="12" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="177"/>
       <c r="B12" s="74"/>
       <c r="C12" s="74"/>
@@ -8992,41 +8998,41 @@
       <c r="L12" s="29"/>
       <c r="M12" s="28"/>
     </row>
-    <row r="13" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="403" t="s">
+    <row r="13" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="405" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="404"/>
-      <c r="C13" s="404"/>
-      <c r="D13" s="404"/>
-      <c r="E13" s="404"/>
-      <c r="F13" s="404"/>
-      <c r="G13" s="404"/>
-      <c r="H13" s="404"/>
-      <c r="I13" s="404"/>
-      <c r="J13" s="404"/>
-      <c r="K13" s="404"/>
-      <c r="L13" s="405"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="406"/>
+      <c r="D13" s="406"/>
+      <c r="E13" s="406"/>
+      <c r="F13" s="406"/>
+      <c r="G13" s="406"/>
+      <c r="H13" s="406"/>
+      <c r="I13" s="406"/>
+      <c r="J13" s="406"/>
+      <c r="K13" s="406"/>
+      <c r="L13" s="407"/>
       <c r="M13" s="28"/>
     </row>
-    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="406" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="407"/>
-      <c r="C14" s="407"/>
-      <c r="D14" s="407"/>
-      <c r="E14" s="407"/>
-      <c r="F14" s="407"/>
-      <c r="G14" s="407"/>
-      <c r="H14" s="407"/>
-      <c r="I14" s="407"/>
-      <c r="J14" s="407"/>
-      <c r="K14" s="407"/>
-      <c r="L14" s="408"/>
+    <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="408" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="409"/>
+      <c r="C14" s="409"/>
+      <c r="D14" s="409"/>
+      <c r="E14" s="409"/>
+      <c r="F14" s="409"/>
+      <c r="G14" s="409"/>
+      <c r="H14" s="409"/>
+      <c r="I14" s="409"/>
+      <c r="J14" s="409"/>
+      <c r="K14" s="409"/>
+      <c r="L14" s="410"/>
       <c r="M14" s="28"/>
     </row>
-    <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45"/>
       <c r="B15" s="46"/>
       <c r="C15" s="46"/>
@@ -9041,7 +9047,7 @@
       <c r="L15" s="50"/>
       <c r="M15" s="28"/>
     </row>
-    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="51" t="s">
         <v>11</v>
       </c>
@@ -9057,7 +9063,7 @@
       <c r="K16" s="296"/>
       <c r="L16" s="52"/>
     </row>
-    <row r="17" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>12</v>
       </c>
@@ -9085,7 +9091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>15</v>
       </c>
@@ -9113,9 +9119,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B19" s="297"/>
       <c r="C19" s="297"/>
@@ -9140,13 +9146,13 @@
         <f>+FORMATO!M13</f>
         <v>0</v>
       </c>
-      <c r="M19" s="414">
+      <c r="M19" s="416">
         <f>+FORMATO!E11</f>
         <v>0</v>
       </c>
-      <c r="N19" s="415"/>
-    </row>
-    <row r="20" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N19" s="417"/>
+    </row>
+    <row r="20" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
         <v>18</v>
       </c>
@@ -9166,7 +9172,7 @@
       <c r="K20" s="56"/>
       <c r="L20" s="31"/>
     </row>
-    <row r="21" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57"/>
       <c r="B21" s="58"/>
       <c r="C21" s="58"/>
@@ -9181,17 +9187,17 @@
       <c r="L21" s="59"/>
       <c r="M21" s="32"/>
     </row>
-    <row r="22" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60"/>
-      <c r="B22" s="410" t="s">
+      <c r="B22" s="412" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="411"/>
-      <c r="D22" s="411"/>
-      <c r="E22" s="411"/>
-      <c r="F22" s="411"/>
-      <c r="G22" s="411"/>
-      <c r="H22" s="412"/>
+      <c r="C22" s="413"/>
+      <c r="D22" s="413"/>
+      <c r="E22" s="413"/>
+      <c r="F22" s="413"/>
+      <c r="G22" s="413"/>
+      <c r="H22" s="414"/>
       <c r="I22" s="182" t="s">
         <v>20</v>
       </c>
@@ -9202,7 +9208,7 @@
       <c r="L22" s="62"/>
       <c r="M22" s="32"/>
     </row>
-    <row r="23" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60"/>
       <c r="B23" s="223" t="s">
         <v>22</v>
@@ -9224,7 +9230,7 @@
       <c r="L23" s="62"/>
       <c r="M23" s="32"/>
     </row>
-    <row r="24" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60"/>
       <c r="B24" s="224" t="s">
         <v>24</v>
@@ -9246,7 +9252,7 @@
       <c r="L24" s="64"/>
       <c r="M24" s="32"/>
     </row>
-    <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60"/>
       <c r="B25" s="225" t="s">
         <v>25</v>
@@ -9267,7 +9273,7 @@
       <c r="L25" s="62"/>
       <c r="M25" s="33"/>
     </row>
-    <row r="26" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60"/>
       <c r="B26" s="224" t="s">
         <v>26</v>
@@ -9289,39 +9295,39 @@
       <c r="L26" s="62"/>
       <c r="M26" s="32"/>
     </row>
-    <row r="27" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
       <c r="D27" s="91"/>
-      <c r="E27" s="418"/>
-      <c r="F27" s="418"/>
-      <c r="G27" s="418"/>
-      <c r="H27" s="418"/>
+      <c r="E27" s="420"/>
+      <c r="F27" s="420"/>
+      <c r="G27" s="420"/>
+      <c r="H27" s="420"/>
       <c r="I27" s="38"/>
       <c r="J27" s="61"/>
       <c r="K27" s="61"/>
       <c r="L27" s="62"/>
       <c r="M27" s="32"/>
     </row>
-    <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60"/>
-      <c r="B28" s="410" t="s">
+      <c r="B28" s="412" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="411"/>
-      <c r="D28" s="411"/>
-      <c r="E28" s="411"/>
-      <c r="F28" s="411"/>
-      <c r="G28" s="411"/>
-      <c r="H28" s="411"/>
-      <c r="I28" s="411"/>
-      <c r="J28" s="412"/>
+      <c r="C28" s="413"/>
+      <c r="D28" s="413"/>
+      <c r="E28" s="413"/>
+      <c r="F28" s="413"/>
+      <c r="G28" s="413"/>
+      <c r="H28" s="413"/>
+      <c r="I28" s="413"/>
+      <c r="J28" s="414"/>
       <c r="K28" s="61"/>
       <c r="L28" s="62"/>
       <c r="M28" s="32"/>
     </row>
-    <row r="29" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60"/>
       <c r="B29" s="223" t="s">
         <v>28</v>
@@ -9343,7 +9349,7 @@
       <c r="L29" s="62"/>
       <c r="M29" s="32"/>
     </row>
-    <row r="30" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="60"/>
       <c r="B30" s="224" t="s">
         <v>29</v>
@@ -9365,7 +9371,7 @@
       <c r="L30" s="62"/>
       <c r="M30" s="32"/>
     </row>
-    <row r="31" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60"/>
       <c r="B31" s="224" t="s">
         <v>30</v>
@@ -9387,7 +9393,7 @@
       <c r="L31" s="62"/>
       <c r="M31" s="32"/>
     </row>
-    <row r="32" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="226" t="s">
         <v>31</v>
@@ -9409,7 +9415,7 @@
       <c r="L32" s="62"/>
       <c r="M32" s="32"/>
     </row>
-    <row r="33" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67"/>
       <c r="B33" s="69"/>
       <c r="C33" s="69"/>
@@ -9424,7 +9430,7 @@
       <c r="L33" s="70"/>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="76"/>
       <c r="B34" s="76"/>
       <c r="C34" s="76"/>
@@ -9439,7 +9445,7 @@
       <c r="L34" s="77"/>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="178" t="s">
         <v>33</v>
       </c>
@@ -9456,7 +9462,7 @@
       <c r="L35" s="181"/>
       <c r="M35" s="15"/>
     </row>
-    <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="200" t="s">
         <v>34</v>
       </c>
@@ -9475,7 +9481,7 @@
       <c r="L36" s="71"/>
       <c r="M36" s="28"/>
     </row>
-    <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="178" t="s">
         <v>35</v>
       </c>
@@ -9490,92 +9496,92 @@
       <c r="L37" s="71"/>
       <c r="M37" s="28"/>
     </row>
-    <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="419" t="s">
+    <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="421" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" s="421"/>
+      <c r="C38" s="421"/>
+      <c r="D38" s="421"/>
+      <c r="E38" s="421"/>
+      <c r="F38" s="421"/>
+      <c r="G38" s="421"/>
+      <c r="H38" s="421"/>
+      <c r="I38" s="421"/>
+      <c r="J38" s="421"/>
+      <c r="K38" s="421"/>
+      <c r="L38" s="421"/>
+      <c r="M38" s="28"/>
+    </row>
+    <row r="39" spans="1:15" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="419" t="s">
         <v>218</v>
       </c>
-      <c r="B38" s="419"/>
-      <c r="C38" s="419"/>
-      <c r="D38" s="419"/>
-      <c r="E38" s="419"/>
-      <c r="F38" s="419"/>
-      <c r="G38" s="419"/>
-      <c r="H38" s="419"/>
-      <c r="I38" s="419"/>
-      <c r="J38" s="419"/>
-      <c r="K38" s="419"/>
-      <c r="L38" s="419"/>
-      <c r="M38" s="28"/>
-    </row>
-    <row r="39" spans="1:15" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="417" t="s">
+      <c r="B39" s="419"/>
+      <c r="C39" s="419"/>
+      <c r="D39" s="419"/>
+      <c r="E39" s="419"/>
+      <c r="F39" s="419"/>
+      <c r="G39" s="419"/>
+      <c r="H39" s="419"/>
+      <c r="I39" s="419"/>
+      <c r="J39" s="419"/>
+      <c r="K39" s="419"/>
+      <c r="L39" s="419"/>
+      <c r="M39" s="28"/>
+    </row>
+    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="419" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="417"/>
-      <c r="C39" s="417"/>
-      <c r="D39" s="417"/>
-      <c r="E39" s="417"/>
-      <c r="F39" s="417"/>
-      <c r="G39" s="417"/>
-      <c r="H39" s="417"/>
-      <c r="I39" s="417"/>
-      <c r="J39" s="417"/>
-      <c r="K39" s="417"/>
-      <c r="L39" s="417"/>
-      <c r="M39" s="28"/>
-    </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="417" t="s">
+      <c r="B40" s="419"/>
+      <c r="C40" s="419"/>
+      <c r="D40" s="419"/>
+      <c r="E40" s="419"/>
+      <c r="F40" s="419"/>
+      <c r="G40" s="419"/>
+      <c r="H40" s="419"/>
+      <c r="I40" s="419"/>
+      <c r="J40" s="419"/>
+      <c r="K40" s="419"/>
+      <c r="L40" s="419"/>
+      <c r="M40" s="28"/>
+    </row>
+    <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="419" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="417"/>
-      <c r="C40" s="417"/>
-      <c r="D40" s="417"/>
-      <c r="E40" s="417"/>
-      <c r="F40" s="417"/>
-      <c r="G40" s="417"/>
-      <c r="H40" s="417"/>
-      <c r="I40" s="417"/>
-      <c r="J40" s="417"/>
-      <c r="K40" s="417"/>
-      <c r="L40" s="417"/>
-      <c r="M40" s="28"/>
-    </row>
-    <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="417" t="s">
+      <c r="B41" s="419"/>
+      <c r="C41" s="419"/>
+      <c r="D41" s="419"/>
+      <c r="E41" s="419"/>
+      <c r="F41" s="419"/>
+      <c r="G41" s="419"/>
+      <c r="H41" s="419"/>
+      <c r="I41" s="419"/>
+      <c r="J41" s="419"/>
+      <c r="K41" s="419"/>
+      <c r="L41" s="419"/>
+      <c r="M41" s="28"/>
+    </row>
+    <row r="42" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="418" t="s">
         <v>221</v>
       </c>
-      <c r="B41" s="417"/>
-      <c r="C41" s="417"/>
-      <c r="D41" s="417"/>
-      <c r="E41" s="417"/>
-      <c r="F41" s="417"/>
-      <c r="G41" s="417"/>
-      <c r="H41" s="417"/>
-      <c r="I41" s="417"/>
-      <c r="J41" s="417"/>
-      <c r="K41" s="417"/>
-      <c r="L41" s="417"/>
-      <c r="M41" s="28"/>
-    </row>
-    <row r="42" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="416" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="416"/>
-      <c r="C42" s="416"/>
-      <c r="D42" s="416"/>
-      <c r="E42" s="416"/>
-      <c r="F42" s="416"/>
-      <c r="G42" s="416"/>
-      <c r="H42" s="416"/>
-      <c r="I42" s="416"/>
-      <c r="J42" s="416"/>
-      <c r="K42" s="416"/>
-      <c r="L42" s="416"/>
+      <c r="B42" s="418"/>
+      <c r="C42" s="418"/>
+      <c r="D42" s="418"/>
+      <c r="E42" s="418"/>
+      <c r="F42" s="418"/>
+      <c r="G42" s="418"/>
+      <c r="H42" s="418"/>
+      <c r="I42" s="418"/>
+      <c r="J42" s="418"/>
+      <c r="K42" s="418"/>
+      <c r="L42" s="418"/>
       <c r="M42" s="28"/>
     </row>
-    <row r="43" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="252" t="s">
         <v>36</v>
       </c>
@@ -9593,7 +9599,7 @@
       <c r="N43" s="179"/>
       <c r="O43" s="180"/>
     </row>
-    <row r="44" spans="1:15" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="44.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="72"/>
       <c r="B44" s="72"/>
       <c r="C44" s="72"/>
@@ -9653,7 +9659,7 @@
       <c r="L47" s="79"/>
       <c r="M47" s="34"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="61" t="s">
         <v>38</v>
       </c>
@@ -9670,9 +9676,9 @@
       <c r="L48" s="38"/>
       <c r="M48" s="35"/>
     </row>
-    <row r="49" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="61" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -9688,7 +9694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="a0jVN26LD4Ku7LM4W33/ZrRuR438/T2WNsoJXCPrHH/tSdEUH3pciBSh2baHAoWXvOieRPNE2kMzh4Pc+wqgJA==" saltValue="VomNuyJRaC+XJqCKpnlPOA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -9728,62 +9734,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="6.44140625" style="32" customWidth="1"/>
     <col min="3" max="3" width="12" style="32" customWidth="1"/>
-    <col min="4" max="8" width="10.42578125" style="32" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" style="32" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="32" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" style="32" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="32" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="32" customWidth="1"/>
-    <col min="14" max="14" width="1.28515625" style="32" customWidth="1"/>
-    <col min="15" max="16384" width="10.28515625" style="32"/>
+    <col min="4" max="8" width="10.44140625" style="32" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="32" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" style="32" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="32" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" style="32" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" style="32" customWidth="1"/>
+    <col min="14" max="14" width="1.33203125" style="32" customWidth="1"/>
+    <col min="15" max="16384" width="10.33203125" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:16" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="420" t="s">
+    <row r="1" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="422" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="421"/>
-      <c r="D2" s="421"/>
-      <c r="E2" s="421"/>
-      <c r="F2" s="421"/>
-      <c r="G2" s="421"/>
-      <c r="H2" s="421"/>
-      <c r="I2" s="421"/>
-      <c r="J2" s="421"/>
-      <c r="K2" s="422"/>
+      <c r="C2" s="423"/>
+      <c r="D2" s="423"/>
+      <c r="E2" s="423"/>
+      <c r="F2" s="423"/>
+      <c r="G2" s="423"/>
+      <c r="H2" s="423"/>
+      <c r="I2" s="423"/>
+      <c r="J2" s="423"/>
+      <c r="K2" s="424"/>
       <c r="L2" s="85"/>
       <c r="M2" s="85"/>
       <c r="N2" s="85"/>
       <c r="O2" s="85"/>
       <c r="P2" s="85"/>
     </row>
-    <row r="3" spans="2:16" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="423" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="424"/>
-      <c r="D3" s="424"/>
-      <c r="E3" s="424"/>
-      <c r="F3" s="424"/>
-      <c r="G3" s="424"/>
-      <c r="H3" s="424"/>
-      <c r="I3" s="424"/>
-      <c r="J3" s="424"/>
-      <c r="K3" s="425"/>
+    <row r="3" spans="2:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="425" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="426"/>
+      <c r="D3" s="426"/>
+      <c r="E3" s="426"/>
+      <c r="F3" s="426"/>
+      <c r="G3" s="426"/>
+      <c r="H3" s="426"/>
+      <c r="I3" s="426"/>
+      <c r="J3" s="426"/>
+      <c r="K3" s="427"/>
       <c r="L3" s="85"/>
       <c r="M3" s="85"/>
       <c r="N3" s="85"/>
       <c r="O3" s="85"/>
       <c r="P3" s="85"/>
     </row>
-    <row r="4" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="2:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:16" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="204" t="s">
         <v>39</v>
       </c>
@@ -9796,14 +9802,14 @@
       <c r="I5" s="166"/>
       <c r="J5" s="94"/>
       <c r="K5" s="258" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L5" s="86"/>
       <c r="M5" s="86"/>
       <c r="N5" s="86"/>
       <c r="O5" s="86"/>
     </row>
-    <row r="6" spans="2:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:16" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="205" t="s">
         <v>40</v>
       </c>
@@ -9826,7 +9832,7 @@
       <c r="N6" s="86"/>
       <c r="O6" s="86"/>
     </row>
-    <row r="7" spans="2:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:16" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="205" t="s">
         <v>41</v>
       </c>
@@ -9847,7 +9853,7 @@
       <c r="N7" s="86"/>
       <c r="O7" s="86"/>
     </row>
-    <row r="8" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="205" t="s">
         <v>42</v>
       </c>
@@ -9867,7 +9873,7 @@
       <c r="N8" s="86"/>
       <c r="O8" s="86"/>
     </row>
-    <row r="9" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="206" t="s">
         <v>43</v>
       </c>
@@ -9888,34 +9894,34 @@
       <c r="N9" s="86"/>
       <c r="O9" s="86"/>
     </row>
-    <row r="10" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" s="86"/>
       <c r="M10" s="86"/>
       <c r="N10" s="86"/>
       <c r="O10" s="86"/>
     </row>
-    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="410" t="s">
+    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="412" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="411"/>
-      <c r="D11" s="411"/>
-      <c r="E11" s="411"/>
-      <c r="F11" s="411"/>
-      <c r="G11" s="411"/>
-      <c r="H11" s="412"/>
+      <c r="C11" s="413"/>
+      <c r="D11" s="413"/>
+      <c r="E11" s="413"/>
+      <c r="F11" s="413"/>
+      <c r="G11" s="413"/>
+      <c r="H11" s="414"/>
       <c r="I11" s="169" t="s">
         <v>44</v>
       </c>
       <c r="J11" s="169" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" s="169" t="s">
         <v>148</v>
       </c>
-      <c r="K11" s="169" t="s">
-        <v>149</v>
-      </c>
       <c r="L11" s="196"/>
     </row>
-    <row r="12" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="284" t="s">
         <v>89</v>
       </c>
@@ -9943,7 +9949,7 @@
       <c r="N12" s="86"/>
       <c r="O12" s="86"/>
     </row>
-    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="284" t="s">
         <v>47</v>
       </c>
@@ -9968,12 +9974,12 @@
       </c>
       <c r="L13" s="253"/>
     </row>
-    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="284" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="285" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D14" s="288"/>
       <c r="E14" s="288"/>
@@ -9996,12 +10002,12 @@
       <c r="N14" s="86"/>
       <c r="O14" s="86"/>
     </row>
-    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="284" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="285" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D15" s="288"/>
       <c r="E15" s="288"/>
@@ -10021,12 +10027,12 @@
       </c>
       <c r="L15" s="254"/>
     </row>
-    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="284" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C16" s="285" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D16" s="288"/>
       <c r="E16" s="288"/>
@@ -10048,12 +10054,12 @@
       <c r="M16" s="86"/>
       <c r="N16" s="86"/>
     </row>
-    <row r="17" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="284" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="285" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D17" s="288"/>
       <c r="E17" s="288"/>
@@ -10073,12 +10079,12 @@
       </c>
       <c r="L17" s="255"/>
     </row>
-    <row r="18" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="284" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="285" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D18" s="288"/>
       <c r="E18" s="288"/>
@@ -10101,12 +10107,12 @@
       <c r="N18" s="86"/>
       <c r="O18" s="86"/>
     </row>
-    <row r="19" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="284" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="285" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D19" s="288"/>
       <c r="E19" s="288"/>
@@ -10126,12 +10132,12 @@
       </c>
       <c r="L19" s="256"/>
     </row>
-    <row r="20" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="285" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D20" s="288"/>
       <c r="E20" s="288"/>
@@ -10153,12 +10159,12 @@
       <c r="N20" s="86"/>
       <c r="O20" s="86"/>
     </row>
-    <row r="21" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="285" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D21" s="288"/>
       <c r="E21" s="288"/>
@@ -10177,12 +10183,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="285" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D22" s="288"/>
       <c r="E22" s="288"/>
@@ -10201,12 +10207,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="284" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="285" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D23" s="288"/>
       <c r="E23" s="288"/>
@@ -10225,30 +10231,30 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:15" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="80"/>
       <c r="B33" s="80"/>
       <c r="C33" s="80"/>
     </row>
-    <row r="34" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="88"/>
     </row>
-    <row r="40" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="39yePXdmprQmqKRuMQpSBhvWNA3bP9Jje6FQXZFEFfLneWI45/E7vyfkIjS6eGAI14y/S00QiAocL+tcqavi0w==" saltValue="4D418gddrAeSpJ8+GNHlbQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
@@ -10277,33 +10283,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="167" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="167" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="167" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="167" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="167" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="167" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="167" customWidth="1"/>
     <col min="5" max="6" width="14" style="167" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="167" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="167" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="167" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="167" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="167" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="167" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="167"/>
+    <col min="7" max="7" width="13.6640625" style="167" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="167" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="167" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="167" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="167" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" style="167" customWidth="1"/>
+    <col min="13" max="16384" width="11.44140625" style="167"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="434"/>
-      <c r="B1" s="437" t="s">
+    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="436"/>
+      <c r="B1" s="439" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="438"/>
-      <c r="D1" s="438"/>
-      <c r="E1" s="438"/>
-      <c r="F1" s="438"/>
-      <c r="G1" s="438"/>
-      <c r="H1" s="439"/>
+      <c r="C1" s="440"/>
+      <c r="D1" s="440"/>
+      <c r="E1" s="440"/>
+      <c r="F1" s="440"/>
+      <c r="G1" s="440"/>
+      <c r="H1" s="441"/>
       <c r="I1" s="103" t="s">
         <v>51</v>
       </c>
@@ -10311,15 +10317,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="435"/>
-      <c r="B2" s="440"/>
-      <c r="C2" s="441"/>
-      <c r="D2" s="441"/>
-      <c r="E2" s="441"/>
-      <c r="F2" s="441"/>
-      <c r="G2" s="441"/>
-      <c r="H2" s="442"/>
+    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="437"/>
+      <c r="B2" s="442"/>
+      <c r="C2" s="443"/>
+      <c r="D2" s="443"/>
+      <c r="E2" s="443"/>
+      <c r="F2" s="443"/>
+      <c r="G2" s="443"/>
+      <c r="H2" s="444"/>
       <c r="I2" s="103" t="s">
         <v>53</v>
       </c>
@@ -10327,15 +10333,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="435"/>
-      <c r="B3" s="440"/>
-      <c r="C3" s="441"/>
-      <c r="D3" s="441"/>
-      <c r="E3" s="441"/>
-      <c r="F3" s="441"/>
-      <c r="G3" s="441"/>
-      <c r="H3" s="442"/>
+    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="437"/>
+      <c r="B3" s="442"/>
+      <c r="C3" s="443"/>
+      <c r="D3" s="443"/>
+      <c r="E3" s="443"/>
+      <c r="F3" s="443"/>
+      <c r="G3" s="443"/>
+      <c r="H3" s="444"/>
       <c r="I3" s="103" t="s">
         <v>54</v>
       </c>
@@ -10343,15 +10349,15 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="436"/>
-      <c r="B4" s="443"/>
-      <c r="C4" s="444"/>
-      <c r="D4" s="444"/>
-      <c r="E4" s="444"/>
-      <c r="F4" s="444"/>
-      <c r="G4" s="444"/>
-      <c r="H4" s="445"/>
+    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="438"/>
+      <c r="B4" s="445"/>
+      <c r="C4" s="446"/>
+      <c r="D4" s="446"/>
+      <c r="E4" s="446"/>
+      <c r="F4" s="446"/>
+      <c r="G4" s="446"/>
+      <c r="H4" s="447"/>
       <c r="I4" s="103" t="s">
         <v>55</v>
       </c>
@@ -10359,7 +10365,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="105" t="s">
         <v>57</v>
       </c>
@@ -10376,12 +10382,12 @@
       <c r="J6" s="235"/>
       <c r="L6" s="102"/>
     </row>
-    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="105" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -10393,7 +10399,7 @@
       <c r="J7" s="235"/>
       <c r="L7" s="257"/>
     </row>
-    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="105" t="s">
         <v>59</v>
       </c>
@@ -10409,12 +10415,12 @@
       <c r="I8" s="234"/>
       <c r="J8" s="235"/>
     </row>
-    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="106" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -10425,15 +10431,15 @@
       <c r="I9" s="234"/>
       <c r="J9" s="235"/>
     </row>
-    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="102" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="102"/>
     </row>
-    <row r="13" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="251" t="s">
         <v>61</v>
       </c>
@@ -10442,15 +10448,15 @@
       </c>
       <c r="I13" s="102"/>
     </row>
-    <row r="14" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F14" s="236"/>
       <c r="H14" s="236"/>
       <c r="K14" s="236"/>
       <c r="M14" s="236"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="250" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B15" s="250"/>
       <c r="C15" s="250"/>
@@ -10460,9 +10466,9 @@
       <c r="G15" s="237"/>
       <c r="I15" s="102"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="250" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" s="250"/>
       <c r="C16" s="250"/>
@@ -10472,9 +10478,9 @@
       <c r="H16" s="237"/>
       <c r="K16" s="237"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="250" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" s="250"/>
       <c r="C17" s="250"/>
@@ -10483,20 +10489,20 @@
       <c r="I17" s="102"/>
       <c r="M17" s="237"/>
     </row>
-    <row r="18" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="448" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="448"/>
-      <c r="C18" s="448"/>
-      <c r="D18" s="448"/>
-      <c r="E18" s="448"/>
-    </row>
-    <row r="19" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="450" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="450"/>
+      <c r="C18" s="450"/>
+      <c r="D18" s="450"/>
+      <c r="E18" s="450"/>
+    </row>
+    <row r="19" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F19" s="237"/>
       <c r="K19" s="237"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="251" t="s">
         <v>66</v>
       </c>
@@ -10508,7 +10514,7 @@
       <c r="N20" s="237"/>
       <c r="S20" s="237"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="G21" s="237"/>
       <c r="H21" s="237"/>
       <c r="I21" s="237"/>
@@ -10517,7 +10523,7 @@
       <c r="N21" s="237"/>
       <c r="S21" s="237"/>
     </row>
-    <row r="22" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="250" t="s">
         <v>67</v>
       </c>
@@ -10534,7 +10540,7 @@
       <c r="Q22" s="102"/>
       <c r="R22" s="102"/>
     </row>
-    <row r="23" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="250" t="s">
         <v>68</v>
       </c>
@@ -10547,7 +10553,7 @@
       <c r="M23" s="237"/>
       <c r="R23" s="237"/>
     </row>
-    <row r="24" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="250" t="s">
         <v>69</v>
       </c>
@@ -10560,7 +10566,7 @@
       <c r="M24" s="237"/>
       <c r="R24" s="237"/>
     </row>
-    <row r="25" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" s="237"/>
       <c r="H25" s="237"/>
       <c r="I25" s="237"/>
@@ -10571,7 +10577,7 @@
       <c r="T25" s="170"/>
       <c r="U25" s="170"/>
     </row>
-    <row r="26" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="102" t="s">
         <v>70</v>
       </c>
@@ -10592,7 +10598,7 @@
       <c r="T26" s="170"/>
       <c r="U26" s="170"/>
     </row>
-    <row r="27" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" s="237"/>
       <c r="H27" s="237"/>
       <c r="I27" s="237"/>
@@ -10603,7 +10609,7 @@
       <c r="T27" s="170"/>
       <c r="U27" s="170"/>
     </row>
-    <row r="28" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G28" s="237"/>
       <c r="H28" s="237"/>
       <c r="I28" s="237"/>
@@ -10617,7 +10623,7 @@
       <c r="T28" s="170"/>
       <c r="U28" s="170"/>
     </row>
-    <row r="29" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G29" s="237"/>
       <c r="H29" s="237"/>
       <c r="I29" s="237"/>
@@ -10634,7 +10640,7 @@
       <c r="T29" s="170"/>
       <c r="U29" s="170"/>
     </row>
-    <row r="30" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G30" s="237"/>
       <c r="H30" s="237"/>
       <c r="I30" s="237"/>
@@ -10645,7 +10651,7 @@
       <c r="T30" s="170"/>
       <c r="U30" s="170"/>
     </row>
-    <row r="31" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G31" s="236"/>
       <c r="K31" s="236"/>
       <c r="N31" s="236"/>
@@ -10654,7 +10660,7 @@
       <c r="T31" s="170"/>
       <c r="U31" s="170"/>
     </row>
-    <row r="32" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G32" s="237"/>
       <c r="H32" s="237"/>
       <c r="I32" s="237"/>
@@ -10671,7 +10677,7 @@
       <c r="T32" s="170"/>
       <c r="U32" s="170"/>
     </row>
-    <row r="33" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G33" s="237"/>
       <c r="H33" s="237"/>
       <c r="I33" s="237"/>
@@ -10682,7 +10688,7 @@
       <c r="T33" s="170"/>
       <c r="U33" s="170"/>
     </row>
-    <row r="34" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G34" s="237"/>
       <c r="H34" s="237"/>
       <c r="I34" s="237"/>
@@ -10699,7 +10705,7 @@
       <c r="T34" s="171"/>
       <c r="U34" s="171"/>
     </row>
-    <row r="35" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G35" s="237"/>
       <c r="H35" s="237"/>
       <c r="I35" s="237"/>
@@ -10712,7 +10718,7 @@
       <c r="T35" s="176"/>
       <c r="U35" s="176"/>
     </row>
-    <row r="36" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G36" s="237"/>
       <c r="H36" s="237"/>
       <c r="I36" s="237"/>
@@ -10727,7 +10733,7 @@
       <c r="T36" s="176"/>
       <c r="U36" s="176"/>
     </row>
-    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G37" s="237"/>
       <c r="H37" s="237"/>
       <c r="I37" s="237"/>
@@ -10742,25 +10748,25 @@
       <c r="T37" s="176"/>
       <c r="U37" s="176"/>
     </row>
-    <row r="38" spans="1:21" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I38" s="107"/>
       <c r="J38" s="107"/>
     </row>
-    <row r="39" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="451" t="s">
+    <row r="39" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="453" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="452"/>
-      <c r="C39" s="452"/>
-      <c r="D39" s="452"/>
-      <c r="E39" s="452"/>
-      <c r="F39" s="452"/>
-      <c r="G39" s="452"/>
-      <c r="H39" s="453"/>
+      <c r="B39" s="454"/>
+      <c r="C39" s="454"/>
+      <c r="D39" s="454"/>
+      <c r="E39" s="454"/>
+      <c r="F39" s="454"/>
+      <c r="G39" s="454"/>
+      <c r="H39" s="455"/>
       <c r="I39" s="107"/>
       <c r="J39" s="107"/>
     </row>
-    <row r="40" spans="1:21" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="118" t="s">
         <v>71</v>
       </c>
@@ -10788,7 +10794,7 @@
       <c r="I40" s="107"/>
       <c r="J40" s="107"/>
     </row>
-    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="115" t="s">
         <v>79</v>
       </c>
@@ -10805,7 +10811,7 @@
       <c r="I41" s="107"/>
       <c r="J41" s="107"/>
     </row>
-    <row r="42" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="122" t="str">
         <f>Balanza!E25</f>
         <v>Peso material seco en estufa</v>
@@ -10823,9 +10829,9 @@
       <c r="E42" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="126" t="e">
+      <c r="F42" s="126">
         <f>SQRT((F43*F43)+(F44*F44)+(F45*F45))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G42" s="125" t="e">
         <f>1/(B46+B54-B50)</f>
@@ -10839,7 +10845,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="108" t="s">
         <v>81</v>
       </c>
@@ -10866,7 +10872,7 @@
       </c>
       <c r="I43" s="107"/>
     </row>
-    <row r="44" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="108" t="s">
         <v>83</v>
       </c>
@@ -10892,10 +10898,10 @@
         <v>80</v>
       </c>
       <c r="I44" s="107"/>
-      <c r="J44" s="446" t="s">
+      <c r="J44" s="448" t="s">
         <v>85</v>
       </c>
-      <c r="K44" s="447"/>
+      <c r="K44" s="449"/>
       <c r="L44" s="101" t="s">
         <v>72</v>
       </c>
@@ -10903,12 +10909,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B45" s="209"/>
-      <c r="C45" s="111" t="str">
+      <c r="C45" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -10918,9 +10924,9 @@
       <c r="E45" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="111" t="e">
+      <c r="F45" s="111">
         <f>C45/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G45" s="112" t="s">
         <v>80</v>
@@ -10943,7 +10949,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="46" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="122" t="str">
         <f>Balanza!E26</f>
         <v>Peso picnometro+agua</v>
@@ -10959,9 +10965,9 @@
       <c r="E46" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F46" s="126" t="e">
+      <c r="F46" s="126">
         <f>SQRT((F47*F47)+(F48*F48)+(F49*F49))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G46" s="124" t="e">
         <f>B42/POWER((B46+B54-B50),2)</f>
@@ -10988,7 +10994,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="47" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="108" t="s">
         <v>81</v>
       </c>
@@ -11028,7 +11034,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="108" t="s">
         <v>83</v>
       </c>
@@ -11068,12 +11074,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B49" s="209"/>
-      <c r="C49" s="111" t="str">
+      <c r="C49" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -11083,9 +11089,9 @@
       <c r="E49" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="111" t="e">
+      <c r="F49" s="111">
         <f>C49/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G49" s="112" t="s">
         <v>80</v>
@@ -11108,7 +11114,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="122" t="str">
         <f>Balanza!E27</f>
         <v>Peso picnometro+material+agua</v>
@@ -11124,9 +11130,9 @@
       <c r="E50" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F50" s="126" t="e">
+      <c r="F50" s="126">
         <f>SQRT((F51*F51)+(F52*F52)+(F53*F53))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G50" s="130" t="e">
         <f>+B42/POWER((B46+B54-B50),2)</f>
@@ -11149,7 +11155,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="108" t="s">
         <v>81</v>
       </c>
@@ -11177,7 +11183,7 @@
       <c r="I51" s="107"/>
       <c r="J51" s="107"/>
     </row>
-    <row r="52" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="108" t="s">
         <v>83</v>
       </c>
@@ -11205,12 +11211,12 @@
       <c r="I52" s="107"/>
       <c r="J52" s="107"/>
     </row>
-    <row r="53" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B53" s="209"/>
-      <c r="C53" s="111" t="str">
+      <c r="C53" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -11220,9 +11226,9 @@
       <c r="E53" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F53" s="111" t="e">
+      <c r="F53" s="111">
         <f>C53/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G53" s="112" t="s">
         <v>80</v>
@@ -11233,7 +11239,7 @@
       <c r="I53" s="107"/>
       <c r="J53" s="107"/>
     </row>
-    <row r="54" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="122" t="str">
         <f>Balanza!E28</f>
         <v>Peso material saturado sup. Seca</v>
@@ -11249,9 +11255,9 @@
       <c r="E54" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F54" s="126" t="e">
+      <c r="F54" s="126">
         <f>SQRT((F55*F55)+(F56*F56)+(F57*F57))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G54" s="130" t="e">
         <f>B42/POWER((B54+B46-B50),2)</f>
@@ -11266,7 +11272,7 @@
       </c>
       <c r="J54" s="107"/>
     </row>
-    <row r="55" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="108" t="s">
         <v>81</v>
       </c>
@@ -11294,7 +11300,7 @@
       <c r="I55" s="107"/>
       <c r="J55" s="107"/>
     </row>
-    <row r="56" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="108" t="s">
         <v>83</v>
       </c>
@@ -11322,12 +11328,12 @@
       <c r="I56" s="107"/>
       <c r="J56" s="107"/>
     </row>
-    <row r="57" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B57" s="111"/>
-      <c r="C57" s="111" t="str">
+      <c r="C57" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -11337,9 +11343,9 @@
       <c r="E57" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F57" s="111" t="e">
+      <c r="F57" s="111">
         <f>C57/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G57" s="112" t="s">
         <v>80</v>
@@ -11350,7 +11356,7 @@
       <c r="I57" s="107"/>
       <c r="J57" s="107"/>
     </row>
-    <row r="58" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="132" t="s">
         <v>90</v>
       </c>
@@ -11377,7 +11383,7 @@
       <c r="I58" s="107"/>
       <c r="J58" s="107"/>
     </row>
-    <row r="59" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="241"/>
       <c r="B59" s="242"/>
       <c r="C59" s="243" t="s">
@@ -11394,7 +11400,7 @@
       <c r="I59" s="107"/>
       <c r="J59" s="107"/>
     </row>
-    <row r="60" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="244"/>
       <c r="B60" s="245"/>
       <c r="C60" s="246" t="s">
@@ -11411,7 +11417,7 @@
       <c r="I60" s="107"/>
       <c r="J60" s="107"/>
     </row>
-    <row r="61" spans="1:13" s="238" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" s="238" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -11423,7 +11429,7 @@
       <c r="I61" s="107"/>
       <c r="J61" s="107"/>
     </row>
-    <row r="62" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="138"/>
       <c r="B62" s="139"/>
       <c r="C62" s="139"/>
@@ -11437,7 +11443,7 @@
       <c r="I62" s="107"/>
       <c r="J62" s="107"/>
     </row>
-    <row r="63" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="233" t="s">
         <v>94</v>
       </c>
@@ -11454,7 +11460,7 @@
       <c r="I63" s="107"/>
       <c r="J63" s="107"/>
     </row>
-    <row r="64" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="122" t="s">
         <v>95</v>
       </c>
@@ -11469,9 +11475,9 @@
       <c r="E64" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="126" t="e">
+      <c r="F64" s="126">
         <f>SQRT((F65*F65)+(F66*F66)+(F67*F67))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G64" s="130" t="e">
         <f>+ABS((B68-B72)/POWER((B64+B68-B72),2))</f>
@@ -11484,10 +11490,10 @@
       <c r="I64" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="J64" s="446" t="s">
+      <c r="J64" s="448" t="s">
         <v>85</v>
       </c>
-      <c r="K64" s="447"/>
+      <c r="K64" s="449"/>
       <c r="L64" s="101" t="s">
         <v>72</v>
       </c>
@@ -11495,7 +11501,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="65" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="108" t="s">
         <v>81</v>
       </c>
@@ -11534,7 +11540,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="66" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="108" t="s">
         <v>83</v>
       </c>
@@ -11573,12 +11579,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="67" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B67" s="209"/>
-      <c r="C67" s="111" t="str">
+      <c r="C67" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -11588,9 +11594,9 @@
       <c r="E67" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F67" s="111" t="e">
+      <c r="F67" s="111">
         <f>C67/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G67" s="112" t="s">
         <v>80</v>
@@ -11614,7 +11620,7 @@
       <c r="S67" s="107"/>
       <c r="T67" s="107"/>
     </row>
-    <row r="68" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="122" t="s">
         <v>97</v>
       </c>
@@ -11629,9 +11635,9 @@
       <c r="E68" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F68" s="126" t="e">
+      <c r="F68" s="126">
         <f>SQRT((F69*F69)+(F70*F70)+(F71*F71))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G68" s="124" t="e">
         <f>+B64/POWER((B68+B64-B72),2)</f>
@@ -11660,7 +11666,7 @@
       <c r="S68" s="107"/>
       <c r="T68" s="107"/>
     </row>
-    <row r="69" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" s="238" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="108" t="s">
         <v>81</v>
       </c>
@@ -11686,8 +11692,8 @@
         <v>80</v>
       </c>
       <c r="I69" s="107"/>
-      <c r="J69" s="449"/>
-      <c r="K69" s="450"/>
+      <c r="J69" s="451"/>
+      <c r="K69" s="452"/>
       <c r="L69" s="158" t="e">
         <f>SUM(L65:L68)</f>
         <v>#DIV/0!</v>
@@ -11699,7 +11705,7 @@
       <c r="S69" s="107"/>
       <c r="T69" s="107"/>
     </row>
-    <row r="70" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="108" t="s">
         <v>83</v>
       </c>
@@ -11735,12 +11741,12 @@
       <c r="S70" s="107"/>
       <c r="T70" s="107"/>
     </row>
-    <row r="71" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B71" s="209"/>
-      <c r="C71" s="111" t="str">
+      <c r="C71" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -11750,9 +11756,9 @@
       <c r="E71" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F71" s="111" t="e">
+      <c r="F71" s="111">
         <f>C71/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G71" s="112" t="s">
         <v>80</v>
@@ -11772,7 +11778,7 @@
       <c r="S71" s="107"/>
       <c r="T71" s="107"/>
     </row>
-    <row r="72" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="122" t="s">
         <v>98</v>
       </c>
@@ -11787,9 +11793,9 @@
       <c r="E72" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F72" s="126" t="e">
+      <c r="F72" s="126">
         <f>SQRT((F73*F73)+(F74*F74)+(F75*F75))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G72" s="130" t="e">
         <f>+B64/POWER((B68+B64-B72),2)</f>
@@ -11813,7 +11819,7 @@
       <c r="S72" s="107"/>
       <c r="T72" s="107"/>
     </row>
-    <row r="73" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="108" t="s">
         <v>81</v>
       </c>
@@ -11848,7 +11854,7 @@
       <c r="S73" s="107"/>
       <c r="T73" s="107"/>
     </row>
-    <row r="74" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="108" t="s">
         <v>83</v>
       </c>
@@ -11883,12 +11889,12 @@
       <c r="S74" s="107"/>
       <c r="T74" s="107"/>
     </row>
-    <row r="75" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B75" s="111"/>
-      <c r="C75" s="111" t="str">
+      <c r="C75" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -11898,9 +11904,9 @@
       <c r="E75" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F75" s="111" t="e">
+      <c r="F75" s="111">
         <f>C75/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G75" s="112" t="s">
         <v>80</v>
@@ -11918,7 +11924,7 @@
       <c r="S75" s="107"/>
       <c r="T75" s="107"/>
     </row>
-    <row r="76" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="150" t="s">
         <v>99</v>
       </c>
@@ -11954,7 +11960,7 @@
       <c r="S76" s="107"/>
       <c r="T76" s="107"/>
     </row>
-    <row r="77" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="241"/>
       <c r="B77" s="242"/>
       <c r="C77" s="243" t="s">
@@ -11980,7 +11986,7 @@
       <c r="S77" s="107"/>
       <c r="T77" s="107"/>
     </row>
-    <row r="78" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="244"/>
       <c r="B78" s="245"/>
       <c r="C78" s="246" t="s">
@@ -12003,7 +12009,7 @@
       <c r="Q78" s="107"/>
       <c r="R78" s="107"/>
     </row>
-    <row r="79" spans="1:20" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K79" s="107"/>
       <c r="L79" s="107"/>
       <c r="M79" s="107"/>
@@ -12013,7 +12019,7 @@
       <c r="Q79" s="107"/>
       <c r="R79" s="107"/>
     </row>
-    <row r="80" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="138"/>
       <c r="B80" s="139"/>
       <c r="C80" s="139"/>
@@ -12033,7 +12039,7 @@
       <c r="Q80" s="107"/>
       <c r="R80" s="107"/>
     </row>
-    <row r="81" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="233" t="s">
         <v>101</v>
       </c>
@@ -12056,7 +12062,7 @@
       <c r="Q81" s="107"/>
       <c r="R81" s="107"/>
     </row>
-    <row r="82" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="122" t="s">
         <v>96</v>
       </c>
@@ -12073,9 +12079,9 @@
       <c r="E82" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="F82" s="126" t="e">
+      <c r="F82" s="126">
         <f>SQRT((F83*F83)+(F84*F84)+(F85*F85))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G82" s="125" t="e">
         <f>+ABS((B86-B90)/POWER((B86-B90+B82),2))</f>
@@ -12097,7 +12103,7 @@
       <c r="Q82" s="107"/>
       <c r="R82" s="107"/>
     </row>
-    <row r="83" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="108" t="s">
         <v>81</v>
       </c>
@@ -12132,7 +12138,7 @@
       <c r="Q83" s="107"/>
       <c r="R83" s="107"/>
     </row>
-    <row r="84" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="108" t="s">
         <v>83</v>
       </c>
@@ -12158,10 +12164,10 @@
         <v>80</v>
       </c>
       <c r="I84" s="107"/>
-      <c r="J84" s="446" t="s">
+      <c r="J84" s="448" t="s">
         <v>85</v>
       </c>
-      <c r="K84" s="447"/>
+      <c r="K84" s="449"/>
       <c r="L84" s="101" t="s">
         <v>72</v>
       </c>
@@ -12174,12 +12180,12 @@
       <c r="Q84" s="107"/>
       <c r="R84" s="107"/>
     </row>
-    <row r="85" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B85" s="209"/>
-      <c r="C85" s="111" t="str">
+      <c r="C85" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -12189,9 +12195,9 @@
       <c r="E85" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F85" s="111" t="e">
+      <c r="F85" s="111">
         <f>C85/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G85" s="112" t="s">
         <v>80</v>
@@ -12218,7 +12224,7 @@
       <c r="Q85" s="107"/>
       <c r="R85" s="107"/>
     </row>
-    <row r="86" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="122" t="s">
         <v>97</v>
       </c>
@@ -12233,9 +12239,9 @@
       <c r="E86" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F86" s="126" t="e">
+      <c r="F86" s="126">
         <f>SQRT((F87*F87)+(F88*F88)+(F89*F89))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G86" s="124" t="e">
         <f>+B82/POWER((B86+B82-B90),2)</f>
@@ -12266,7 +12272,7 @@
       <c r="Q86" s="107"/>
       <c r="R86" s="107"/>
     </row>
-    <row r="87" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="108" t="s">
         <v>81</v>
       </c>
@@ -12310,7 +12316,7 @@
       <c r="Q87" s="107"/>
       <c r="R87" s="107"/>
     </row>
-    <row r="88" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="108" t="s">
         <v>83</v>
       </c>
@@ -12354,12 +12360,12 @@
       <c r="Q88" s="107"/>
       <c r="R88" s="107"/>
     </row>
-    <row r="89" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B89" s="209"/>
-      <c r="C89" s="111" t="str">
+      <c r="C89" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -12369,9 +12375,9 @@
       <c r="E89" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F89" s="111" t="e">
+      <c r="F89" s="111">
         <f>C89/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G89" s="112" t="s">
         <v>80</v>
@@ -12395,7 +12401,7 @@
       <c r="Q89" s="107"/>
       <c r="R89" s="107"/>
     </row>
-    <row r="90" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="122" t="s">
         <v>98</v>
       </c>
@@ -12410,9 +12416,9 @@
       <c r="E90" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F90" s="126" t="e">
+      <c r="F90" s="126">
         <f>SQRT((F91*F91)+(F92*F92)+(F93*F93))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G90" s="130" t="e">
         <f>+B82/POWER((B86+B82-B90),2)</f>
@@ -12434,7 +12440,7 @@
       <c r="Q90" s="107"/>
       <c r="R90" s="107"/>
     </row>
-    <row r="91" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="108" t="s">
         <v>81</v>
       </c>
@@ -12469,7 +12475,7 @@
       <c r="Q91" s="107"/>
       <c r="R91" s="107"/>
     </row>
-    <row r="92" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="108" t="s">
         <v>83</v>
       </c>
@@ -12504,12 +12510,12 @@
       <c r="Q92" s="107"/>
       <c r="R92" s="107"/>
     </row>
-    <row r="93" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B93" s="111"/>
-      <c r="C93" s="111" t="str">
+      <c r="C93" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -12519,9 +12525,9 @@
       <c r="E93" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F93" s="111" t="e">
+      <c r="F93" s="111">
         <f>C93/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G93" s="112" t="s">
         <v>80</v>
@@ -12539,7 +12545,7 @@
       <c r="Q93" s="107"/>
       <c r="R93" s="107"/>
     </row>
-    <row r="94" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="150" t="s">
         <v>102</v>
       </c>
@@ -12571,7 +12577,7 @@
       <c r="Q94" s="107"/>
       <c r="R94" s="107"/>
     </row>
-    <row r="95" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="241"/>
       <c r="B95" s="242"/>
       <c r="C95" s="243" t="s">
@@ -12593,7 +12599,7 @@
       <c r="Q95" s="107"/>
       <c r="R95" s="107"/>
     </row>
-    <row r="96" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="244"/>
       <c r="B96" s="245"/>
       <c r="C96" s="246" t="s">
@@ -12614,7 +12620,7 @@
       <c r="Q96" s="107"/>
       <c r="R96" s="107"/>
     </row>
-    <row r="97" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K97" s="107"/>
       <c r="N97" s="107"/>
       <c r="O97" s="107"/>
@@ -12622,7 +12628,7 @@
       <c r="Q97" s="107"/>
       <c r="R97" s="107"/>
     </row>
-    <row r="98" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="138"/>
       <c r="B98" s="139"/>
       <c r="C98" s="139"/>
@@ -12640,7 +12646,7 @@
       <c r="Q98" s="107"/>
       <c r="R98" s="107"/>
     </row>
-    <row r="99" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="233" t="s">
         <v>105</v>
       </c>
@@ -12654,10 +12660,10 @@
       <c r="F99" s="147"/>
       <c r="G99" s="148"/>
       <c r="H99" s="149"/>
-      <c r="J99" s="446" t="s">
+      <c r="J99" s="448" t="s">
         <v>85</v>
       </c>
-      <c r="K99" s="447"/>
+      <c r="K99" s="449"/>
       <c r="L99" s="101" t="s">
         <v>72</v>
       </c>
@@ -12670,7 +12676,7 @@
       <c r="Q99" s="107"/>
       <c r="R99" s="107"/>
     </row>
-    <row r="100" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="122" t="s">
         <v>95</v>
       </c>
@@ -12685,9 +12691,9 @@
       <c r="E100" s="123" t="s">
         <v>80</v>
       </c>
-      <c r="F100" s="126" t="e">
+      <c r="F100" s="126">
         <f>SQRT((F101*F101)+(F102*F102)+(F103*F103))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G100" s="130" t="e">
         <f>100/B104</f>
@@ -12718,7 +12724,7 @@
       <c r="Q100" s="107"/>
       <c r="R100" s="107"/>
     </row>
-    <row r="101" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="108" t="s">
         <v>81</v>
       </c>
@@ -12762,7 +12768,7 @@
       <c r="Q101" s="107"/>
       <c r="R101" s="107"/>
     </row>
-    <row r="102" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="108" t="s">
         <v>83</v>
       </c>
@@ -12806,12 +12812,12 @@
       <c r="Q102" s="107"/>
       <c r="R102" s="107"/>
     </row>
-    <row r="103" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B103" s="209"/>
-      <c r="C103" s="111" t="str">
+      <c r="C103" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -12821,9 +12827,9 @@
       <c r="E103" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F103" s="111" t="e">
+      <c r="F103" s="111">
         <f>C103/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G103" s="112" t="s">
         <v>80</v>
@@ -12846,7 +12852,7 @@
       <c r="Q103" s="107"/>
       <c r="R103" s="107"/>
     </row>
-    <row r="104" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="122" t="s">
         <v>96</v>
       </c>
@@ -12863,9 +12869,9 @@
       <c r="E104" s="125" t="s">
         <v>80</v>
       </c>
-      <c r="F104" s="126" t="e">
+      <c r="F104" s="126">
         <f>SQRT((F105*F105)+(F106*F106)+(F107*F107))</f>
-        <v>#VALUE!</v>
+        <v>5.1413357538030266E-2</v>
       </c>
       <c r="G104" s="125" t="e">
         <f>100*B100/B104/B104</f>
@@ -12887,7 +12893,7 @@
       <c r="Q104" s="107"/>
       <c r="R104" s="107"/>
     </row>
-    <row r="105" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="108" t="s">
         <v>81</v>
       </c>
@@ -12921,7 +12927,7 @@
       <c r="Q105" s="107"/>
       <c r="R105" s="107"/>
     </row>
-    <row r="106" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="108" t="s">
         <v>83</v>
       </c>
@@ -12954,12 +12960,12 @@
       <c r="Q106" s="107"/>
       <c r="R106" s="107"/>
     </row>
-    <row r="107" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="108" t="s">
         <v>87</v>
       </c>
       <c r="B107" s="111"/>
-      <c r="C107" s="111" t="str">
+      <c r="C107" s="111">
         <f>Balanza!$C$10</f>
         <v>0.1</v>
       </c>
@@ -12969,9 +12975,9 @@
       <c r="E107" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="F107" s="111" t="e">
+      <c r="F107" s="111">
         <f>C107/SQRT(3)/2</f>
-        <v>#VALUE!</v>
+        <v>2.8867513459481291E-2</v>
       </c>
       <c r="G107" s="112" t="s">
         <v>80</v>
@@ -12987,7 +12993,7 @@
       <c r="Q107" s="107"/>
       <c r="R107" s="107"/>
     </row>
-    <row r="108" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="150" t="s">
         <v>106</v>
       </c>
@@ -13018,7 +13024,7 @@
       <c r="Q108" s="107"/>
       <c r="R108" s="107"/>
     </row>
-    <row r="109" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="241"/>
       <c r="B109" s="242"/>
       <c r="C109" s="243" t="s">
@@ -13039,7 +13045,7 @@
       <c r="Q109" s="107"/>
       <c r="R109" s="107"/>
     </row>
-    <row r="110" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="244"/>
       <c r="B110" s="245"/>
       <c r="C110" s="246" t="s">
@@ -13060,7 +13066,7 @@
       <c r="Q110" s="107"/>
       <c r="R110" s="107"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K111" s="107"/>
       <c r="N111" s="107"/>
       <c r="O111" s="107"/>
@@ -13068,7 +13074,7 @@
       <c r="Q111" s="107"/>
       <c r="R111" s="107"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K112" s="107"/>
       <c r="N112" s="107"/>
       <c r="O112" s="107"/>
@@ -13076,23 +13082,23 @@
       <c r="Q112" s="107"/>
       <c r="R112" s="107"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="376" t="s">
+        <v>205</v>
+      </c>
+      <c r="B113" s="428" t="s">
         <v>206</v>
       </c>
-      <c r="B113" s="426" t="s">
+      <c r="C113" s="429"/>
+      <c r="D113" s="377"/>
+      <c r="E113" s="430" t="s">
         <v>207</v>
       </c>
-      <c r="C113" s="427"/>
-      <c r="D113" s="377"/>
-      <c r="E113" s="428" t="s">
+      <c r="F113" s="430"/>
+      <c r="G113" s="431" t="s">
         <v>208</v>
       </c>
-      <c r="F113" s="428"/>
-      <c r="G113" s="429" t="s">
-        <v>209</v>
-      </c>
-      <c r="H113" s="430"/>
+      <c r="H113" s="432"/>
       <c r="K113" s="107"/>
       <c r="N113" s="107"/>
       <c r="O113" s="107"/>
@@ -13100,7 +13106,7 @@
       <c r="Q113" s="107"/>
       <c r="R113" s="107"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K114" s="107"/>
       <c r="L114" s="107"/>
       <c r="M114" s="107"/>
@@ -13110,22 +13116,22 @@
       <c r="Q114" s="107"/>
       <c r="R114" s="107"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="378" t="s">
+        <v>209</v>
+      </c>
+      <c r="B115" s="433">
+        <v>44869</v>
+      </c>
+      <c r="C115" s="434"/>
+      <c r="E115" s="435" t="s">
         <v>210</v>
       </c>
-      <c r="B115" s="431">
-        <v>44869</v>
-      </c>
-      <c r="C115" s="432"/>
-      <c r="E115" s="433" t="s">
-        <v>211</v>
-      </c>
-      <c r="F115" s="433"/>
-      <c r="G115" s="431">
+      <c r="F115" s="435"/>
+      <c r="G115" s="433">
         <v>44870</v>
       </c>
-      <c r="H115" s="432"/>
+      <c r="H115" s="434"/>
       <c r="K115" s="107"/>
       <c r="L115" s="107"/>
       <c r="M115" s="107"/>
@@ -13175,27 +13181,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B6:I30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="167" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="167"/>
-    <col min="3" max="3" width="11.42578125" style="167" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="167" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="167"/>
+    <col min="3" max="3" width="11.44140625" style="167" customWidth="1"/>
     <col min="4" max="4" width="12" style="167" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="167"/>
-    <col min="8" max="8" width="14.42578125" style="167" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="167"/>
-    <col min="10" max="10" width="11.85546875" style="167" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="167"/>
+    <col min="5" max="7" width="11.44140625" style="167"/>
+    <col min="8" max="8" width="14.44140625" style="167" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="167"/>
+    <col min="10" max="10" width="11.88671875" style="167" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="167"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="260" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="251"/>
       <c r="D6" s="251"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="261" t="s">
         <v>109</v>
       </c>
@@ -13204,7 +13210,7 @@
       </c>
       <c r="D7" s="263"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="102" t="s">
         <v>110</v>
       </c>
@@ -13215,52 +13221,52 @@
         <v>2.1500000000000001E-10</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="102" t="s">
         <v>111</v>
       </c>
       <c r="C9" s="264" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D9" s="263"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="265" t="s">
+      <c r="C10" s="265">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="263"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="102" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="263"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="102" t="s">
-        <v>114</v>
-      </c>
       <c r="C11" s="263" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" s="263"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="102" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12" s="302">
         <v>46160</v>
       </c>
       <c r="D12" s="263"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="102"/>
       <c r="C13" s="261"/>
     </row>
-    <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="268" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="267" t="s">
         <v>115</v>
-      </c>
-      <c r="C14" s="267" t="s">
-        <v>116</v>
       </c>
       <c r="D14" s="268">
         <v>20</v>
@@ -13278,7 +13284,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="267"/>
       <c r="C15" s="269"/>
       <c r="D15" s="270"/>
@@ -13287,7 +13293,7 @@
       <c r="G15" s="270"/>
       <c r="H15" s="270"/>
     </row>
-    <row r="16" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="267"/>
       <c r="C16" s="269"/>
       <c r="D16" s="270"/>
@@ -13296,7 +13302,7 @@
       <c r="G16" s="270"/>
       <c r="H16" s="270"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="263"/>
       <c r="C17" s="263"/>
       <c r="D17" s="263"/>
@@ -13305,10 +13311,10 @@
       <c r="G17" s="263"/>
       <c r="H17" s="291"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="271"/>
       <c r="C18" s="266" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18" s="272">
         <v>0</v>
@@ -13326,12 +13332,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D20" s="236" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="268">
         <v>20</v>
       </c>
@@ -13348,7 +13354,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D23" s="272">
         <f>D18</f>
         <v>0</v>
@@ -13370,12 +13376,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G24" s="102"/>
       <c r="H24" s="102"/>
       <c r="I24" s="102"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C25" s="273"/>
       <c r="D25" s="160"/>
       <c r="E25" s="274" t="s">
@@ -13393,7 +13399,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C26" s="276"/>
       <c r="D26" s="161"/>
       <c r="E26" s="277" t="s">
@@ -13411,7 +13417,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C27" s="273"/>
       <c r="D27" s="163"/>
       <c r="E27" s="274" t="s">
@@ -13429,7 +13435,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C28" s="279"/>
       <c r="D28" s="162"/>
       <c r="E28" s="280" t="s">
@@ -13447,17 +13453,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="E29" s="282"/>
       <c r="F29" s="282"/>
       <c r="G29" s="282"/>
       <c r="H29" s="282"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D30" s="283"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="EAqObaoqPC+2lUqUqiMpSKKwEdpxvIlRf90O/7URKY7plyAcOQhjVm9s4AfuvqeBFdJU+0SrpozEyFxBRKNUWQ==" saltValue="LvXqKudW1ADd1xduHBkjcw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -13467,1171 +13473,1171 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Y37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="213" customWidth="1"/>
-    <col min="2" max="4" width="11.85546875" style="213" customWidth="1"/>
-    <col min="5" max="5" width="1.85546875" style="213" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" style="213" customWidth="1"/>
-    <col min="7" max="9" width="11.85546875" style="213" customWidth="1"/>
-    <col min="10" max="10" width="1.28515625" style="213" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" style="213" customWidth="1"/>
-    <col min="12" max="14" width="11.85546875" style="213" customWidth="1"/>
-    <col min="15" max="15" width="2.140625" style="213" customWidth="1"/>
-    <col min="16" max="16" width="29.85546875" style="213" customWidth="1"/>
-    <col min="17" max="19" width="11.85546875" style="213" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="213" customWidth="1"/>
+    <col min="2" max="4" width="11.88671875" style="213" customWidth="1"/>
+    <col min="5" max="5" width="1.88671875" style="213" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" style="213" customWidth="1"/>
+    <col min="7" max="9" width="11.88671875" style="213" customWidth="1"/>
+    <col min="10" max="10" width="1.33203125" style="213" customWidth="1"/>
+    <col min="11" max="11" width="29.88671875" style="213" customWidth="1"/>
+    <col min="12" max="14" width="11.88671875" style="213" customWidth="1"/>
+    <col min="15" max="15" width="2.109375" style="213" customWidth="1"/>
+    <col min="16" max="16" width="29.88671875" style="213" customWidth="1"/>
+    <col min="17" max="19" width="11.88671875" style="213" customWidth="1"/>
     <col min="20" max="20" width="5" style="213" customWidth="1"/>
-    <col min="21" max="21" width="16.5703125" style="213" customWidth="1"/>
-    <col min="22" max="250" width="11.42578125" style="213"/>
+    <col min="21" max="21" width="16.5546875" style="213" customWidth="1"/>
+    <col min="22" max="250" width="11.44140625" style="213"/>
     <col min="251" max="252" width="20" style="213" customWidth="1"/>
-    <col min="253" max="253" width="11.42578125" style="213"/>
-    <col min="254" max="255" width="6.140625" style="213" customWidth="1"/>
+    <col min="253" max="253" width="11.44140625" style="213"/>
+    <col min="254" max="255" width="6.109375" style="213" customWidth="1"/>
     <col min="256" max="256" width="14" style="213" customWidth="1"/>
-    <col min="257" max="257" width="4.42578125" style="213" customWidth="1"/>
-    <col min="258" max="258" width="20.85546875" style="213" customWidth="1"/>
-    <col min="259" max="260" width="11.42578125" style="213"/>
-    <col min="261" max="262" width="4.140625" style="213" customWidth="1"/>
-    <col min="263" max="263" width="11.42578125" style="213"/>
-    <col min="264" max="264" width="19.140625" style="213" customWidth="1"/>
-    <col min="265" max="266" width="11.42578125" style="213"/>
-    <col min="267" max="268" width="4.85546875" style="213" customWidth="1"/>
-    <col min="269" max="269" width="10.85546875" style="213" customWidth="1"/>
-    <col min="270" max="270" width="11.42578125" style="213"/>
+    <col min="257" max="257" width="4.44140625" style="213" customWidth="1"/>
+    <col min="258" max="258" width="20.88671875" style="213" customWidth="1"/>
+    <col min="259" max="260" width="11.44140625" style="213"/>
+    <col min="261" max="262" width="4.109375" style="213" customWidth="1"/>
+    <col min="263" max="263" width="11.44140625" style="213"/>
+    <col min="264" max="264" width="19.109375" style="213" customWidth="1"/>
+    <col min="265" max="266" width="11.44140625" style="213"/>
+    <col min="267" max="268" width="4.88671875" style="213" customWidth="1"/>
+    <col min="269" max="269" width="10.88671875" style="213" customWidth="1"/>
+    <col min="270" max="270" width="11.44140625" style="213"/>
     <col min="271" max="271" width="22" style="213" customWidth="1"/>
-    <col min="272" max="273" width="11.42578125" style="213"/>
+    <col min="272" max="273" width="11.44140625" style="213"/>
     <col min="274" max="275" width="6" style="213" customWidth="1"/>
-    <col min="276" max="506" width="11.42578125" style="213"/>
+    <col min="276" max="506" width="11.44140625" style="213"/>
     <col min="507" max="508" width="20" style="213" customWidth="1"/>
-    <col min="509" max="509" width="11.42578125" style="213"/>
-    <col min="510" max="511" width="6.140625" style="213" customWidth="1"/>
+    <col min="509" max="509" width="11.44140625" style="213"/>
+    <col min="510" max="511" width="6.109375" style="213" customWidth="1"/>
     <col min="512" max="512" width="14" style="213" customWidth="1"/>
-    <col min="513" max="513" width="4.42578125" style="213" customWidth="1"/>
-    <col min="514" max="514" width="20.85546875" style="213" customWidth="1"/>
-    <col min="515" max="516" width="11.42578125" style="213"/>
-    <col min="517" max="518" width="4.140625" style="213" customWidth="1"/>
-    <col min="519" max="519" width="11.42578125" style="213"/>
-    <col min="520" max="520" width="19.140625" style="213" customWidth="1"/>
-    <col min="521" max="522" width="11.42578125" style="213"/>
-    <col min="523" max="524" width="4.85546875" style="213" customWidth="1"/>
-    <col min="525" max="525" width="10.85546875" style="213" customWidth="1"/>
-    <col min="526" max="526" width="11.42578125" style="213"/>
+    <col min="513" max="513" width="4.44140625" style="213" customWidth="1"/>
+    <col min="514" max="514" width="20.88671875" style="213" customWidth="1"/>
+    <col min="515" max="516" width="11.44140625" style="213"/>
+    <col min="517" max="518" width="4.109375" style="213" customWidth="1"/>
+    <col min="519" max="519" width="11.44140625" style="213"/>
+    <col min="520" max="520" width="19.109375" style="213" customWidth="1"/>
+    <col min="521" max="522" width="11.44140625" style="213"/>
+    <col min="523" max="524" width="4.88671875" style="213" customWidth="1"/>
+    <col min="525" max="525" width="10.88671875" style="213" customWidth="1"/>
+    <col min="526" max="526" width="11.44140625" style="213"/>
     <col min="527" max="527" width="22" style="213" customWidth="1"/>
-    <col min="528" max="529" width="11.42578125" style="213"/>
+    <col min="528" max="529" width="11.44140625" style="213"/>
     <col min="530" max="531" width="6" style="213" customWidth="1"/>
-    <col min="532" max="762" width="11.42578125" style="213"/>
+    <col min="532" max="762" width="11.44140625" style="213"/>
     <col min="763" max="764" width="20" style="213" customWidth="1"/>
-    <col min="765" max="765" width="11.42578125" style="213"/>
-    <col min="766" max="767" width="6.140625" style="213" customWidth="1"/>
+    <col min="765" max="765" width="11.44140625" style="213"/>
+    <col min="766" max="767" width="6.109375" style="213" customWidth="1"/>
     <col min="768" max="768" width="14" style="213" customWidth="1"/>
-    <col min="769" max="769" width="4.42578125" style="213" customWidth="1"/>
-    <col min="770" max="770" width="20.85546875" style="213" customWidth="1"/>
-    <col min="771" max="772" width="11.42578125" style="213"/>
-    <col min="773" max="774" width="4.140625" style="213" customWidth="1"/>
-    <col min="775" max="775" width="11.42578125" style="213"/>
-    <col min="776" max="776" width="19.140625" style="213" customWidth="1"/>
-    <col min="777" max="778" width="11.42578125" style="213"/>
-    <col min="779" max="780" width="4.85546875" style="213" customWidth="1"/>
-    <col min="781" max="781" width="10.85546875" style="213" customWidth="1"/>
-    <col min="782" max="782" width="11.42578125" style="213"/>
+    <col min="769" max="769" width="4.44140625" style="213" customWidth="1"/>
+    <col min="770" max="770" width="20.88671875" style="213" customWidth="1"/>
+    <col min="771" max="772" width="11.44140625" style="213"/>
+    <col min="773" max="774" width="4.109375" style="213" customWidth="1"/>
+    <col min="775" max="775" width="11.44140625" style="213"/>
+    <col min="776" max="776" width="19.109375" style="213" customWidth="1"/>
+    <col min="777" max="778" width="11.44140625" style="213"/>
+    <col min="779" max="780" width="4.88671875" style="213" customWidth="1"/>
+    <col min="781" max="781" width="10.88671875" style="213" customWidth="1"/>
+    <col min="782" max="782" width="11.44140625" style="213"/>
     <col min="783" max="783" width="22" style="213" customWidth="1"/>
-    <col min="784" max="785" width="11.42578125" style="213"/>
+    <col min="784" max="785" width="11.44140625" style="213"/>
     <col min="786" max="787" width="6" style="213" customWidth="1"/>
-    <col min="788" max="1018" width="11.42578125" style="213"/>
+    <col min="788" max="1018" width="11.44140625" style="213"/>
     <col min="1019" max="1020" width="20" style="213" customWidth="1"/>
-    <col min="1021" max="1021" width="11.42578125" style="213"/>
-    <col min="1022" max="1023" width="6.140625" style="213" customWidth="1"/>
+    <col min="1021" max="1021" width="11.44140625" style="213"/>
+    <col min="1022" max="1023" width="6.109375" style="213" customWidth="1"/>
     <col min="1024" max="1024" width="14" style="213" customWidth="1"/>
-    <col min="1025" max="1025" width="4.42578125" style="213" customWidth="1"/>
-    <col min="1026" max="1026" width="20.85546875" style="213" customWidth="1"/>
-    <col min="1027" max="1028" width="11.42578125" style="213"/>
-    <col min="1029" max="1030" width="4.140625" style="213" customWidth="1"/>
-    <col min="1031" max="1031" width="11.42578125" style="213"/>
-    <col min="1032" max="1032" width="19.140625" style="213" customWidth="1"/>
-    <col min="1033" max="1034" width="11.42578125" style="213"/>
-    <col min="1035" max="1036" width="4.85546875" style="213" customWidth="1"/>
-    <col min="1037" max="1037" width="10.85546875" style="213" customWidth="1"/>
-    <col min="1038" max="1038" width="11.42578125" style="213"/>
+    <col min="1025" max="1025" width="4.44140625" style="213" customWidth="1"/>
+    <col min="1026" max="1026" width="20.88671875" style="213" customWidth="1"/>
+    <col min="1027" max="1028" width="11.44140625" style="213"/>
+    <col min="1029" max="1030" width="4.109375" style="213" customWidth="1"/>
+    <col min="1031" max="1031" width="11.44140625" style="213"/>
+    <col min="1032" max="1032" width="19.109375" style="213" customWidth="1"/>
+    <col min="1033" max="1034" width="11.44140625" style="213"/>
+    <col min="1035" max="1036" width="4.88671875" style="213" customWidth="1"/>
+    <col min="1037" max="1037" width="10.88671875" style="213" customWidth="1"/>
+    <col min="1038" max="1038" width="11.44140625" style="213"/>
     <col min="1039" max="1039" width="22" style="213" customWidth="1"/>
-    <col min="1040" max="1041" width="11.42578125" style="213"/>
+    <col min="1040" max="1041" width="11.44140625" style="213"/>
     <col min="1042" max="1043" width="6" style="213" customWidth="1"/>
-    <col min="1044" max="1274" width="11.42578125" style="213"/>
+    <col min="1044" max="1274" width="11.44140625" style="213"/>
     <col min="1275" max="1276" width="20" style="213" customWidth="1"/>
-    <col min="1277" max="1277" width="11.42578125" style="213"/>
-    <col min="1278" max="1279" width="6.140625" style="213" customWidth="1"/>
+    <col min="1277" max="1277" width="11.44140625" style="213"/>
+    <col min="1278" max="1279" width="6.109375" style="213" customWidth="1"/>
     <col min="1280" max="1280" width="14" style="213" customWidth="1"/>
-    <col min="1281" max="1281" width="4.42578125" style="213" customWidth="1"/>
-    <col min="1282" max="1282" width="20.85546875" style="213" customWidth="1"/>
-    <col min="1283" max="1284" width="11.42578125" style="213"/>
-    <col min="1285" max="1286" width="4.140625" style="213" customWidth="1"/>
-    <col min="1287" max="1287" width="11.42578125" style="213"/>
-    <col min="1288" max="1288" width="19.140625" style="213" customWidth="1"/>
-    <col min="1289" max="1290" width="11.42578125" style="213"/>
-    <col min="1291" max="1292" width="4.85546875" style="213" customWidth="1"/>
-    <col min="1293" max="1293" width="10.85546875" style="213" customWidth="1"/>
-    <col min="1294" max="1294" width="11.42578125" style="213"/>
+    <col min="1281" max="1281" width="4.44140625" style="213" customWidth="1"/>
+    <col min="1282" max="1282" width="20.88671875" style="213" customWidth="1"/>
+    <col min="1283" max="1284" width="11.44140625" style="213"/>
+    <col min="1285" max="1286" width="4.109375" style="213" customWidth="1"/>
+    <col min="1287" max="1287" width="11.44140625" style="213"/>
+    <col min="1288" max="1288" width="19.109375" style="213" customWidth="1"/>
+    <col min="1289" max="1290" width="11.44140625" style="213"/>
+    <col min="1291" max="1292" width="4.88671875" style="213" customWidth="1"/>
+    <col min="1293" max="1293" width="10.88671875" style="213" customWidth="1"/>
+    <col min="1294" max="1294" width="11.44140625" style="213"/>
     <col min="1295" max="1295" width="22" style="213" customWidth="1"/>
-    <col min="1296" max="1297" width="11.42578125" style="213"/>
+    <col min="1296" max="1297" width="11.44140625" style="213"/>
     <col min="1298" max="1299" width="6" style="213" customWidth="1"/>
-    <col min="1300" max="1530" width="11.42578125" style="213"/>
+    <col min="1300" max="1530" width="11.44140625" style="213"/>
     <col min="1531" max="1532" width="20" style="213" customWidth="1"/>
-    <col min="1533" max="1533" width="11.42578125" style="213"/>
-    <col min="1534" max="1535" width="6.140625" style="213" customWidth="1"/>
+    <col min="1533" max="1533" width="11.44140625" style="213"/>
+    <col min="1534" max="1535" width="6.109375" style="213" customWidth="1"/>
     <col min="1536" max="1536" width="14" style="213" customWidth="1"/>
-    <col min="1537" max="1537" width="4.42578125" style="213" customWidth="1"/>
-    <col min="1538" max="1538" width="20.85546875" style="213" customWidth="1"/>
-    <col min="1539" max="1540" width="11.42578125" style="213"/>
-    <col min="1541" max="1542" width="4.140625" style="213" customWidth="1"/>
-    <col min="1543" max="1543" width="11.42578125" style="213"/>
-    <col min="1544" max="1544" width="19.140625" style="213" customWidth="1"/>
-    <col min="1545" max="1546" width="11.42578125" style="213"/>
-    <col min="1547" max="1548" width="4.85546875" style="213" customWidth="1"/>
-    <col min="1549" max="1549" width="10.85546875" style="213" customWidth="1"/>
-    <col min="1550" max="1550" width="11.42578125" style="213"/>
+    <col min="1537" max="1537" width="4.44140625" style="213" customWidth="1"/>
+    <col min="1538" max="1538" width="20.88671875" style="213" customWidth="1"/>
+    <col min="1539" max="1540" width="11.44140625" style="213"/>
+    <col min="1541" max="1542" width="4.109375" style="213" customWidth="1"/>
+    <col min="1543" max="1543" width="11.44140625" style="213"/>
+    <col min="1544" max="1544" width="19.109375" style="213" customWidth="1"/>
+    <col min="1545" max="1546" width="11.44140625" style="213"/>
+    <col min="1547" max="1548" width="4.88671875" style="213" customWidth="1"/>
+    <col min="1549" max="1549" width="10.88671875" style="213" customWidth="1"/>
+    <col min="1550" max="1550" width="11.44140625" style="213"/>
     <col min="1551" max="1551" width="22" style="213" customWidth="1"/>
-    <col min="1552" max="1553" width="11.42578125" style="213"/>
+    <col min="1552" max="1553" width="11.44140625" style="213"/>
     <col min="1554" max="1555" width="6" style="213" customWidth="1"/>
-    <col min="1556" max="1786" width="11.42578125" style="213"/>
+    <col min="1556" max="1786" width="11.44140625" style="213"/>
     <col min="1787" max="1788" width="20" style="213" customWidth="1"/>
-    <col min="1789" max="1789" width="11.42578125" style="213"/>
-    <col min="1790" max="1791" width="6.140625" style="213" customWidth="1"/>
+    <col min="1789" max="1789" width="11.44140625" style="213"/>
+    <col min="1790" max="1791" width="6.109375" style="213" customWidth="1"/>
     <col min="1792" max="1792" width="14" style="213" customWidth="1"/>
-    <col min="1793" max="1793" width="4.42578125" style="213" customWidth="1"/>
-    <col min="1794" max="1794" width="20.85546875" style="213" customWidth="1"/>
-    <col min="1795" max="1796" width="11.42578125" style="213"/>
-    <col min="1797" max="1798" width="4.140625" style="213" customWidth="1"/>
-    <col min="1799" max="1799" width="11.42578125" style="213"/>
-    <col min="1800" max="1800" width="19.140625" style="213" customWidth="1"/>
-    <col min="1801" max="1802" width="11.42578125" style="213"/>
-    <col min="1803" max="1804" width="4.85546875" style="213" customWidth="1"/>
-    <col min="1805" max="1805" width="10.85546875" style="213" customWidth="1"/>
-    <col min="1806" max="1806" width="11.42578125" style="213"/>
+    <col min="1793" max="1793" width="4.44140625" style="213" customWidth="1"/>
+    <col min="1794" max="1794" width="20.88671875" style="213" customWidth="1"/>
+    <col min="1795" max="1796" width="11.44140625" style="213"/>
+    <col min="1797" max="1798" width="4.109375" style="213" customWidth="1"/>
+    <col min="1799" max="1799" width="11.44140625" style="213"/>
+    <col min="1800" max="1800" width="19.109375" style="213" customWidth="1"/>
+    <col min="1801" max="1802" width="11.44140625" style="213"/>
+    <col min="1803" max="1804" width="4.88671875" style="213" customWidth="1"/>
+    <col min="1805" max="1805" width="10.88671875" style="213" customWidth="1"/>
+    <col min="1806" max="1806" width="11.44140625" style="213"/>
     <col min="1807" max="1807" width="22" style="213" customWidth="1"/>
-    <col min="1808" max="1809" width="11.42578125" style="213"/>
+    <col min="1808" max="1809" width="11.44140625" style="213"/>
     <col min="1810" max="1811" width="6" style="213" customWidth="1"/>
-    <col min="1812" max="2042" width="11.42578125" style="213"/>
+    <col min="1812" max="2042" width="11.44140625" style="213"/>
     <col min="2043" max="2044" width="20" style="213" customWidth="1"/>
-    <col min="2045" max="2045" width="11.42578125" style="213"/>
-    <col min="2046" max="2047" width="6.140625" style="213" customWidth="1"/>
+    <col min="2045" max="2045" width="11.44140625" style="213"/>
+    <col min="2046" max="2047" width="6.109375" style="213" customWidth="1"/>
     <col min="2048" max="2048" width="14" style="213" customWidth="1"/>
-    <col min="2049" max="2049" width="4.42578125" style="213" customWidth="1"/>
-    <col min="2050" max="2050" width="20.85546875" style="213" customWidth="1"/>
-    <col min="2051" max="2052" width="11.42578125" style="213"/>
-    <col min="2053" max="2054" width="4.140625" style="213" customWidth="1"/>
-    <col min="2055" max="2055" width="11.42578125" style="213"/>
-    <col min="2056" max="2056" width="19.140625" style="213" customWidth="1"/>
-    <col min="2057" max="2058" width="11.42578125" style="213"/>
-    <col min="2059" max="2060" width="4.85546875" style="213" customWidth="1"/>
-    <col min="2061" max="2061" width="10.85546875" style="213" customWidth="1"/>
-    <col min="2062" max="2062" width="11.42578125" style="213"/>
+    <col min="2049" max="2049" width="4.44140625" style="213" customWidth="1"/>
+    <col min="2050" max="2050" width="20.88671875" style="213" customWidth="1"/>
+    <col min="2051" max="2052" width="11.44140625" style="213"/>
+    <col min="2053" max="2054" width="4.109375" style="213" customWidth="1"/>
+    <col min="2055" max="2055" width="11.44140625" style="213"/>
+    <col min="2056" max="2056" width="19.109375" style="213" customWidth="1"/>
+    <col min="2057" max="2058" width="11.44140625" style="213"/>
+    <col min="2059" max="2060" width="4.88671875" style="213" customWidth="1"/>
+    <col min="2061" max="2061" width="10.88671875" style="213" customWidth="1"/>
+    <col min="2062" max="2062" width="11.44140625" style="213"/>
     <col min="2063" max="2063" width="22" style="213" customWidth="1"/>
-    <col min="2064" max="2065" width="11.42578125" style="213"/>
+    <col min="2064" max="2065" width="11.44140625" style="213"/>
     <col min="2066" max="2067" width="6" style="213" customWidth="1"/>
-    <col min="2068" max="2298" width="11.42578125" style="213"/>
+    <col min="2068" max="2298" width="11.44140625" style="213"/>
     <col min="2299" max="2300" width="20" style="213" customWidth="1"/>
-    <col min="2301" max="2301" width="11.42578125" style="213"/>
-    <col min="2302" max="2303" width="6.140625" style="213" customWidth="1"/>
+    <col min="2301" max="2301" width="11.44140625" style="213"/>
+    <col min="2302" max="2303" width="6.109375" style="213" customWidth="1"/>
     <col min="2304" max="2304" width="14" style="213" customWidth="1"/>
-    <col min="2305" max="2305" width="4.42578125" style="213" customWidth="1"/>
-    <col min="2306" max="2306" width="20.85546875" style="213" customWidth="1"/>
-    <col min="2307" max="2308" width="11.42578125" style="213"/>
-    <col min="2309" max="2310" width="4.140625" style="213" customWidth="1"/>
-    <col min="2311" max="2311" width="11.42578125" style="213"/>
-    <col min="2312" max="2312" width="19.140625" style="213" customWidth="1"/>
-    <col min="2313" max="2314" width="11.42578125" style="213"/>
-    <col min="2315" max="2316" width="4.85546875" style="213" customWidth="1"/>
-    <col min="2317" max="2317" width="10.85546875" style="213" customWidth="1"/>
-    <col min="2318" max="2318" width="11.42578125" style="213"/>
+    <col min="2305" max="2305" width="4.44140625" style="213" customWidth="1"/>
+    <col min="2306" max="2306" width="20.88671875" style="213" customWidth="1"/>
+    <col min="2307" max="2308" width="11.44140625" style="213"/>
+    <col min="2309" max="2310" width="4.109375" style="213" customWidth="1"/>
+    <col min="2311" max="2311" width="11.44140625" style="213"/>
+    <col min="2312" max="2312" width="19.109375" style="213" customWidth="1"/>
+    <col min="2313" max="2314" width="11.44140625" style="213"/>
+    <col min="2315" max="2316" width="4.88671875" style="213" customWidth="1"/>
+    <col min="2317" max="2317" width="10.88671875" style="213" customWidth="1"/>
+    <col min="2318" max="2318" width="11.44140625" style="213"/>
     <col min="2319" max="2319" width="22" style="213" customWidth="1"/>
-    <col min="2320" max="2321" width="11.42578125" style="213"/>
+    <col min="2320" max="2321" width="11.44140625" style="213"/>
     <col min="2322" max="2323" width="6" style="213" customWidth="1"/>
-    <col min="2324" max="2554" width="11.42578125" style="213"/>
+    <col min="2324" max="2554" width="11.44140625" style="213"/>
     <col min="2555" max="2556" width="20" style="213" customWidth="1"/>
-    <col min="2557" max="2557" width="11.42578125" style="213"/>
-    <col min="2558" max="2559" width="6.140625" style="213" customWidth="1"/>
+    <col min="2557" max="2557" width="11.44140625" style="213"/>
+    <col min="2558" max="2559" width="6.109375" style="213" customWidth="1"/>
     <col min="2560" max="2560" width="14" style="213" customWidth="1"/>
-    <col min="2561" max="2561" width="4.42578125" style="213" customWidth="1"/>
-    <col min="2562" max="2562" width="20.85546875" style="213" customWidth="1"/>
-    <col min="2563" max="2564" width="11.42578125" style="213"/>
-    <col min="2565" max="2566" width="4.140625" style="213" customWidth="1"/>
-    <col min="2567" max="2567" width="11.42578125" style="213"/>
-    <col min="2568" max="2568" width="19.140625" style="213" customWidth="1"/>
-    <col min="2569" max="2570" width="11.42578125" style="213"/>
-    <col min="2571" max="2572" width="4.85546875" style="213" customWidth="1"/>
-    <col min="2573" max="2573" width="10.85546875" style="213" customWidth="1"/>
-    <col min="2574" max="2574" width="11.42578125" style="213"/>
+    <col min="2561" max="2561" width="4.44140625" style="213" customWidth="1"/>
+    <col min="2562" max="2562" width="20.88671875" style="213" customWidth="1"/>
+    <col min="2563" max="2564" width="11.44140625" style="213"/>
+    <col min="2565" max="2566" width="4.109375" style="213" customWidth="1"/>
+    <col min="2567" max="2567" width="11.44140625" style="213"/>
+    <col min="2568" max="2568" width="19.109375" style="213" customWidth="1"/>
+    <col min="2569" max="2570" width="11.44140625" style="213"/>
+    <col min="2571" max="2572" width="4.88671875" style="213" customWidth="1"/>
+    <col min="2573" max="2573" width="10.88671875" style="213" customWidth="1"/>
+    <col min="2574" max="2574" width="11.44140625" style="213"/>
     <col min="2575" max="2575" width="22" style="213" customWidth="1"/>
-    <col min="2576" max="2577" width="11.42578125" style="213"/>
+    <col min="2576" max="2577" width="11.44140625" style="213"/>
     <col min="2578" max="2579" width="6" style="213" customWidth="1"/>
-    <col min="2580" max="2810" width="11.42578125" style="213"/>
+    <col min="2580" max="2810" width="11.44140625" style="213"/>
     <col min="2811" max="2812" width="20" style="213" customWidth="1"/>
-    <col min="2813" max="2813" width="11.42578125" style="213"/>
-    <col min="2814" max="2815" width="6.140625" style="213" customWidth="1"/>
+    <col min="2813" max="2813" width="11.44140625" style="213"/>
+    <col min="2814" max="2815" width="6.109375" style="213" customWidth="1"/>
     <col min="2816" max="2816" width="14" style="213" customWidth="1"/>
-    <col min="2817" max="2817" width="4.42578125" style="213" customWidth="1"/>
-    <col min="2818" max="2818" width="20.85546875" style="213" customWidth="1"/>
-    <col min="2819" max="2820" width="11.42578125" style="213"/>
-    <col min="2821" max="2822" width="4.140625" style="213" customWidth="1"/>
-    <col min="2823" max="2823" width="11.42578125" style="213"/>
-    <col min="2824" max="2824" width="19.140625" style="213" customWidth="1"/>
-    <col min="2825" max="2826" width="11.42578125" style="213"/>
-    <col min="2827" max="2828" width="4.85546875" style="213" customWidth="1"/>
-    <col min="2829" max="2829" width="10.85546875" style="213" customWidth="1"/>
-    <col min="2830" max="2830" width="11.42578125" style="213"/>
+    <col min="2817" max="2817" width="4.44140625" style="213" customWidth="1"/>
+    <col min="2818" max="2818" width="20.88671875" style="213" customWidth="1"/>
+    <col min="2819" max="2820" width="11.44140625" style="213"/>
+    <col min="2821" max="2822" width="4.109375" style="213" customWidth="1"/>
+    <col min="2823" max="2823" width="11.44140625" style="213"/>
+    <col min="2824" max="2824" width="19.109375" style="213" customWidth="1"/>
+    <col min="2825" max="2826" width="11.44140625" style="213"/>
+    <col min="2827" max="2828" width="4.88671875" style="213" customWidth="1"/>
+    <col min="2829" max="2829" width="10.88671875" style="213" customWidth="1"/>
+    <col min="2830" max="2830" width="11.44140625" style="213"/>
     <col min="2831" max="2831" width="22" style="213" customWidth="1"/>
-    <col min="2832" max="2833" width="11.42578125" style="213"/>
+    <col min="2832" max="2833" width="11.44140625" style="213"/>
     <col min="2834" max="2835" width="6" style="213" customWidth="1"/>
-    <col min="2836" max="3066" width="11.42578125" style="213"/>
+    <col min="2836" max="3066" width="11.44140625" style="213"/>
     <col min="3067" max="3068" width="20" style="213" customWidth="1"/>
-    <col min="3069" max="3069" width="11.42578125" style="213"/>
-    <col min="3070" max="3071" width="6.140625" style="213" customWidth="1"/>
+    <col min="3069" max="3069" width="11.44140625" style="213"/>
+    <col min="3070" max="3071" width="6.109375" style="213" customWidth="1"/>
     <col min="3072" max="3072" width="14" style="213" customWidth="1"/>
-    <col min="3073" max="3073" width="4.42578125" style="213" customWidth="1"/>
-    <col min="3074" max="3074" width="20.85546875" style="213" customWidth="1"/>
-    <col min="3075" max="3076" width="11.42578125" style="213"/>
-    <col min="3077" max="3078" width="4.140625" style="213" customWidth="1"/>
-    <col min="3079" max="3079" width="11.42578125" style="213"/>
-    <col min="3080" max="3080" width="19.140625" style="213" customWidth="1"/>
-    <col min="3081" max="3082" width="11.42578125" style="213"/>
-    <col min="3083" max="3084" width="4.85546875" style="213" customWidth="1"/>
-    <col min="3085" max="3085" width="10.85546875" style="213" customWidth="1"/>
-    <col min="3086" max="3086" width="11.42578125" style="213"/>
+    <col min="3073" max="3073" width="4.44140625" style="213" customWidth="1"/>
+    <col min="3074" max="3074" width="20.88671875" style="213" customWidth="1"/>
+    <col min="3075" max="3076" width="11.44140625" style="213"/>
+    <col min="3077" max="3078" width="4.109375" style="213" customWidth="1"/>
+    <col min="3079" max="3079" width="11.44140625" style="213"/>
+    <col min="3080" max="3080" width="19.109375" style="213" customWidth="1"/>
+    <col min="3081" max="3082" width="11.44140625" style="213"/>
+    <col min="3083" max="3084" width="4.88671875" style="213" customWidth="1"/>
+    <col min="3085" max="3085" width="10.88671875" style="213" customWidth="1"/>
+    <col min="3086" max="3086" width="11.44140625" style="213"/>
     <col min="3087" max="3087" width="22" style="213" customWidth="1"/>
-    <col min="3088" max="3089" width="11.42578125" style="213"/>
+    <col min="3088" max="3089" width="11.44140625" style="213"/>
     <col min="3090" max="3091" width="6" style="213" customWidth="1"/>
-    <col min="3092" max="3322" width="11.42578125" style="213"/>
+    <col min="3092" max="3322" width="11.44140625" style="213"/>
     <col min="3323" max="3324" width="20" style="213" customWidth="1"/>
-    <col min="3325" max="3325" width="11.42578125" style="213"/>
-    <col min="3326" max="3327" width="6.140625" style="213" customWidth="1"/>
+    <col min="3325" max="3325" width="11.44140625" style="213"/>
+    <col min="3326" max="3327" width="6.109375" style="213" customWidth="1"/>
     <col min="3328" max="3328" width="14" style="213" customWidth="1"/>
-    <col min="3329" max="3329" width="4.42578125" style="213" customWidth="1"/>
-    <col min="3330" max="3330" width="20.85546875" style="213" customWidth="1"/>
-    <col min="3331" max="3332" width="11.42578125" style="213"/>
-    <col min="3333" max="3334" width="4.140625" style="213" customWidth="1"/>
-    <col min="3335" max="3335" width="11.42578125" style="213"/>
-    <col min="3336" max="3336" width="19.140625" style="213" customWidth="1"/>
-    <col min="3337" max="3338" width="11.42578125" style="213"/>
-    <col min="3339" max="3340" width="4.85546875" style="213" customWidth="1"/>
-    <col min="3341" max="3341" width="10.85546875" style="213" customWidth="1"/>
-    <col min="3342" max="3342" width="11.42578125" style="213"/>
+    <col min="3329" max="3329" width="4.44140625" style="213" customWidth="1"/>
+    <col min="3330" max="3330" width="20.88671875" style="213" customWidth="1"/>
+    <col min="3331" max="3332" width="11.44140625" style="213"/>
+    <col min="3333" max="3334" width="4.109375" style="213" customWidth="1"/>
+    <col min="3335" max="3335" width="11.44140625" style="213"/>
+    <col min="3336" max="3336" width="19.109375" style="213" customWidth="1"/>
+    <col min="3337" max="3338" width="11.44140625" style="213"/>
+    <col min="3339" max="3340" width="4.88671875" style="213" customWidth="1"/>
+    <col min="3341" max="3341" width="10.88671875" style="213" customWidth="1"/>
+    <col min="3342" max="3342" width="11.44140625" style="213"/>
     <col min="3343" max="3343" width="22" style="213" customWidth="1"/>
-    <col min="3344" max="3345" width="11.42578125" style="213"/>
+    <col min="3344" max="3345" width="11.44140625" style="213"/>
     <col min="3346" max="3347" width="6" style="213" customWidth="1"/>
-    <col min="3348" max="3578" width="11.42578125" style="213"/>
+    <col min="3348" max="3578" width="11.44140625" style="213"/>
     <col min="3579" max="3580" width="20" style="213" customWidth="1"/>
-    <col min="3581" max="3581" width="11.42578125" style="213"/>
-    <col min="3582" max="3583" width="6.140625" style="213" customWidth="1"/>
+    <col min="3581" max="3581" width="11.44140625" style="213"/>
+    <col min="3582" max="3583" width="6.109375" style="213" customWidth="1"/>
     <col min="3584" max="3584" width="14" style="213" customWidth="1"/>
-    <col min="3585" max="3585" width="4.42578125" style="213" customWidth="1"/>
-    <col min="3586" max="3586" width="20.85546875" style="213" customWidth="1"/>
-    <col min="3587" max="3588" width="11.42578125" style="213"/>
-    <col min="3589" max="3590" width="4.140625" style="213" customWidth="1"/>
-    <col min="3591" max="3591" width="11.42578125" style="213"/>
-    <col min="3592" max="3592" width="19.140625" style="213" customWidth="1"/>
-    <col min="3593" max="3594" width="11.42578125" style="213"/>
-    <col min="3595" max="3596" width="4.85546875" style="213" customWidth="1"/>
-    <col min="3597" max="3597" width="10.85546875" style="213" customWidth="1"/>
-    <col min="3598" max="3598" width="11.42578125" style="213"/>
+    <col min="3585" max="3585" width="4.44140625" style="213" customWidth="1"/>
+    <col min="3586" max="3586" width="20.88671875" style="213" customWidth="1"/>
+    <col min="3587" max="3588" width="11.44140625" style="213"/>
+    <col min="3589" max="3590" width="4.109375" style="213" customWidth="1"/>
+    <col min="3591" max="3591" width="11.44140625" style="213"/>
+    <col min="3592" max="3592" width="19.109375" style="213" customWidth="1"/>
+    <col min="3593" max="3594" width="11.44140625" style="213"/>
+    <col min="3595" max="3596" width="4.88671875" style="213" customWidth="1"/>
+    <col min="3597" max="3597" width="10.88671875" style="213" customWidth="1"/>
+    <col min="3598" max="3598" width="11.44140625" style="213"/>
     <col min="3599" max="3599" width="22" style="213" customWidth="1"/>
-    <col min="3600" max="3601" width="11.42578125" style="213"/>
+    <col min="3600" max="3601" width="11.44140625" style="213"/>
     <col min="3602" max="3603" width="6" style="213" customWidth="1"/>
-    <col min="3604" max="3834" width="11.42578125" style="213"/>
+    <col min="3604" max="3834" width="11.44140625" style="213"/>
     <col min="3835" max="3836" width="20" style="213" customWidth="1"/>
-    <col min="3837" max="3837" width="11.42578125" style="213"/>
-    <col min="3838" max="3839" width="6.140625" style="213" customWidth="1"/>
+    <col min="3837" max="3837" width="11.44140625" style="213"/>
+    <col min="3838" max="3839" width="6.109375" style="213" customWidth="1"/>
     <col min="3840" max="3840" width="14" style="213" customWidth="1"/>
-    <col min="3841" max="3841" width="4.42578125" style="213" customWidth="1"/>
-    <col min="3842" max="3842" width="20.85546875" style="213" customWidth="1"/>
-    <col min="3843" max="3844" width="11.42578125" style="213"/>
-    <col min="3845" max="3846" width="4.140625" style="213" customWidth="1"/>
-    <col min="3847" max="3847" width="11.42578125" style="213"/>
-    <col min="3848" max="3848" width="19.140625" style="213" customWidth="1"/>
-    <col min="3849" max="3850" width="11.42578125" style="213"/>
-    <col min="3851" max="3852" width="4.85546875" style="213" customWidth="1"/>
-    <col min="3853" max="3853" width="10.85546875" style="213" customWidth="1"/>
-    <col min="3854" max="3854" width="11.42578125" style="213"/>
+    <col min="3841" max="3841" width="4.44140625" style="213" customWidth="1"/>
+    <col min="3842" max="3842" width="20.88671875" style="213" customWidth="1"/>
+    <col min="3843" max="3844" width="11.44140625" style="213"/>
+    <col min="3845" max="3846" width="4.109375" style="213" customWidth="1"/>
+    <col min="3847" max="3847" width="11.44140625" style="213"/>
+    <col min="3848" max="3848" width="19.109375" style="213" customWidth="1"/>
+    <col min="3849" max="3850" width="11.44140625" style="213"/>
+    <col min="3851" max="3852" width="4.88671875" style="213" customWidth="1"/>
+    <col min="3853" max="3853" width="10.88671875" style="213" customWidth="1"/>
+    <col min="3854" max="3854" width="11.44140625" style="213"/>
     <col min="3855" max="3855" width="22" style="213" customWidth="1"/>
-    <col min="3856" max="3857" width="11.42578125" style="213"/>
+    <col min="3856" max="3857" width="11.44140625" style="213"/>
     <col min="3858" max="3859" width="6" style="213" customWidth="1"/>
-    <col min="3860" max="4090" width="11.42578125" style="213"/>
+    <col min="3860" max="4090" width="11.44140625" style="213"/>
     <col min="4091" max="4092" width="20" style="213" customWidth="1"/>
-    <col min="4093" max="4093" width="11.42578125" style="213"/>
-    <col min="4094" max="4095" width="6.140625" style="213" customWidth="1"/>
+    <col min="4093" max="4093" width="11.44140625" style="213"/>
+    <col min="4094" max="4095" width="6.109375" style="213" customWidth="1"/>
     <col min="4096" max="4096" width="14" style="213" customWidth="1"/>
-    <col min="4097" max="4097" width="4.42578125" style="213" customWidth="1"/>
-    <col min="4098" max="4098" width="20.85546875" style="213" customWidth="1"/>
-    <col min="4099" max="4100" width="11.42578125" style="213"/>
-    <col min="4101" max="4102" width="4.140625" style="213" customWidth="1"/>
-    <col min="4103" max="4103" width="11.42578125" style="213"/>
-    <col min="4104" max="4104" width="19.140625" style="213" customWidth="1"/>
-    <col min="4105" max="4106" width="11.42578125" style="213"/>
-    <col min="4107" max="4108" width="4.85546875" style="213" customWidth="1"/>
-    <col min="4109" max="4109" width="10.85546875" style="213" customWidth="1"/>
-    <col min="4110" max="4110" width="11.42578125" style="213"/>
+    <col min="4097" max="4097" width="4.44140625" style="213" customWidth="1"/>
+    <col min="4098" max="4098" width="20.88671875" style="213" customWidth="1"/>
+    <col min="4099" max="4100" width="11.44140625" style="213"/>
+    <col min="4101" max="4102" width="4.109375" style="213" customWidth="1"/>
+    <col min="4103" max="4103" width="11.44140625" style="213"/>
+    <col min="4104" max="4104" width="19.109375" style="213" customWidth="1"/>
+    <col min="4105" max="4106" width="11.44140625" style="213"/>
+    <col min="4107" max="4108" width="4.88671875" style="213" customWidth="1"/>
+    <col min="4109" max="4109" width="10.88671875" style="213" customWidth="1"/>
+    <col min="4110" max="4110" width="11.44140625" style="213"/>
     <col min="4111" max="4111" width="22" style="213" customWidth="1"/>
-    <col min="4112" max="4113" width="11.42578125" style="213"/>
+    <col min="4112" max="4113" width="11.44140625" style="213"/>
     <col min="4114" max="4115" width="6" style="213" customWidth="1"/>
-    <col min="4116" max="4346" width="11.42578125" style="213"/>
+    <col min="4116" max="4346" width="11.44140625" style="213"/>
     <col min="4347" max="4348" width="20" style="213" customWidth="1"/>
-    <col min="4349" max="4349" width="11.42578125" style="213"/>
-    <col min="4350" max="4351" width="6.140625" style="213" customWidth="1"/>
+    <col min="4349" max="4349" width="11.44140625" style="213"/>
+    <col min="4350" max="4351" width="6.109375" style="213" customWidth="1"/>
     <col min="4352" max="4352" width="14" style="213" customWidth="1"/>
-    <col min="4353" max="4353" width="4.42578125" style="213" customWidth="1"/>
-    <col min="4354" max="4354" width="20.85546875" style="213" customWidth="1"/>
-    <col min="4355" max="4356" width="11.42578125" style="213"/>
-    <col min="4357" max="4358" width="4.140625" style="213" customWidth="1"/>
-    <col min="4359" max="4359" width="11.42578125" style="213"/>
-    <col min="4360" max="4360" width="19.140625" style="213" customWidth="1"/>
-    <col min="4361" max="4362" width="11.42578125" style="213"/>
-    <col min="4363" max="4364" width="4.85546875" style="213" customWidth="1"/>
-    <col min="4365" max="4365" width="10.85546875" style="213" customWidth="1"/>
-    <col min="4366" max="4366" width="11.42578125" style="213"/>
+    <col min="4353" max="4353" width="4.44140625" style="213" customWidth="1"/>
+    <col min="4354" max="4354" width="20.88671875" style="213" customWidth="1"/>
+    <col min="4355" max="4356" width="11.44140625" style="213"/>
+    <col min="4357" max="4358" width="4.109375" style="213" customWidth="1"/>
+    <col min="4359" max="4359" width="11.44140625" style="213"/>
+    <col min="4360" max="4360" width="19.109375" style="213" customWidth="1"/>
+    <col min="4361" max="4362" width="11.44140625" style="213"/>
+    <col min="4363" max="4364" width="4.88671875" style="213" customWidth="1"/>
+    <col min="4365" max="4365" width="10.88671875" style="213" customWidth="1"/>
+    <col min="4366" max="4366" width="11.44140625" style="213"/>
     <col min="4367" max="4367" width="22" style="213" customWidth="1"/>
-    <col min="4368" max="4369" width="11.42578125" style="213"/>
+    <col min="4368" max="4369" width="11.44140625" style="213"/>
     <col min="4370" max="4371" width="6" style="213" customWidth="1"/>
-    <col min="4372" max="4602" width="11.42578125" style="213"/>
+    <col min="4372" max="4602" width="11.44140625" style="213"/>
     <col min="4603" max="4604" width="20" style="213" customWidth="1"/>
-    <col min="4605" max="4605" width="11.42578125" style="213"/>
-    <col min="4606" max="4607" width="6.140625" style="213" customWidth="1"/>
+    <col min="4605" max="4605" width="11.44140625" style="213"/>
+    <col min="4606" max="4607" width="6.109375" style="213" customWidth="1"/>
     <col min="4608" max="4608" width="14" style="213" customWidth="1"/>
-    <col min="4609" max="4609" width="4.42578125" style="213" customWidth="1"/>
-    <col min="4610" max="4610" width="20.85546875" style="213" customWidth="1"/>
-    <col min="4611" max="4612" width="11.42578125" style="213"/>
-    <col min="4613" max="4614" width="4.140625" style="213" customWidth="1"/>
-    <col min="4615" max="4615" width="11.42578125" style="213"/>
-    <col min="4616" max="4616" width="19.140625" style="213" customWidth="1"/>
-    <col min="4617" max="4618" width="11.42578125" style="213"/>
-    <col min="4619" max="4620" width="4.85546875" style="213" customWidth="1"/>
-    <col min="4621" max="4621" width="10.85546875" style="213" customWidth="1"/>
-    <col min="4622" max="4622" width="11.42578125" style="213"/>
+    <col min="4609" max="4609" width="4.44140625" style="213" customWidth="1"/>
+    <col min="4610" max="4610" width="20.88671875" style="213" customWidth="1"/>
+    <col min="4611" max="4612" width="11.44140625" style="213"/>
+    <col min="4613" max="4614" width="4.109375" style="213" customWidth="1"/>
+    <col min="4615" max="4615" width="11.44140625" style="213"/>
+    <col min="4616" max="4616" width="19.109375" style="213" customWidth="1"/>
+    <col min="4617" max="4618" width="11.44140625" style="213"/>
+    <col min="4619" max="4620" width="4.88671875" style="213" customWidth="1"/>
+    <col min="4621" max="4621" width="10.88671875" style="213" customWidth="1"/>
+    <col min="4622" max="4622" width="11.44140625" style="213"/>
     <col min="4623" max="4623" width="22" style="213" customWidth="1"/>
-    <col min="4624" max="4625" width="11.42578125" style="213"/>
+    <col min="4624" max="4625" width="11.44140625" style="213"/>
     <col min="4626" max="4627" width="6" style="213" customWidth="1"/>
-    <col min="4628" max="4858" width="11.42578125" style="213"/>
+    <col min="4628" max="4858" width="11.44140625" style="213"/>
     <col min="4859" max="4860" width="20" style="213" customWidth="1"/>
-    <col min="4861" max="4861" width="11.42578125" style="213"/>
-    <col min="4862" max="4863" width="6.140625" style="213" customWidth="1"/>
+    <col min="4861" max="4861" width="11.44140625" style="213"/>
+    <col min="4862" max="4863" width="6.109375" style="213" customWidth="1"/>
     <col min="4864" max="4864" width="14" style="213" customWidth="1"/>
-    <col min="4865" max="4865" width="4.42578125" style="213" customWidth="1"/>
-    <col min="4866" max="4866" width="20.85546875" style="213" customWidth="1"/>
-    <col min="4867" max="4868" width="11.42578125" style="213"/>
-    <col min="4869" max="4870" width="4.140625" style="213" customWidth="1"/>
-    <col min="4871" max="4871" width="11.42578125" style="213"/>
-    <col min="4872" max="4872" width="19.140625" style="213" customWidth="1"/>
-    <col min="4873" max="4874" width="11.42578125" style="213"/>
-    <col min="4875" max="4876" width="4.85546875" style="213" customWidth="1"/>
-    <col min="4877" max="4877" width="10.85546875" style="213" customWidth="1"/>
-    <col min="4878" max="4878" width="11.42578125" style="213"/>
+    <col min="4865" max="4865" width="4.44140625" style="213" customWidth="1"/>
+    <col min="4866" max="4866" width="20.88671875" style="213" customWidth="1"/>
+    <col min="4867" max="4868" width="11.44140625" style="213"/>
+    <col min="4869" max="4870" width="4.109375" style="213" customWidth="1"/>
+    <col min="4871" max="4871" width="11.44140625" style="213"/>
+    <col min="4872" max="4872" width="19.109375" style="213" customWidth="1"/>
+    <col min="4873" max="4874" width="11.44140625" style="213"/>
+    <col min="4875" max="4876" width="4.88671875" style="213" customWidth="1"/>
+    <col min="4877" max="4877" width="10.88671875" style="213" customWidth="1"/>
+    <col min="4878" max="4878" width="11.44140625" style="213"/>
     <col min="4879" max="4879" width="22" style="213" customWidth="1"/>
-    <col min="4880" max="4881" width="11.42578125" style="213"/>
+    <col min="4880" max="4881" width="11.44140625" style="213"/>
     <col min="4882" max="4883" width="6" style="213" customWidth="1"/>
-    <col min="4884" max="5114" width="11.42578125" style="213"/>
+    <col min="4884" max="5114" width="11.44140625" style="213"/>
     <col min="5115" max="5116" width="20" style="213" customWidth="1"/>
-    <col min="5117" max="5117" width="11.42578125" style="213"/>
-    <col min="5118" max="5119" width="6.140625" style="213" customWidth="1"/>
+    <col min="5117" max="5117" width="11.44140625" style="213"/>
+    <col min="5118" max="5119" width="6.109375" style="213" customWidth="1"/>
     <col min="5120" max="5120" width="14" style="213" customWidth="1"/>
-    <col min="5121" max="5121" width="4.42578125" style="213" customWidth="1"/>
-    <col min="5122" max="5122" width="20.85546875" style="213" customWidth="1"/>
-    <col min="5123" max="5124" width="11.42578125" style="213"/>
-    <col min="5125" max="5126" width="4.140625" style="213" customWidth="1"/>
-    <col min="5127" max="5127" width="11.42578125" style="213"/>
-    <col min="5128" max="5128" width="19.140625" style="213" customWidth="1"/>
-    <col min="5129" max="5130" width="11.42578125" style="213"/>
-    <col min="5131" max="5132" width="4.85546875" style="213" customWidth="1"/>
-    <col min="5133" max="5133" width="10.85546875" style="213" customWidth="1"/>
-    <col min="5134" max="5134" width="11.42578125" style="213"/>
+    <col min="5121" max="5121" width="4.44140625" style="213" customWidth="1"/>
+    <col min="5122" max="5122" width="20.88671875" style="213" customWidth="1"/>
+    <col min="5123" max="5124" width="11.44140625" style="213"/>
+    <col min="5125" max="5126" width="4.109375" style="213" customWidth="1"/>
+    <col min="5127" max="5127" width="11.44140625" style="213"/>
+    <col min="5128" max="5128" width="19.109375" style="213" customWidth="1"/>
+    <col min="5129" max="5130" width="11.44140625" style="213"/>
+    <col min="5131" max="5132" width="4.88671875" style="213" customWidth="1"/>
+    <col min="5133" max="5133" width="10.88671875" style="213" customWidth="1"/>
+    <col min="5134" max="5134" width="11.44140625" style="213"/>
     <col min="5135" max="5135" width="22" style="213" customWidth="1"/>
-    <col min="5136" max="5137" width="11.42578125" style="213"/>
+    <col min="5136" max="5137" width="11.44140625" style="213"/>
     <col min="5138" max="5139" width="6" style="213" customWidth="1"/>
-    <col min="5140" max="5370" width="11.42578125" style="213"/>
+    <col min="5140" max="5370" width="11.44140625" style="213"/>
     <col min="5371" max="5372" width="20" style="213" customWidth="1"/>
-    <col min="5373" max="5373" width="11.42578125" style="213"/>
-    <col min="5374" max="5375" width="6.140625" style="213" customWidth="1"/>
+    <col min="5373" max="5373" width="11.44140625" style="213"/>
+    <col min="5374" max="5375" width="6.109375" style="213" customWidth="1"/>
     <col min="5376" max="5376" width="14" style="213" customWidth="1"/>
-    <col min="5377" max="5377" width="4.42578125" style="213" customWidth="1"/>
-    <col min="5378" max="5378" width="20.85546875" style="213" customWidth="1"/>
-    <col min="5379" max="5380" width="11.42578125" style="213"/>
-    <col min="5381" max="5382" width="4.140625" style="213" customWidth="1"/>
-    <col min="5383" max="5383" width="11.42578125" style="213"/>
-    <col min="5384" max="5384" width="19.140625" style="213" customWidth="1"/>
-    <col min="5385" max="5386" width="11.42578125" style="213"/>
-    <col min="5387" max="5388" width="4.85546875" style="213" customWidth="1"/>
-    <col min="5389" max="5389" width="10.85546875" style="213" customWidth="1"/>
-    <col min="5390" max="5390" width="11.42578125" style="213"/>
+    <col min="5377" max="5377" width="4.44140625" style="213" customWidth="1"/>
+    <col min="5378" max="5378" width="20.88671875" style="213" customWidth="1"/>
+    <col min="5379" max="5380" width="11.44140625" style="213"/>
+    <col min="5381" max="5382" width="4.109375" style="213" customWidth="1"/>
+    <col min="5383" max="5383" width="11.44140625" style="213"/>
+    <col min="5384" max="5384" width="19.109375" style="213" customWidth="1"/>
+    <col min="5385" max="5386" width="11.44140625" style="213"/>
+    <col min="5387" max="5388" width="4.88671875" style="213" customWidth="1"/>
+    <col min="5389" max="5389" width="10.88671875" style="213" customWidth="1"/>
+    <col min="5390" max="5390" width="11.44140625" style="213"/>
     <col min="5391" max="5391" width="22" style="213" customWidth="1"/>
-    <col min="5392" max="5393" width="11.42578125" style="213"/>
+    <col min="5392" max="5393" width="11.44140625" style="213"/>
     <col min="5394" max="5395" width="6" style="213" customWidth="1"/>
-    <col min="5396" max="5626" width="11.42578125" style="213"/>
+    <col min="5396" max="5626" width="11.44140625" style="213"/>
     <col min="5627" max="5628" width="20" style="213" customWidth="1"/>
-    <col min="5629" max="5629" width="11.42578125" style="213"/>
-    <col min="5630" max="5631" width="6.140625" style="213" customWidth="1"/>
+    <col min="5629" max="5629" width="11.44140625" style="213"/>
+    <col min="5630" max="5631" width="6.109375" style="213" customWidth="1"/>
     <col min="5632" max="5632" width="14" style="213" customWidth="1"/>
-    <col min="5633" max="5633" width="4.42578125" style="213" customWidth="1"/>
-    <col min="5634" max="5634" width="20.85546875" style="213" customWidth="1"/>
-    <col min="5635" max="5636" width="11.42578125" style="213"/>
-    <col min="5637" max="5638" width="4.140625" style="213" customWidth="1"/>
-    <col min="5639" max="5639" width="11.42578125" style="213"/>
-    <col min="5640" max="5640" width="19.140625" style="213" customWidth="1"/>
-    <col min="5641" max="5642" width="11.42578125" style="213"/>
-    <col min="5643" max="5644" width="4.85546875" style="213" customWidth="1"/>
-    <col min="5645" max="5645" width="10.85546875" style="213" customWidth="1"/>
-    <col min="5646" max="5646" width="11.42578125" style="213"/>
+    <col min="5633" max="5633" width="4.44140625" style="213" customWidth="1"/>
+    <col min="5634" max="5634" width="20.88671875" style="213" customWidth="1"/>
+    <col min="5635" max="5636" width="11.44140625" style="213"/>
+    <col min="5637" max="5638" width="4.109375" style="213" customWidth="1"/>
+    <col min="5639" max="5639" width="11.44140625" style="213"/>
+    <col min="5640" max="5640" width="19.109375" style="213" customWidth="1"/>
+    <col min="5641" max="5642" width="11.44140625" style="213"/>
+    <col min="5643" max="5644" width="4.88671875" style="213" customWidth="1"/>
+    <col min="5645" max="5645" width="10.88671875" style="213" customWidth="1"/>
+    <col min="5646" max="5646" width="11.44140625" style="213"/>
     <col min="5647" max="5647" width="22" style="213" customWidth="1"/>
-    <col min="5648" max="5649" width="11.42578125" style="213"/>
+    <col min="5648" max="5649" width="11.44140625" style="213"/>
     <col min="5650" max="5651" width="6" style="213" customWidth="1"/>
-    <col min="5652" max="5882" width="11.42578125" style="213"/>
+    <col min="5652" max="5882" width="11.44140625" style="213"/>
     <col min="5883" max="5884" width="20" style="213" customWidth="1"/>
-    <col min="5885" max="5885" width="11.42578125" style="213"/>
-    <col min="5886" max="5887" width="6.140625" style="213" customWidth="1"/>
+    <col min="5885" max="5885" width="11.44140625" style="213"/>
+    <col min="5886" max="5887" width="6.109375" style="213" customWidth="1"/>
     <col min="5888" max="5888" width="14" style="213" customWidth="1"/>
-    <col min="5889" max="5889" width="4.42578125" style="213" customWidth="1"/>
-    <col min="5890" max="5890" width="20.85546875" style="213" customWidth="1"/>
-    <col min="5891" max="5892" width="11.42578125" style="213"/>
-    <col min="5893" max="5894" width="4.140625" style="213" customWidth="1"/>
-    <col min="5895" max="5895" width="11.42578125" style="213"/>
-    <col min="5896" max="5896" width="19.140625" style="213" customWidth="1"/>
-    <col min="5897" max="5898" width="11.42578125" style="213"/>
-    <col min="5899" max="5900" width="4.85546875" style="213" customWidth="1"/>
-    <col min="5901" max="5901" width="10.85546875" style="213" customWidth="1"/>
-    <col min="5902" max="5902" width="11.42578125" style="213"/>
+    <col min="5889" max="5889" width="4.44140625" style="213" customWidth="1"/>
+    <col min="5890" max="5890" width="20.88671875" style="213" customWidth="1"/>
+    <col min="5891" max="5892" width="11.44140625" style="213"/>
+    <col min="5893" max="5894" width="4.109375" style="213" customWidth="1"/>
+    <col min="5895" max="5895" width="11.44140625" style="213"/>
+    <col min="5896" max="5896" width="19.109375" style="213" customWidth="1"/>
+    <col min="5897" max="5898" width="11.44140625" style="213"/>
+    <col min="5899" max="5900" width="4.88671875" style="213" customWidth="1"/>
+    <col min="5901" max="5901" width="10.88671875" style="213" customWidth="1"/>
+    <col min="5902" max="5902" width="11.44140625" style="213"/>
     <col min="5903" max="5903" width="22" style="213" customWidth="1"/>
-    <col min="5904" max="5905" width="11.42578125" style="213"/>
+    <col min="5904" max="5905" width="11.44140625" style="213"/>
     <col min="5906" max="5907" width="6" style="213" customWidth="1"/>
-    <col min="5908" max="6138" width="11.42578125" style="213"/>
+    <col min="5908" max="6138" width="11.44140625" style="213"/>
     <col min="6139" max="6140" width="20" style="213" customWidth="1"/>
-    <col min="6141" max="6141" width="11.42578125" style="213"/>
-    <col min="6142" max="6143" width="6.140625" style="213" customWidth="1"/>
+    <col min="6141" max="6141" width="11.44140625" style="213"/>
+    <col min="6142" max="6143" width="6.109375" style="213" customWidth="1"/>
     <col min="6144" max="6144" width="14" style="213" customWidth="1"/>
-    <col min="6145" max="6145" width="4.42578125" style="213" customWidth="1"/>
-    <col min="6146" max="6146" width="20.85546875" style="213" customWidth="1"/>
-    <col min="6147" max="6148" width="11.42578125" style="213"/>
-    <col min="6149" max="6150" width="4.140625" style="213" customWidth="1"/>
-    <col min="6151" max="6151" width="11.42578125" style="213"/>
-    <col min="6152" max="6152" width="19.140625" style="213" customWidth="1"/>
-    <col min="6153" max="6154" width="11.42578125" style="213"/>
-    <col min="6155" max="6156" width="4.85546875" style="213" customWidth="1"/>
-    <col min="6157" max="6157" width="10.85546875" style="213" customWidth="1"/>
-    <col min="6158" max="6158" width="11.42578125" style="213"/>
+    <col min="6145" max="6145" width="4.44140625" style="213" customWidth="1"/>
+    <col min="6146" max="6146" width="20.88671875" style="213" customWidth="1"/>
+    <col min="6147" max="6148" width="11.44140625" style="213"/>
+    <col min="6149" max="6150" width="4.109375" style="213" customWidth="1"/>
+    <col min="6151" max="6151" width="11.44140625" style="213"/>
+    <col min="6152" max="6152" width="19.109375" style="213" customWidth="1"/>
+    <col min="6153" max="6154" width="11.44140625" style="213"/>
+    <col min="6155" max="6156" width="4.88671875" style="213" customWidth="1"/>
+    <col min="6157" max="6157" width="10.88671875" style="213" customWidth="1"/>
+    <col min="6158" max="6158" width="11.44140625" style="213"/>
     <col min="6159" max="6159" width="22" style="213" customWidth="1"/>
-    <col min="6160" max="6161" width="11.42578125" style="213"/>
+    <col min="6160" max="6161" width="11.44140625" style="213"/>
     <col min="6162" max="6163" width="6" style="213" customWidth="1"/>
-    <col min="6164" max="6394" width="11.42578125" style="213"/>
+    <col min="6164" max="6394" width="11.44140625" style="213"/>
     <col min="6395" max="6396" width="20" style="213" customWidth="1"/>
-    <col min="6397" max="6397" width="11.42578125" style="213"/>
-    <col min="6398" max="6399" width="6.140625" style="213" customWidth="1"/>
+    <col min="6397" max="6397" width="11.44140625" style="213"/>
+    <col min="6398" max="6399" width="6.109375" style="213" customWidth="1"/>
     <col min="6400" max="6400" width="14" style="213" customWidth="1"/>
-    <col min="6401" max="6401" width="4.42578125" style="213" customWidth="1"/>
-    <col min="6402" max="6402" width="20.85546875" style="213" customWidth="1"/>
-    <col min="6403" max="6404" width="11.42578125" style="213"/>
-    <col min="6405" max="6406" width="4.140625" style="213" customWidth="1"/>
-    <col min="6407" max="6407" width="11.42578125" style="213"/>
-    <col min="6408" max="6408" width="19.140625" style="213" customWidth="1"/>
-    <col min="6409" max="6410" width="11.42578125" style="213"/>
-    <col min="6411" max="6412" width="4.85546875" style="213" customWidth="1"/>
-    <col min="6413" max="6413" width="10.85546875" style="213" customWidth="1"/>
-    <col min="6414" max="6414" width="11.42578125" style="213"/>
+    <col min="6401" max="6401" width="4.44140625" style="213" customWidth="1"/>
+    <col min="6402" max="6402" width="20.88671875" style="213" customWidth="1"/>
+    <col min="6403" max="6404" width="11.44140625" style="213"/>
+    <col min="6405" max="6406" width="4.109375" style="213" customWidth="1"/>
+    <col min="6407" max="6407" width="11.44140625" style="213"/>
+    <col min="6408" max="6408" width="19.109375" style="213" customWidth="1"/>
+    <col min="6409" max="6410" width="11.44140625" style="213"/>
+    <col min="6411" max="6412" width="4.88671875" style="213" customWidth="1"/>
+    <col min="6413" max="6413" width="10.88671875" style="213" customWidth="1"/>
+    <col min="6414" max="6414" width="11.44140625" style="213"/>
     <col min="6415" max="6415" width="22" style="213" customWidth="1"/>
-    <col min="6416" max="6417" width="11.42578125" style="213"/>
+    <col min="6416" max="6417" width="11.44140625" style="213"/>
     <col min="6418" max="6419" width="6" style="213" customWidth="1"/>
-    <col min="6420" max="6650" width="11.42578125" style="213"/>
+    <col min="6420" max="6650" width="11.44140625" style="213"/>
     <col min="6651" max="6652" width="20" style="213" customWidth="1"/>
-    <col min="6653" max="6653" width="11.42578125" style="213"/>
-    <col min="6654" max="6655" width="6.140625" style="213" customWidth="1"/>
+    <col min="6653" max="6653" width="11.44140625" style="213"/>
+    <col min="6654" max="6655" width="6.109375" style="213" customWidth="1"/>
     <col min="6656" max="6656" width="14" style="213" customWidth="1"/>
-    <col min="6657" max="6657" width="4.42578125" style="213" customWidth="1"/>
-    <col min="6658" max="6658" width="20.85546875" style="213" customWidth="1"/>
-    <col min="6659" max="6660" width="11.42578125" style="213"/>
-    <col min="6661" max="6662" width="4.140625" style="213" customWidth="1"/>
-    <col min="6663" max="6663" width="11.42578125" style="213"/>
-    <col min="6664" max="6664" width="19.140625" style="213" customWidth="1"/>
-    <col min="6665" max="6666" width="11.42578125" style="213"/>
-    <col min="6667" max="6668" width="4.85546875" style="213" customWidth="1"/>
-    <col min="6669" max="6669" width="10.85546875" style="213" customWidth="1"/>
-    <col min="6670" max="6670" width="11.42578125" style="213"/>
+    <col min="6657" max="6657" width="4.44140625" style="213" customWidth="1"/>
+    <col min="6658" max="6658" width="20.88671875" style="213" customWidth="1"/>
+    <col min="6659" max="6660" width="11.44140625" style="213"/>
+    <col min="6661" max="6662" width="4.109375" style="213" customWidth="1"/>
+    <col min="6663" max="6663" width="11.44140625" style="213"/>
+    <col min="6664" max="6664" width="19.109375" style="213" customWidth="1"/>
+    <col min="6665" max="6666" width="11.44140625" style="213"/>
+    <col min="6667" max="6668" width="4.88671875" style="213" customWidth="1"/>
+    <col min="6669" max="6669" width="10.88671875" style="213" customWidth="1"/>
+    <col min="6670" max="6670" width="11.44140625" style="213"/>
     <col min="6671" max="6671" width="22" style="213" customWidth="1"/>
-    <col min="6672" max="6673" width="11.42578125" style="213"/>
+    <col min="6672" max="6673" width="11.44140625" style="213"/>
     <col min="6674" max="6675" width="6" style="213" customWidth="1"/>
-    <col min="6676" max="6906" width="11.42578125" style="213"/>
+    <col min="6676" max="6906" width="11.44140625" style="213"/>
     <col min="6907" max="6908" width="20" style="213" customWidth="1"/>
-    <col min="6909" max="6909" width="11.42578125" style="213"/>
-    <col min="6910" max="6911" width="6.140625" style="213" customWidth="1"/>
+    <col min="6909" max="6909" width="11.44140625" style="213"/>
+    <col min="6910" max="6911" width="6.109375" style="213" customWidth="1"/>
     <col min="6912" max="6912" width="14" style="213" customWidth="1"/>
-    <col min="6913" max="6913" width="4.42578125" style="213" customWidth="1"/>
-    <col min="6914" max="6914" width="20.85546875" style="213" customWidth="1"/>
-    <col min="6915" max="6916" width="11.42578125" style="213"/>
-    <col min="6917" max="6918" width="4.140625" style="213" customWidth="1"/>
-    <col min="6919" max="6919" width="11.42578125" style="213"/>
-    <col min="6920" max="6920" width="19.140625" style="213" customWidth="1"/>
-    <col min="6921" max="6922" width="11.42578125" style="213"/>
-    <col min="6923" max="6924" width="4.85546875" style="213" customWidth="1"/>
-    <col min="6925" max="6925" width="10.85546875" style="213" customWidth="1"/>
-    <col min="6926" max="6926" width="11.42578125" style="213"/>
+    <col min="6913" max="6913" width="4.44140625" style="213" customWidth="1"/>
+    <col min="6914" max="6914" width="20.88671875" style="213" customWidth="1"/>
+    <col min="6915" max="6916" width="11.44140625" style="213"/>
+    <col min="6917" max="6918" width="4.109375" style="213" customWidth="1"/>
+    <col min="6919" max="6919" width="11.44140625" style="213"/>
+    <col min="6920" max="6920" width="19.109375" style="213" customWidth="1"/>
+    <col min="6921" max="6922" width="11.44140625" style="213"/>
+    <col min="6923" max="6924" width="4.88671875" style="213" customWidth="1"/>
+    <col min="6925" max="6925" width="10.88671875" style="213" customWidth="1"/>
+    <col min="6926" max="6926" width="11.44140625" style="213"/>
     <col min="6927" max="6927" width="22" style="213" customWidth="1"/>
-    <col min="6928" max="6929" width="11.42578125" style="213"/>
+    <col min="6928" max="6929" width="11.44140625" style="213"/>
     <col min="6930" max="6931" width="6" style="213" customWidth="1"/>
-    <col min="6932" max="7162" width="11.42578125" style="213"/>
+    <col min="6932" max="7162" width="11.44140625" style="213"/>
     <col min="7163" max="7164" width="20" style="213" customWidth="1"/>
-    <col min="7165" max="7165" width="11.42578125" style="213"/>
-    <col min="7166" max="7167" width="6.140625" style="213" customWidth="1"/>
+    <col min="7165" max="7165" width="11.44140625" style="213"/>
+    <col min="7166" max="7167" width="6.109375" style="213" customWidth="1"/>
     <col min="7168" max="7168" width="14" style="213" customWidth="1"/>
-    <col min="7169" max="7169" width="4.42578125" style="213" customWidth="1"/>
-    <col min="7170" max="7170" width="20.85546875" style="213" customWidth="1"/>
-    <col min="7171" max="7172" width="11.42578125" style="213"/>
-    <col min="7173" max="7174" width="4.140625" style="213" customWidth="1"/>
-    <col min="7175" max="7175" width="11.42578125" style="213"/>
-    <col min="7176" max="7176" width="19.140625" style="213" customWidth="1"/>
-    <col min="7177" max="7178" width="11.42578125" style="213"/>
-    <col min="7179" max="7180" width="4.85546875" style="213" customWidth="1"/>
-    <col min="7181" max="7181" width="10.85546875" style="213" customWidth="1"/>
-    <col min="7182" max="7182" width="11.42578125" style="213"/>
+    <col min="7169" max="7169" width="4.44140625" style="213" customWidth="1"/>
+    <col min="7170" max="7170" width="20.88671875" style="213" customWidth="1"/>
+    <col min="7171" max="7172" width="11.44140625" style="213"/>
+    <col min="7173" max="7174" width="4.109375" style="213" customWidth="1"/>
+    <col min="7175" max="7175" width="11.44140625" style="213"/>
+    <col min="7176" max="7176" width="19.109375" style="213" customWidth="1"/>
+    <col min="7177" max="7178" width="11.44140625" style="213"/>
+    <col min="7179" max="7180" width="4.88671875" style="213" customWidth="1"/>
+    <col min="7181" max="7181" width="10.88671875" style="213" customWidth="1"/>
+    <col min="7182" max="7182" width="11.44140625" style="213"/>
     <col min="7183" max="7183" width="22" style="213" customWidth="1"/>
-    <col min="7184" max="7185" width="11.42578125" style="213"/>
+    <col min="7184" max="7185" width="11.44140625" style="213"/>
     <col min="7186" max="7187" width="6" style="213" customWidth="1"/>
-    <col min="7188" max="7418" width="11.42578125" style="213"/>
+    <col min="7188" max="7418" width="11.44140625" style="213"/>
     <col min="7419" max="7420" width="20" style="213" customWidth="1"/>
-    <col min="7421" max="7421" width="11.42578125" style="213"/>
-    <col min="7422" max="7423" width="6.140625" style="213" customWidth="1"/>
+    <col min="7421" max="7421" width="11.44140625" style="213"/>
+    <col min="7422" max="7423" width="6.109375" style="213" customWidth="1"/>
     <col min="7424" max="7424" width="14" style="213" customWidth="1"/>
-    <col min="7425" max="7425" width="4.42578125" style="213" customWidth="1"/>
-    <col min="7426" max="7426" width="20.85546875" style="213" customWidth="1"/>
-    <col min="7427" max="7428" width="11.42578125" style="213"/>
-    <col min="7429" max="7430" width="4.140625" style="213" customWidth="1"/>
-    <col min="7431" max="7431" width="11.42578125" style="213"/>
-    <col min="7432" max="7432" width="19.140625" style="213" customWidth="1"/>
-    <col min="7433" max="7434" width="11.42578125" style="213"/>
-    <col min="7435" max="7436" width="4.85546875" style="213" customWidth="1"/>
-    <col min="7437" max="7437" width="10.85546875" style="213" customWidth="1"/>
-    <col min="7438" max="7438" width="11.42578125" style="213"/>
+    <col min="7425" max="7425" width="4.44140625" style="213" customWidth="1"/>
+    <col min="7426" max="7426" width="20.88671875" style="213" customWidth="1"/>
+    <col min="7427" max="7428" width="11.44140625" style="213"/>
+    <col min="7429" max="7430" width="4.109375" style="213" customWidth="1"/>
+    <col min="7431" max="7431" width="11.44140625" style="213"/>
+    <col min="7432" max="7432" width="19.109375" style="213" customWidth="1"/>
+    <col min="7433" max="7434" width="11.44140625" style="213"/>
+    <col min="7435" max="7436" width="4.88671875" style="213" customWidth="1"/>
+    <col min="7437" max="7437" width="10.88671875" style="213" customWidth="1"/>
+    <col min="7438" max="7438" width="11.44140625" style="213"/>
     <col min="7439" max="7439" width="22" style="213" customWidth="1"/>
-    <col min="7440" max="7441" width="11.42578125" style="213"/>
+    <col min="7440" max="7441" width="11.44140625" style="213"/>
     <col min="7442" max="7443" width="6" style="213" customWidth="1"/>
-    <col min="7444" max="7674" width="11.42578125" style="213"/>
+    <col min="7444" max="7674" width="11.44140625" style="213"/>
     <col min="7675" max="7676" width="20" style="213" customWidth="1"/>
-    <col min="7677" max="7677" width="11.42578125" style="213"/>
-    <col min="7678" max="7679" width="6.140625" style="213" customWidth="1"/>
+    <col min="7677" max="7677" width="11.44140625" style="213"/>
+    <col min="7678" max="7679" width="6.109375" style="213" customWidth="1"/>
     <col min="7680" max="7680" width="14" style="213" customWidth="1"/>
-    <col min="7681" max="7681" width="4.42578125" style="213" customWidth="1"/>
-    <col min="7682" max="7682" width="20.85546875" style="213" customWidth="1"/>
-    <col min="7683" max="7684" width="11.42578125" style="213"/>
-    <col min="7685" max="7686" width="4.140625" style="213" customWidth="1"/>
-    <col min="7687" max="7687" width="11.42578125" style="213"/>
-    <col min="7688" max="7688" width="19.140625" style="213" customWidth="1"/>
-    <col min="7689" max="7690" width="11.42578125" style="213"/>
-    <col min="7691" max="7692" width="4.85546875" style="213" customWidth="1"/>
-    <col min="7693" max="7693" width="10.85546875" style="213" customWidth="1"/>
-    <col min="7694" max="7694" width="11.42578125" style="213"/>
+    <col min="7681" max="7681" width="4.44140625" style="213" customWidth="1"/>
+    <col min="7682" max="7682" width="20.88671875" style="213" customWidth="1"/>
+    <col min="7683" max="7684" width="11.44140625" style="213"/>
+    <col min="7685" max="7686" width="4.109375" style="213" customWidth="1"/>
+    <col min="7687" max="7687" width="11.44140625" style="213"/>
+    <col min="7688" max="7688" width="19.109375" style="213" customWidth="1"/>
+    <col min="7689" max="7690" width="11.44140625" style="213"/>
+    <col min="7691" max="7692" width="4.88671875" style="213" customWidth="1"/>
+    <col min="7693" max="7693" width="10.88671875" style="213" customWidth="1"/>
+    <col min="7694" max="7694" width="11.44140625" style="213"/>
     <col min="7695" max="7695" width="22" style="213" customWidth="1"/>
-    <col min="7696" max="7697" width="11.42578125" style="213"/>
+    <col min="7696" max="7697" width="11.44140625" style="213"/>
     <col min="7698" max="7699" width="6" style="213" customWidth="1"/>
-    <col min="7700" max="7930" width="11.42578125" style="213"/>
+    <col min="7700" max="7930" width="11.44140625" style="213"/>
     <col min="7931" max="7932" width="20" style="213" customWidth="1"/>
-    <col min="7933" max="7933" width="11.42578125" style="213"/>
-    <col min="7934" max="7935" width="6.140625" style="213" customWidth="1"/>
+    <col min="7933" max="7933" width="11.44140625" style="213"/>
+    <col min="7934" max="7935" width="6.109375" style="213" customWidth="1"/>
     <col min="7936" max="7936" width="14" style="213" customWidth="1"/>
-    <col min="7937" max="7937" width="4.42578125" style="213" customWidth="1"/>
-    <col min="7938" max="7938" width="20.85546875" style="213" customWidth="1"/>
-    <col min="7939" max="7940" width="11.42578125" style="213"/>
-    <col min="7941" max="7942" width="4.140625" style="213" customWidth="1"/>
-    <col min="7943" max="7943" width="11.42578125" style="213"/>
-    <col min="7944" max="7944" width="19.140625" style="213" customWidth="1"/>
-    <col min="7945" max="7946" width="11.42578125" style="213"/>
-    <col min="7947" max="7948" width="4.85546875" style="213" customWidth="1"/>
-    <col min="7949" max="7949" width="10.85546875" style="213" customWidth="1"/>
-    <col min="7950" max="7950" width="11.42578125" style="213"/>
+    <col min="7937" max="7937" width="4.44140625" style="213" customWidth="1"/>
+    <col min="7938" max="7938" width="20.88671875" style="213" customWidth="1"/>
+    <col min="7939" max="7940" width="11.44140625" style="213"/>
+    <col min="7941" max="7942" width="4.109375" style="213" customWidth="1"/>
+    <col min="7943" max="7943" width="11.44140625" style="213"/>
+    <col min="7944" max="7944" width="19.109375" style="213" customWidth="1"/>
+    <col min="7945" max="7946" width="11.44140625" style="213"/>
+    <col min="7947" max="7948" width="4.88671875" style="213" customWidth="1"/>
+    <col min="7949" max="7949" width="10.88671875" style="213" customWidth="1"/>
+    <col min="7950" max="7950" width="11.44140625" style="213"/>
     <col min="7951" max="7951" width="22" style="213" customWidth="1"/>
-    <col min="7952" max="7953" width="11.42578125" style="213"/>
+    <col min="7952" max="7953" width="11.44140625" style="213"/>
     <col min="7954" max="7955" width="6" style="213" customWidth="1"/>
-    <col min="7956" max="8186" width="11.42578125" style="213"/>
+    <col min="7956" max="8186" width="11.44140625" style="213"/>
     <col min="8187" max="8188" width="20" style="213" customWidth="1"/>
-    <col min="8189" max="8189" width="11.42578125" style="213"/>
-    <col min="8190" max="8191" width="6.140625" style="213" customWidth="1"/>
+    <col min="8189" max="8189" width="11.44140625" style="213"/>
+    <col min="8190" max="8191" width="6.109375" style="213" customWidth="1"/>
     <col min="8192" max="8192" width="14" style="213" customWidth="1"/>
-    <col min="8193" max="8193" width="4.42578125" style="213" customWidth="1"/>
-    <col min="8194" max="8194" width="20.85546875" style="213" customWidth="1"/>
-    <col min="8195" max="8196" width="11.42578125" style="213"/>
-    <col min="8197" max="8198" width="4.140625" style="213" customWidth="1"/>
-    <col min="8199" max="8199" width="11.42578125" style="213"/>
-    <col min="8200" max="8200" width="19.140625" style="213" customWidth="1"/>
-    <col min="8201" max="8202" width="11.42578125" style="213"/>
-    <col min="8203" max="8204" width="4.85546875" style="213" customWidth="1"/>
-    <col min="8205" max="8205" width="10.85546875" style="213" customWidth="1"/>
-    <col min="8206" max="8206" width="11.42578125" style="213"/>
+    <col min="8193" max="8193" width="4.44140625" style="213" customWidth="1"/>
+    <col min="8194" max="8194" width="20.88671875" style="213" customWidth="1"/>
+    <col min="8195" max="8196" width="11.44140625" style="213"/>
+    <col min="8197" max="8198" width="4.109375" style="213" customWidth="1"/>
+    <col min="8199" max="8199" width="11.44140625" style="213"/>
+    <col min="8200" max="8200" width="19.109375" style="213" customWidth="1"/>
+    <col min="8201" max="8202" width="11.44140625" style="213"/>
+    <col min="8203" max="8204" width="4.88671875" style="213" customWidth="1"/>
+    <col min="8205" max="8205" width="10.88671875" style="213" customWidth="1"/>
+    <col min="8206" max="8206" width="11.44140625" style="213"/>
     <col min="8207" max="8207" width="22" style="213" customWidth="1"/>
-    <col min="8208" max="8209" width="11.42578125" style="213"/>
+    <col min="8208" max="8209" width="11.44140625" style="213"/>
     <col min="8210" max="8211" width="6" style="213" customWidth="1"/>
-    <col min="8212" max="8442" width="11.42578125" style="213"/>
+    <col min="8212" max="8442" width="11.44140625" style="213"/>
     <col min="8443" max="8444" width="20" style="213" customWidth="1"/>
-    <col min="8445" max="8445" width="11.42578125" style="213"/>
-    <col min="8446" max="8447" width="6.140625" style="213" customWidth="1"/>
+    <col min="8445" max="8445" width="11.44140625" style="213"/>
+    <col min="8446" max="8447" width="6.109375" style="213" customWidth="1"/>
     <col min="8448" max="8448" width="14" style="213" customWidth="1"/>
-    <col min="8449" max="8449" width="4.42578125" style="213" customWidth="1"/>
-    <col min="8450" max="8450" width="20.85546875" style="213" customWidth="1"/>
-    <col min="8451" max="8452" width="11.42578125" style="213"/>
-    <col min="8453" max="8454" width="4.140625" style="213" customWidth="1"/>
-    <col min="8455" max="8455" width="11.42578125" style="213"/>
-    <col min="8456" max="8456" width="19.140625" style="213" customWidth="1"/>
-    <col min="8457" max="8458" width="11.42578125" style="213"/>
-    <col min="8459" max="8460" width="4.85546875" style="213" customWidth="1"/>
-    <col min="8461" max="8461" width="10.85546875" style="213" customWidth="1"/>
-    <col min="8462" max="8462" width="11.42578125" style="213"/>
+    <col min="8449" max="8449" width="4.44140625" style="213" customWidth="1"/>
+    <col min="8450" max="8450" width="20.88671875" style="213" customWidth="1"/>
+    <col min="8451" max="8452" width="11.44140625" style="213"/>
+    <col min="8453" max="8454" width="4.109375" style="213" customWidth="1"/>
+    <col min="8455" max="8455" width="11.44140625" style="213"/>
+    <col min="8456" max="8456" width="19.109375" style="213" customWidth="1"/>
+    <col min="8457" max="8458" width="11.44140625" style="213"/>
+    <col min="8459" max="8460" width="4.88671875" style="213" customWidth="1"/>
+    <col min="8461" max="8461" width="10.88671875" style="213" customWidth="1"/>
+    <col min="8462" max="8462" width="11.44140625" style="213"/>
     <col min="8463" max="8463" width="22" style="213" customWidth="1"/>
-    <col min="8464" max="8465" width="11.42578125" style="213"/>
+    <col min="8464" max="8465" width="11.44140625" style="213"/>
     <col min="8466" max="8467" width="6" style="213" customWidth="1"/>
-    <col min="8468" max="8698" width="11.42578125" style="213"/>
+    <col min="8468" max="8698" width="11.44140625" style="213"/>
     <col min="8699" max="8700" width="20" style="213" customWidth="1"/>
-    <col min="8701" max="8701" width="11.42578125" style="213"/>
-    <col min="8702" max="8703" width="6.140625" style="213" customWidth="1"/>
+    <col min="8701" max="8701" width="11.44140625" style="213"/>
+    <col min="8702" max="8703" width="6.109375" style="213" customWidth="1"/>
     <col min="8704" max="8704" width="14" style="213" customWidth="1"/>
-    <col min="8705" max="8705" width="4.42578125" style="213" customWidth="1"/>
-    <col min="8706" max="8706" width="20.85546875" style="213" customWidth="1"/>
-    <col min="8707" max="8708" width="11.42578125" style="213"/>
-    <col min="8709" max="8710" width="4.140625" style="213" customWidth="1"/>
-    <col min="8711" max="8711" width="11.42578125" style="213"/>
-    <col min="8712" max="8712" width="19.140625" style="213" customWidth="1"/>
-    <col min="8713" max="8714" width="11.42578125" style="213"/>
-    <col min="8715" max="8716" width="4.85546875" style="213" customWidth="1"/>
-    <col min="8717" max="8717" width="10.85546875" style="213" customWidth="1"/>
-    <col min="8718" max="8718" width="11.42578125" style="213"/>
+    <col min="8705" max="8705" width="4.44140625" style="213" customWidth="1"/>
+    <col min="8706" max="8706" width="20.88671875" style="213" customWidth="1"/>
+    <col min="8707" max="8708" width="11.44140625" style="213"/>
+    <col min="8709" max="8710" width="4.109375" style="213" customWidth="1"/>
+    <col min="8711" max="8711" width="11.44140625" style="213"/>
+    <col min="8712" max="8712" width="19.109375" style="213" customWidth="1"/>
+    <col min="8713" max="8714" width="11.44140625" style="213"/>
+    <col min="8715" max="8716" width="4.88671875" style="213" customWidth="1"/>
+    <col min="8717" max="8717" width="10.88671875" style="213" customWidth="1"/>
+    <col min="8718" max="8718" width="11.44140625" style="213"/>
     <col min="8719" max="8719" width="22" style="213" customWidth="1"/>
-    <col min="8720" max="8721" width="11.42578125" style="213"/>
+    <col min="8720" max="8721" width="11.44140625" style="213"/>
     <col min="8722" max="8723" width="6" style="213" customWidth="1"/>
-    <col min="8724" max="8954" width="11.42578125" style="213"/>
+    <col min="8724" max="8954" width="11.44140625" style="213"/>
     <col min="8955" max="8956" width="20" style="213" customWidth="1"/>
-    <col min="8957" max="8957" width="11.42578125" style="213"/>
-    <col min="8958" max="8959" width="6.140625" style="213" customWidth="1"/>
+    <col min="8957" max="8957" width="11.44140625" style="213"/>
+    <col min="8958" max="8959" width="6.109375" style="213" customWidth="1"/>
     <col min="8960" max="8960" width="14" style="213" customWidth="1"/>
-    <col min="8961" max="8961" width="4.42578125" style="213" customWidth="1"/>
-    <col min="8962" max="8962" width="20.85546875" style="213" customWidth="1"/>
-    <col min="8963" max="8964" width="11.42578125" style="213"/>
-    <col min="8965" max="8966" width="4.140625" style="213" customWidth="1"/>
-    <col min="8967" max="8967" width="11.42578125" style="213"/>
-    <col min="8968" max="8968" width="19.140625" style="213" customWidth="1"/>
-    <col min="8969" max="8970" width="11.42578125" style="213"/>
-    <col min="8971" max="8972" width="4.85546875" style="213" customWidth="1"/>
-    <col min="8973" max="8973" width="10.85546875" style="213" customWidth="1"/>
-    <col min="8974" max="8974" width="11.42578125" style="213"/>
+    <col min="8961" max="8961" width="4.44140625" style="213" customWidth="1"/>
+    <col min="8962" max="8962" width="20.88671875" style="213" customWidth="1"/>
+    <col min="8963" max="8964" width="11.44140625" style="213"/>
+    <col min="8965" max="8966" width="4.109375" style="213" customWidth="1"/>
+    <col min="8967" max="8967" width="11.44140625" style="213"/>
+    <col min="8968" max="8968" width="19.109375" style="213" customWidth="1"/>
+    <col min="8969" max="8970" width="11.44140625" style="213"/>
+    <col min="8971" max="8972" width="4.88671875" style="213" customWidth="1"/>
+    <col min="8973" max="8973" width="10.88671875" style="213" customWidth="1"/>
+    <col min="8974" max="8974" width="11.44140625" style="213"/>
     <col min="8975" max="8975" width="22" style="213" customWidth="1"/>
-    <col min="8976" max="8977" width="11.42578125" style="213"/>
+    <col min="8976" max="8977" width="11.44140625" style="213"/>
     <col min="8978" max="8979" width="6" style="213" customWidth="1"/>
-    <col min="8980" max="9210" width="11.42578125" style="213"/>
+    <col min="8980" max="9210" width="11.44140625" style="213"/>
     <col min="9211" max="9212" width="20" style="213" customWidth="1"/>
-    <col min="9213" max="9213" width="11.42578125" style="213"/>
-    <col min="9214" max="9215" width="6.140625" style="213" customWidth="1"/>
+    <col min="9213" max="9213" width="11.44140625" style="213"/>
+    <col min="9214" max="9215" width="6.109375" style="213" customWidth="1"/>
     <col min="9216" max="9216" width="14" style="213" customWidth="1"/>
-    <col min="9217" max="9217" width="4.42578125" style="213" customWidth="1"/>
-    <col min="9218" max="9218" width="20.85546875" style="213" customWidth="1"/>
-    <col min="9219" max="9220" width="11.42578125" style="213"/>
-    <col min="9221" max="9222" width="4.140625" style="213" customWidth="1"/>
-    <col min="9223" max="9223" width="11.42578125" style="213"/>
-    <col min="9224" max="9224" width="19.140625" style="213" customWidth="1"/>
-    <col min="9225" max="9226" width="11.42578125" style="213"/>
-    <col min="9227" max="9228" width="4.85546875" style="213" customWidth="1"/>
-    <col min="9229" max="9229" width="10.85546875" style="213" customWidth="1"/>
-    <col min="9230" max="9230" width="11.42578125" style="213"/>
+    <col min="9217" max="9217" width="4.44140625" style="213" customWidth="1"/>
+    <col min="9218" max="9218" width="20.88671875" style="213" customWidth="1"/>
+    <col min="9219" max="9220" width="11.44140625" style="213"/>
+    <col min="9221" max="9222" width="4.109375" style="213" customWidth="1"/>
+    <col min="9223" max="9223" width="11.44140625" style="213"/>
+    <col min="9224" max="9224" width="19.109375" style="213" customWidth="1"/>
+    <col min="9225" max="9226" width="11.44140625" style="213"/>
+    <col min="9227" max="9228" width="4.88671875" style="213" customWidth="1"/>
+    <col min="9229" max="9229" width="10.88671875" style="213" customWidth="1"/>
+    <col min="9230" max="9230" width="11.44140625" style="213"/>
     <col min="9231" max="9231" width="22" style="213" customWidth="1"/>
-    <col min="9232" max="9233" width="11.42578125" style="213"/>
+    <col min="9232" max="9233" width="11.44140625" style="213"/>
     <col min="9234" max="9235" width="6" style="213" customWidth="1"/>
-    <col min="9236" max="9466" width="11.42578125" style="213"/>
+    <col min="9236" max="9466" width="11.44140625" style="213"/>
     <col min="9467" max="9468" width="20" style="213" customWidth="1"/>
-    <col min="9469" max="9469" width="11.42578125" style="213"/>
-    <col min="9470" max="9471" width="6.140625" style="213" customWidth="1"/>
+    <col min="9469" max="9469" width="11.44140625" style="213"/>
+    <col min="9470" max="9471" width="6.109375" style="213" customWidth="1"/>
     <col min="9472" max="9472" width="14" style="213" customWidth="1"/>
-    <col min="9473" max="9473" width="4.42578125" style="213" customWidth="1"/>
-    <col min="9474" max="9474" width="20.85546875" style="213" customWidth="1"/>
-    <col min="9475" max="9476" width="11.42578125" style="213"/>
-    <col min="9477" max="9478" width="4.140625" style="213" customWidth="1"/>
-    <col min="9479" max="9479" width="11.42578125" style="213"/>
-    <col min="9480" max="9480" width="19.140625" style="213" customWidth="1"/>
-    <col min="9481" max="9482" width="11.42578125" style="213"/>
-    <col min="9483" max="9484" width="4.85546875" style="213" customWidth="1"/>
-    <col min="9485" max="9485" width="10.85546875" style="213" customWidth="1"/>
-    <col min="9486" max="9486" width="11.42578125" style="213"/>
+    <col min="9473" max="9473" width="4.44140625" style="213" customWidth="1"/>
+    <col min="9474" max="9474" width="20.88671875" style="213" customWidth="1"/>
+    <col min="9475" max="9476" width="11.44140625" style="213"/>
+    <col min="9477" max="9478" width="4.109375" style="213" customWidth="1"/>
+    <col min="9479" max="9479" width="11.44140625" style="213"/>
+    <col min="9480" max="9480" width="19.109375" style="213" customWidth="1"/>
+    <col min="9481" max="9482" width="11.44140625" style="213"/>
+    <col min="9483" max="9484" width="4.88671875" style="213" customWidth="1"/>
+    <col min="9485" max="9485" width="10.88671875" style="213" customWidth="1"/>
+    <col min="9486" max="9486" width="11.44140625" style="213"/>
     <col min="9487" max="9487" width="22" style="213" customWidth="1"/>
-    <col min="9488" max="9489" width="11.42578125" style="213"/>
+    <col min="9488" max="9489" width="11.44140625" style="213"/>
     <col min="9490" max="9491" width="6" style="213" customWidth="1"/>
-    <col min="9492" max="9722" width="11.42578125" style="213"/>
+    <col min="9492" max="9722" width="11.44140625" style="213"/>
     <col min="9723" max="9724" width="20" style="213" customWidth="1"/>
-    <col min="9725" max="9725" width="11.42578125" style="213"/>
-    <col min="9726" max="9727" width="6.140625" style="213" customWidth="1"/>
+    <col min="9725" max="9725" width="11.44140625" style="213"/>
+    <col min="9726" max="9727" width="6.109375" style="213" customWidth="1"/>
     <col min="9728" max="9728" width="14" style="213" customWidth="1"/>
-    <col min="9729" max="9729" width="4.42578125" style="213" customWidth="1"/>
-    <col min="9730" max="9730" width="20.85546875" style="213" customWidth="1"/>
-    <col min="9731" max="9732" width="11.42578125" style="213"/>
-    <col min="9733" max="9734" width="4.140625" style="213" customWidth="1"/>
-    <col min="9735" max="9735" width="11.42578125" style="213"/>
-    <col min="9736" max="9736" width="19.140625" style="213" customWidth="1"/>
-    <col min="9737" max="9738" width="11.42578125" style="213"/>
-    <col min="9739" max="9740" width="4.85546875" style="213" customWidth="1"/>
-    <col min="9741" max="9741" width="10.85546875" style="213" customWidth="1"/>
-    <col min="9742" max="9742" width="11.42578125" style="213"/>
+    <col min="9729" max="9729" width="4.44140625" style="213" customWidth="1"/>
+    <col min="9730" max="9730" width="20.88671875" style="213" customWidth="1"/>
+    <col min="9731" max="9732" width="11.44140625" style="213"/>
+    <col min="9733" max="9734" width="4.109375" style="213" customWidth="1"/>
+    <col min="9735" max="9735" width="11.44140625" style="213"/>
+    <col min="9736" max="9736" width="19.109375" style="213" customWidth="1"/>
+    <col min="9737" max="9738" width="11.44140625" style="213"/>
+    <col min="9739" max="9740" width="4.88671875" style="213" customWidth="1"/>
+    <col min="9741" max="9741" width="10.88671875" style="213" customWidth="1"/>
+    <col min="9742" max="9742" width="11.44140625" style="213"/>
     <col min="9743" max="9743" width="22" style="213" customWidth="1"/>
-    <col min="9744" max="9745" width="11.42578125" style="213"/>
+    <col min="9744" max="9745" width="11.44140625" style="213"/>
     <col min="9746" max="9747" width="6" style="213" customWidth="1"/>
-    <col min="9748" max="9978" width="11.42578125" style="213"/>
+    <col min="9748" max="9978" width="11.44140625" style="213"/>
     <col min="9979" max="9980" width="20" style="213" customWidth="1"/>
-    <col min="9981" max="9981" width="11.42578125" style="213"/>
-    <col min="9982" max="9983" width="6.140625" style="213" customWidth="1"/>
+    <col min="9981" max="9981" width="11.44140625" style="213"/>
+    <col min="9982" max="9983" width="6.109375" style="213" customWidth="1"/>
     <col min="9984" max="9984" width="14" style="213" customWidth="1"/>
-    <col min="9985" max="9985" width="4.42578125" style="213" customWidth="1"/>
-    <col min="9986" max="9986" width="20.85546875" style="213" customWidth="1"/>
-    <col min="9987" max="9988" width="11.42578125" style="213"/>
-    <col min="9989" max="9990" width="4.140625" style="213" customWidth="1"/>
-    <col min="9991" max="9991" width="11.42578125" style="213"/>
-    <col min="9992" max="9992" width="19.140625" style="213" customWidth="1"/>
-    <col min="9993" max="9994" width="11.42578125" style="213"/>
-    <col min="9995" max="9996" width="4.85546875" style="213" customWidth="1"/>
-    <col min="9997" max="9997" width="10.85546875" style="213" customWidth="1"/>
-    <col min="9998" max="9998" width="11.42578125" style="213"/>
+    <col min="9985" max="9985" width="4.44140625" style="213" customWidth="1"/>
+    <col min="9986" max="9986" width="20.88671875" style="213" customWidth="1"/>
+    <col min="9987" max="9988" width="11.44140625" style="213"/>
+    <col min="9989" max="9990" width="4.109375" style="213" customWidth="1"/>
+    <col min="9991" max="9991" width="11.44140625" style="213"/>
+    <col min="9992" max="9992" width="19.109375" style="213" customWidth="1"/>
+    <col min="9993" max="9994" width="11.44140625" style="213"/>
+    <col min="9995" max="9996" width="4.88671875" style="213" customWidth="1"/>
+    <col min="9997" max="9997" width="10.88671875" style="213" customWidth="1"/>
+    <col min="9998" max="9998" width="11.44140625" style="213"/>
     <col min="9999" max="9999" width="22" style="213" customWidth="1"/>
-    <col min="10000" max="10001" width="11.42578125" style="213"/>
+    <col min="10000" max="10001" width="11.44140625" style="213"/>
     <col min="10002" max="10003" width="6" style="213" customWidth="1"/>
-    <col min="10004" max="10234" width="11.42578125" style="213"/>
+    <col min="10004" max="10234" width="11.44140625" style="213"/>
     <col min="10235" max="10236" width="20" style="213" customWidth="1"/>
-    <col min="10237" max="10237" width="11.42578125" style="213"/>
-    <col min="10238" max="10239" width="6.140625" style="213" customWidth="1"/>
+    <col min="10237" max="10237" width="11.44140625" style="213"/>
+    <col min="10238" max="10239" width="6.109375" style="213" customWidth="1"/>
     <col min="10240" max="10240" width="14" style="213" customWidth="1"/>
-    <col min="10241" max="10241" width="4.42578125" style="213" customWidth="1"/>
-    <col min="10242" max="10242" width="20.85546875" style="213" customWidth="1"/>
-    <col min="10243" max="10244" width="11.42578125" style="213"/>
-    <col min="10245" max="10246" width="4.140625" style="213" customWidth="1"/>
-    <col min="10247" max="10247" width="11.42578125" style="213"/>
-    <col min="10248" max="10248" width="19.140625" style="213" customWidth="1"/>
-    <col min="10249" max="10250" width="11.42578125" style="213"/>
-    <col min="10251" max="10252" width="4.85546875" style="213" customWidth="1"/>
-    <col min="10253" max="10253" width="10.85546875" style="213" customWidth="1"/>
-    <col min="10254" max="10254" width="11.42578125" style="213"/>
+    <col min="10241" max="10241" width="4.44140625" style="213" customWidth="1"/>
+    <col min="10242" max="10242" width="20.88671875" style="213" customWidth="1"/>
+    <col min="10243" max="10244" width="11.44140625" style="213"/>
+    <col min="10245" max="10246" width="4.109375" style="213" customWidth="1"/>
+    <col min="10247" max="10247" width="11.44140625" style="213"/>
+    <col min="10248" max="10248" width="19.109375" style="213" customWidth="1"/>
+    <col min="10249" max="10250" width="11.44140625" style="213"/>
+    <col min="10251" max="10252" width="4.88671875" style="213" customWidth="1"/>
+    <col min="10253" max="10253" width="10.88671875" style="213" customWidth="1"/>
+    <col min="10254" max="10254" width="11.44140625" style="213"/>
     <col min="10255" max="10255" width="22" style="213" customWidth="1"/>
-    <col min="10256" max="10257" width="11.42578125" style="213"/>
+    <col min="10256" max="10257" width="11.44140625" style="213"/>
     <col min="10258" max="10259" width="6" style="213" customWidth="1"/>
-    <col min="10260" max="10490" width="11.42578125" style="213"/>
+    <col min="10260" max="10490" width="11.44140625" style="213"/>
     <col min="10491" max="10492" width="20" style="213" customWidth="1"/>
-    <col min="10493" max="10493" width="11.42578125" style="213"/>
-    <col min="10494" max="10495" width="6.140625" style="213" customWidth="1"/>
+    <col min="10493" max="10493" width="11.44140625" style="213"/>
+    <col min="10494" max="10495" width="6.109375" style="213" customWidth="1"/>
     <col min="10496" max="10496" width="14" style="213" customWidth="1"/>
-    <col min="10497" max="10497" width="4.42578125" style="213" customWidth="1"/>
-    <col min="10498" max="10498" width="20.85546875" style="213" customWidth="1"/>
-    <col min="10499" max="10500" width="11.42578125" style="213"/>
-    <col min="10501" max="10502" width="4.140625" style="213" customWidth="1"/>
-    <col min="10503" max="10503" width="11.42578125" style="213"/>
-    <col min="10504" max="10504" width="19.140625" style="213" customWidth="1"/>
-    <col min="10505" max="10506" width="11.42578125" style="213"/>
-    <col min="10507" max="10508" width="4.85546875" style="213" customWidth="1"/>
-    <col min="10509" max="10509" width="10.85546875" style="213" customWidth="1"/>
-    <col min="10510" max="10510" width="11.42578125" style="213"/>
+    <col min="10497" max="10497" width="4.44140625" style="213" customWidth="1"/>
+    <col min="10498" max="10498" width="20.88671875" style="213" customWidth="1"/>
+    <col min="10499" max="10500" width="11.44140625" style="213"/>
+    <col min="10501" max="10502" width="4.109375" style="213" customWidth="1"/>
+    <col min="10503" max="10503" width="11.44140625" style="213"/>
+    <col min="10504" max="10504" width="19.109375" style="213" customWidth="1"/>
+    <col min="10505" max="10506" width="11.44140625" style="213"/>
+    <col min="10507" max="10508" width="4.88671875" style="213" customWidth="1"/>
+    <col min="10509" max="10509" width="10.88671875" style="213" customWidth="1"/>
+    <col min="10510" max="10510" width="11.44140625" style="213"/>
     <col min="10511" max="10511" width="22" style="213" customWidth="1"/>
-    <col min="10512" max="10513" width="11.42578125" style="213"/>
+    <col min="10512" max="10513" width="11.44140625" style="213"/>
     <col min="10514" max="10515" width="6" style="213" customWidth="1"/>
-    <col min="10516" max="10746" width="11.42578125" style="213"/>
+    <col min="10516" max="10746" width="11.44140625" style="213"/>
     <col min="10747" max="10748" width="20" style="213" customWidth="1"/>
-    <col min="10749" max="10749" width="11.42578125" style="213"/>
-    <col min="10750" max="10751" width="6.140625" style="213" customWidth="1"/>
+    <col min="10749" max="10749" width="11.44140625" style="213"/>
+    <col min="10750" max="10751" width="6.109375" style="213" customWidth="1"/>
     <col min="10752" max="10752" width="14" style="213" customWidth="1"/>
-    <col min="10753" max="10753" width="4.42578125" style="213" customWidth="1"/>
-    <col min="10754" max="10754" width="20.85546875" style="213" customWidth="1"/>
-    <col min="10755" max="10756" width="11.42578125" style="213"/>
-    <col min="10757" max="10758" width="4.140625" style="213" customWidth="1"/>
-    <col min="10759" max="10759" width="11.42578125" style="213"/>
-    <col min="10760" max="10760" width="19.140625" style="213" customWidth="1"/>
-    <col min="10761" max="10762" width="11.42578125" style="213"/>
-    <col min="10763" max="10764" width="4.85546875" style="213" customWidth="1"/>
-    <col min="10765" max="10765" width="10.85546875" style="213" customWidth="1"/>
-    <col min="10766" max="10766" width="11.42578125" style="213"/>
+    <col min="10753" max="10753" width="4.44140625" style="213" customWidth="1"/>
+    <col min="10754" max="10754" width="20.88671875" style="213" customWidth="1"/>
+    <col min="10755" max="10756" width="11.44140625" style="213"/>
+    <col min="10757" max="10758" width="4.109375" style="213" customWidth="1"/>
+    <col min="10759" max="10759" width="11.44140625" style="213"/>
+    <col min="10760" max="10760" width="19.109375" style="213" customWidth="1"/>
+    <col min="10761" max="10762" width="11.44140625" style="213"/>
+    <col min="10763" max="10764" width="4.88671875" style="213" customWidth="1"/>
+    <col min="10765" max="10765" width="10.88671875" style="213" customWidth="1"/>
+    <col min="10766" max="10766" width="11.44140625" style="213"/>
     <col min="10767" max="10767" width="22" style="213" customWidth="1"/>
-    <col min="10768" max="10769" width="11.42578125" style="213"/>
+    <col min="10768" max="10769" width="11.44140625" style="213"/>
     <col min="10770" max="10771" width="6" style="213" customWidth="1"/>
-    <col min="10772" max="11002" width="11.42578125" style="213"/>
+    <col min="10772" max="11002" width="11.44140625" style="213"/>
     <col min="11003" max="11004" width="20" style="213" customWidth="1"/>
-    <col min="11005" max="11005" width="11.42578125" style="213"/>
-    <col min="11006" max="11007" width="6.140625" style="213" customWidth="1"/>
+    <col min="11005" max="11005" width="11.44140625" style="213"/>
+    <col min="11006" max="11007" width="6.109375" style="213" customWidth="1"/>
     <col min="11008" max="11008" width="14" style="213" customWidth="1"/>
-    <col min="11009" max="11009" width="4.42578125" style="213" customWidth="1"/>
-    <col min="11010" max="11010" width="20.85546875" style="213" customWidth="1"/>
-    <col min="11011" max="11012" width="11.42578125" style="213"/>
-    <col min="11013" max="11014" width="4.140625" style="213" customWidth="1"/>
-    <col min="11015" max="11015" width="11.42578125" style="213"/>
-    <col min="11016" max="11016" width="19.140625" style="213" customWidth="1"/>
-    <col min="11017" max="11018" width="11.42578125" style="213"/>
-    <col min="11019" max="11020" width="4.85546875" style="213" customWidth="1"/>
-    <col min="11021" max="11021" width="10.85546875" style="213" customWidth="1"/>
-    <col min="11022" max="11022" width="11.42578125" style="213"/>
+    <col min="11009" max="11009" width="4.44140625" style="213" customWidth="1"/>
+    <col min="11010" max="11010" width="20.88671875" style="213" customWidth="1"/>
+    <col min="11011" max="11012" width="11.44140625" style="213"/>
+    <col min="11013" max="11014" width="4.109375" style="213" customWidth="1"/>
+    <col min="11015" max="11015" width="11.44140625" style="213"/>
+    <col min="11016" max="11016" width="19.109375" style="213" customWidth="1"/>
+    <col min="11017" max="11018" width="11.44140625" style="213"/>
+    <col min="11019" max="11020" width="4.88671875" style="213" customWidth="1"/>
+    <col min="11021" max="11021" width="10.88671875" style="213" customWidth="1"/>
+    <col min="11022" max="11022" width="11.44140625" style="213"/>
     <col min="11023" max="11023" width="22" style="213" customWidth="1"/>
-    <col min="11024" max="11025" width="11.42578125" style="213"/>
+    <col min="11024" max="11025" width="11.44140625" style="213"/>
     <col min="11026" max="11027" width="6" style="213" customWidth="1"/>
-    <col min="11028" max="11258" width="11.42578125" style="213"/>
+    <col min="11028" max="11258" width="11.44140625" style="213"/>
     <col min="11259" max="11260" width="20" style="213" customWidth="1"/>
-    <col min="11261" max="11261" width="11.42578125" style="213"/>
-    <col min="11262" max="11263" width="6.140625" style="213" customWidth="1"/>
+    <col min="11261" max="11261" width="11.44140625" style="213"/>
+    <col min="11262" max="11263" width="6.109375" style="213" customWidth="1"/>
     <col min="11264" max="11264" width="14" style="213" customWidth="1"/>
-    <col min="11265" max="11265" width="4.42578125" style="213" customWidth="1"/>
-    <col min="11266" max="11266" width="20.85546875" style="213" customWidth="1"/>
-    <col min="11267" max="11268" width="11.42578125" style="213"/>
-    <col min="11269" max="11270" width="4.140625" style="213" customWidth="1"/>
-    <col min="11271" max="11271" width="11.42578125" style="213"/>
-    <col min="11272" max="11272" width="19.140625" style="213" customWidth="1"/>
-    <col min="11273" max="11274" width="11.42578125" style="213"/>
-    <col min="11275" max="11276" width="4.85546875" style="213" customWidth="1"/>
-    <col min="11277" max="11277" width="10.85546875" style="213" customWidth="1"/>
-    <col min="11278" max="11278" width="11.42578125" style="213"/>
+    <col min="11265" max="11265" width="4.44140625" style="213" customWidth="1"/>
+    <col min="11266" max="11266" width="20.88671875" style="213" customWidth="1"/>
+    <col min="11267" max="11268" width="11.44140625" style="213"/>
+    <col min="11269" max="11270" width="4.109375" style="213" customWidth="1"/>
+    <col min="11271" max="11271" width="11.44140625" style="213"/>
+    <col min="11272" max="11272" width="19.109375" style="213" customWidth="1"/>
+    <col min="11273" max="11274" width="11.44140625" style="213"/>
+    <col min="11275" max="11276" width="4.88671875" style="213" customWidth="1"/>
+    <col min="11277" max="11277" width="10.88671875" style="213" customWidth="1"/>
+    <col min="11278" max="11278" width="11.44140625" style="213"/>
     <col min="11279" max="11279" width="22" style="213" customWidth="1"/>
-    <col min="11280" max="11281" width="11.42578125" style="213"/>
+    <col min="11280" max="11281" width="11.44140625" style="213"/>
     <col min="11282" max="11283" width="6" style="213" customWidth="1"/>
-    <col min="11284" max="11514" width="11.42578125" style="213"/>
+    <col min="11284" max="11514" width="11.44140625" style="213"/>
     <col min="11515" max="11516" width="20" style="213" customWidth="1"/>
-    <col min="11517" max="11517" width="11.42578125" style="213"/>
-    <col min="11518" max="11519" width="6.140625" style="213" customWidth="1"/>
+    <col min="11517" max="11517" width="11.44140625" style="213"/>
+    <col min="11518" max="11519" width="6.109375" style="213" customWidth="1"/>
     <col min="11520" max="11520" width="14" style="213" customWidth="1"/>
-    <col min="11521" max="11521" width="4.42578125" style="213" customWidth="1"/>
-    <col min="11522" max="11522" width="20.85546875" style="213" customWidth="1"/>
-    <col min="11523" max="11524" width="11.42578125" style="213"/>
-    <col min="11525" max="11526" width="4.140625" style="213" customWidth="1"/>
-    <col min="11527" max="11527" width="11.42578125" style="213"/>
-    <col min="11528" max="11528" width="19.140625" style="213" customWidth="1"/>
-    <col min="11529" max="11530" width="11.42578125" style="213"/>
-    <col min="11531" max="11532" width="4.85546875" style="213" customWidth="1"/>
-    <col min="11533" max="11533" width="10.85546875" style="213" customWidth="1"/>
-    <col min="11534" max="11534" width="11.42578125" style="213"/>
+    <col min="11521" max="11521" width="4.44140625" style="213" customWidth="1"/>
+    <col min="11522" max="11522" width="20.88671875" style="213" customWidth="1"/>
+    <col min="11523" max="11524" width="11.44140625" style="213"/>
+    <col min="11525" max="11526" width="4.109375" style="213" customWidth="1"/>
+    <col min="11527" max="11527" width="11.44140625" style="213"/>
+    <col min="11528" max="11528" width="19.109375" style="213" customWidth="1"/>
+    <col min="11529" max="11530" width="11.44140625" style="213"/>
+    <col min="11531" max="11532" width="4.88671875" style="213" customWidth="1"/>
+    <col min="11533" max="11533" width="10.88671875" style="213" customWidth="1"/>
+    <col min="11534" max="11534" width="11.44140625" style="213"/>
     <col min="11535" max="11535" width="22" style="213" customWidth="1"/>
-    <col min="11536" max="11537" width="11.42578125" style="213"/>
+    <col min="11536" max="11537" width="11.44140625" style="213"/>
     <col min="11538" max="11539" width="6" style="213" customWidth="1"/>
-    <col min="11540" max="11770" width="11.42578125" style="213"/>
+    <col min="11540" max="11770" width="11.44140625" style="213"/>
     <col min="11771" max="11772" width="20" style="213" customWidth="1"/>
-    <col min="11773" max="11773" width="11.42578125" style="213"/>
-    <col min="11774" max="11775" width="6.140625" style="213" customWidth="1"/>
+    <col min="11773" max="11773" width="11.44140625" style="213"/>
+    <col min="11774" max="11775" width="6.109375" style="213" customWidth="1"/>
     <col min="11776" max="11776" width="14" style="213" customWidth="1"/>
-    <col min="11777" max="11777" width="4.42578125" style="213" customWidth="1"/>
-    <col min="11778" max="11778" width="20.85546875" style="213" customWidth="1"/>
-    <col min="11779" max="11780" width="11.42578125" style="213"/>
-    <col min="11781" max="11782" width="4.140625" style="213" customWidth="1"/>
-    <col min="11783" max="11783" width="11.42578125" style="213"/>
-    <col min="11784" max="11784" width="19.140625" style="213" customWidth="1"/>
-    <col min="11785" max="11786" width="11.42578125" style="213"/>
-    <col min="11787" max="11788" width="4.85546875" style="213" customWidth="1"/>
-    <col min="11789" max="11789" width="10.85546875" style="213" customWidth="1"/>
-    <col min="11790" max="11790" width="11.42578125" style="213"/>
+    <col min="11777" max="11777" width="4.44140625" style="213" customWidth="1"/>
+    <col min="11778" max="11778" width="20.88671875" style="213" customWidth="1"/>
+    <col min="11779" max="11780" width="11.44140625" style="213"/>
+    <col min="11781" max="11782" width="4.109375" style="213" customWidth="1"/>
+    <col min="11783" max="11783" width="11.44140625" style="213"/>
+    <col min="11784" max="11784" width="19.109375" style="213" customWidth="1"/>
+    <col min="11785" max="11786" width="11.44140625" style="213"/>
+    <col min="11787" max="11788" width="4.88671875" style="213" customWidth="1"/>
+    <col min="11789" max="11789" width="10.88671875" style="213" customWidth="1"/>
+    <col min="11790" max="11790" width="11.44140625" style="213"/>
     <col min="11791" max="11791" width="22" style="213" customWidth="1"/>
-    <col min="11792" max="11793" width="11.42578125" style="213"/>
+    <col min="11792" max="11793" width="11.44140625" style="213"/>
     <col min="11794" max="11795" width="6" style="213" customWidth="1"/>
-    <col min="11796" max="12026" width="11.42578125" style="213"/>
+    <col min="11796" max="12026" width="11.44140625" style="213"/>
     <col min="12027" max="12028" width="20" style="213" customWidth="1"/>
-    <col min="12029" max="12029" width="11.42578125" style="213"/>
-    <col min="12030" max="12031" width="6.140625" style="213" customWidth="1"/>
+    <col min="12029" max="12029" width="11.44140625" style="213"/>
+    <col min="12030" max="12031" width="6.109375" style="213" customWidth="1"/>
     <col min="12032" max="12032" width="14" style="213" customWidth="1"/>
-    <col min="12033" max="12033" width="4.42578125" style="213" customWidth="1"/>
-    <col min="12034" max="12034" width="20.85546875" style="213" customWidth="1"/>
-    <col min="12035" max="12036" width="11.42578125" style="213"/>
-    <col min="12037" max="12038" width="4.140625" style="213" customWidth="1"/>
-    <col min="12039" max="12039" width="11.42578125" style="213"/>
-    <col min="12040" max="12040" width="19.140625" style="213" customWidth="1"/>
-    <col min="12041" max="12042" width="11.42578125" style="213"/>
-    <col min="12043" max="12044" width="4.85546875" style="213" customWidth="1"/>
-    <col min="12045" max="12045" width="10.85546875" style="213" customWidth="1"/>
-    <col min="12046" max="12046" width="11.42578125" style="213"/>
+    <col min="12033" max="12033" width="4.44140625" style="213" customWidth="1"/>
+    <col min="12034" max="12034" width="20.88671875" style="213" customWidth="1"/>
+    <col min="12035" max="12036" width="11.44140625" style="213"/>
+    <col min="12037" max="12038" width="4.109375" style="213" customWidth="1"/>
+    <col min="12039" max="12039" width="11.44140625" style="213"/>
+    <col min="12040" max="12040" width="19.109375" style="213" customWidth="1"/>
+    <col min="12041" max="12042" width="11.44140625" style="213"/>
+    <col min="12043" max="12044" width="4.88671875" style="213" customWidth="1"/>
+    <col min="12045" max="12045" width="10.88671875" style="213" customWidth="1"/>
+    <col min="12046" max="12046" width="11.44140625" style="213"/>
     <col min="12047" max="12047" width="22" style="213" customWidth="1"/>
-    <col min="12048" max="12049" width="11.42578125" style="213"/>
+    <col min="12048" max="12049" width="11.44140625" style="213"/>
     <col min="12050" max="12051" width="6" style="213" customWidth="1"/>
-    <col min="12052" max="12282" width="11.42578125" style="213"/>
+    <col min="12052" max="12282" width="11.44140625" style="213"/>
     <col min="12283" max="12284" width="20" style="213" customWidth="1"/>
-    <col min="12285" max="12285" width="11.42578125" style="213"/>
-    <col min="12286" max="12287" width="6.140625" style="213" customWidth="1"/>
+    <col min="12285" max="12285" width="11.44140625" style="213"/>
+    <col min="12286" max="12287" width="6.109375" style="213" customWidth="1"/>
     <col min="12288" max="12288" width="14" style="213" customWidth="1"/>
-    <col min="12289" max="12289" width="4.42578125" style="213" customWidth="1"/>
-    <col min="12290" max="12290" width="20.85546875" style="213" customWidth="1"/>
-    <col min="12291" max="12292" width="11.42578125" style="213"/>
-    <col min="12293" max="12294" width="4.140625" style="213" customWidth="1"/>
-    <col min="12295" max="12295" width="11.42578125" style="213"/>
-    <col min="12296" max="12296" width="19.140625" style="213" customWidth="1"/>
-    <col min="12297" max="12298" width="11.42578125" style="213"/>
-    <col min="12299" max="12300" width="4.85546875" style="213" customWidth="1"/>
-    <col min="12301" max="12301" width="10.85546875" style="213" customWidth="1"/>
-    <col min="12302" max="12302" width="11.42578125" style="213"/>
+    <col min="12289" max="12289" width="4.44140625" style="213" customWidth="1"/>
+    <col min="12290" max="12290" width="20.88671875" style="213" customWidth="1"/>
+    <col min="12291" max="12292" width="11.44140625" style="213"/>
+    <col min="12293" max="12294" width="4.109375" style="213" customWidth="1"/>
+    <col min="12295" max="12295" width="11.44140625" style="213"/>
+    <col min="12296" max="12296" width="19.109375" style="213" customWidth="1"/>
+    <col min="12297" max="12298" width="11.44140625" style="213"/>
+    <col min="12299" max="12300" width="4.88671875" style="213" customWidth="1"/>
+    <col min="12301" max="12301" width="10.88671875" style="213" customWidth="1"/>
+    <col min="12302" max="12302" width="11.44140625" style="213"/>
     <col min="12303" max="12303" width="22" style="213" customWidth="1"/>
-    <col min="12304" max="12305" width="11.42578125" style="213"/>
+    <col min="12304" max="12305" width="11.44140625" style="213"/>
     <col min="12306" max="12307" width="6" style="213" customWidth="1"/>
-    <col min="12308" max="12538" width="11.42578125" style="213"/>
+    <col min="12308" max="12538" width="11.44140625" style="213"/>
     <col min="12539" max="12540" width="20" style="213" customWidth="1"/>
-    <col min="12541" max="12541" width="11.42578125" style="213"/>
-    <col min="12542" max="12543" width="6.140625" style="213" customWidth="1"/>
+    <col min="12541" max="12541" width="11.44140625" style="213"/>
+    <col min="12542" max="12543" width="6.109375" style="213" customWidth="1"/>
     <col min="12544" max="12544" width="14" style="213" customWidth="1"/>
-    <col min="12545" max="12545" width="4.42578125" style="213" customWidth="1"/>
-    <col min="12546" max="12546" width="20.85546875" style="213" customWidth="1"/>
-    <col min="12547" max="12548" width="11.42578125" style="213"/>
-    <col min="12549" max="12550" width="4.140625" style="213" customWidth="1"/>
-    <col min="12551" max="12551" width="11.42578125" style="213"/>
-    <col min="12552" max="12552" width="19.140625" style="213" customWidth="1"/>
-    <col min="12553" max="12554" width="11.42578125" style="213"/>
-    <col min="12555" max="12556" width="4.85546875" style="213" customWidth="1"/>
-    <col min="12557" max="12557" width="10.85546875" style="213" customWidth="1"/>
-    <col min="12558" max="12558" width="11.42578125" style="213"/>
+    <col min="12545" max="12545" width="4.44140625" style="213" customWidth="1"/>
+    <col min="12546" max="12546" width="20.88671875" style="213" customWidth="1"/>
+    <col min="12547" max="12548" width="11.44140625" style="213"/>
+    <col min="12549" max="12550" width="4.109375" style="213" customWidth="1"/>
+    <col min="12551" max="12551" width="11.44140625" style="213"/>
+    <col min="12552" max="12552" width="19.109375" style="213" customWidth="1"/>
+    <col min="12553" max="12554" width="11.44140625" style="213"/>
+    <col min="12555" max="12556" width="4.88671875" style="213" customWidth="1"/>
+    <col min="12557" max="12557" width="10.88671875" style="213" customWidth="1"/>
+    <col min="12558" max="12558" width="11.44140625" style="213"/>
     <col min="12559" max="12559" width="22" style="213" customWidth="1"/>
-    <col min="12560" max="12561" width="11.42578125" style="213"/>
+    <col min="12560" max="12561" width="11.44140625" style="213"/>
     <col min="12562" max="12563" width="6" style="213" customWidth="1"/>
-    <col min="12564" max="12794" width="11.42578125" style="213"/>
+    <col min="12564" max="12794" width="11.44140625" style="213"/>
     <col min="12795" max="12796" width="20" style="213" customWidth="1"/>
-    <col min="12797" max="12797" width="11.42578125" style="213"/>
-    <col min="12798" max="12799" width="6.140625" style="213" customWidth="1"/>
+    <col min="12797" max="12797" width="11.44140625" style="213"/>
+    <col min="12798" max="12799" width="6.109375" style="213" customWidth="1"/>
     <col min="12800" max="12800" width="14" style="213" customWidth="1"/>
-    <col min="12801" max="12801" width="4.42578125" style="213" customWidth="1"/>
-    <col min="12802" max="12802" width="20.85546875" style="213" customWidth="1"/>
-    <col min="12803" max="12804" width="11.42578125" style="213"/>
-    <col min="12805" max="12806" width="4.140625" style="213" customWidth="1"/>
-    <col min="12807" max="12807" width="11.42578125" style="213"/>
-    <col min="12808" max="12808" width="19.140625" style="213" customWidth="1"/>
-    <col min="12809" max="12810" width="11.42578125" style="213"/>
-    <col min="12811" max="12812" width="4.85546875" style="213" customWidth="1"/>
-    <col min="12813" max="12813" width="10.85546875" style="213" customWidth="1"/>
-    <col min="12814" max="12814" width="11.42578125" style="213"/>
+    <col min="12801" max="12801" width="4.44140625" style="213" customWidth="1"/>
+    <col min="12802" max="12802" width="20.88671875" style="213" customWidth="1"/>
+    <col min="12803" max="12804" width="11.44140625" style="213"/>
+    <col min="12805" max="12806" width="4.109375" style="213" customWidth="1"/>
+    <col min="12807" max="12807" width="11.44140625" style="213"/>
+    <col min="12808" max="12808" width="19.109375" style="213" customWidth="1"/>
+    <col min="12809" max="12810" width="11.44140625" style="213"/>
+    <col min="12811" max="12812" width="4.88671875" style="213" customWidth="1"/>
+    <col min="12813" max="12813" width="10.88671875" style="213" customWidth="1"/>
+    <col min="12814" max="12814" width="11.44140625" style="213"/>
     <col min="12815" max="12815" width="22" style="213" customWidth="1"/>
-    <col min="12816" max="12817" width="11.42578125" style="213"/>
+    <col min="12816" max="12817" width="11.44140625" style="213"/>
     <col min="12818" max="12819" width="6" style="213" customWidth="1"/>
-    <col min="12820" max="13050" width="11.42578125" style="213"/>
+    <col min="12820" max="13050" width="11.44140625" style="213"/>
     <col min="13051" max="13052" width="20" style="213" customWidth="1"/>
-    <col min="13053" max="13053" width="11.42578125" style="213"/>
-    <col min="13054" max="13055" width="6.140625" style="213" customWidth="1"/>
+    <col min="13053" max="13053" width="11.44140625" style="213"/>
+    <col min="13054" max="13055" width="6.109375" style="213" customWidth="1"/>
     <col min="13056" max="13056" width="14" style="213" customWidth="1"/>
-    <col min="13057" max="13057" width="4.42578125" style="213" customWidth="1"/>
-    <col min="13058" max="13058" width="20.85546875" style="213" customWidth="1"/>
-    <col min="13059" max="13060" width="11.42578125" style="213"/>
-    <col min="13061" max="13062" width="4.140625" style="213" customWidth="1"/>
-    <col min="13063" max="13063" width="11.42578125" style="213"/>
-    <col min="13064" max="13064" width="19.140625" style="213" customWidth="1"/>
-    <col min="13065" max="13066" width="11.42578125" style="213"/>
-    <col min="13067" max="13068" width="4.85546875" style="213" customWidth="1"/>
-    <col min="13069" max="13069" width="10.85546875" style="213" customWidth="1"/>
-    <col min="13070" max="13070" width="11.42578125" style="213"/>
+    <col min="13057" max="13057" width="4.44140625" style="213" customWidth="1"/>
+    <col min="13058" max="13058" width="20.88671875" style="213" customWidth="1"/>
+    <col min="13059" max="13060" width="11.44140625" style="213"/>
+    <col min="13061" max="13062" width="4.109375" style="213" customWidth="1"/>
+    <col min="13063" max="13063" width="11.44140625" style="213"/>
+    <col min="13064" max="13064" width="19.109375" style="213" customWidth="1"/>
+    <col min="13065" max="13066" width="11.44140625" style="213"/>
+    <col min="13067" max="13068" width="4.88671875" style="213" customWidth="1"/>
+    <col min="13069" max="13069" width="10.88671875" style="213" customWidth="1"/>
+    <col min="13070" max="13070" width="11.44140625" style="213"/>
     <col min="13071" max="13071" width="22" style="213" customWidth="1"/>
-    <col min="13072" max="13073" width="11.42578125" style="213"/>
+    <col min="13072" max="13073" width="11.44140625" style="213"/>
     <col min="13074" max="13075" width="6" style="213" customWidth="1"/>
-    <col min="13076" max="13306" width="11.42578125" style="213"/>
+    <col min="13076" max="13306" width="11.44140625" style="213"/>
     <col min="13307" max="13308" width="20" style="213" customWidth="1"/>
-    <col min="13309" max="13309" width="11.42578125" style="213"/>
-    <col min="13310" max="13311" width="6.140625" style="213" customWidth="1"/>
+    <col min="13309" max="13309" width="11.44140625" style="213"/>
+    <col min="13310" max="13311" width="6.109375" style="213" customWidth="1"/>
     <col min="13312" max="13312" width="14" style="213" customWidth="1"/>
-    <col min="13313" max="13313" width="4.42578125" style="213" customWidth="1"/>
-    <col min="13314" max="13314" width="20.85546875" style="213" customWidth="1"/>
-    <col min="13315" max="13316" width="11.42578125" style="213"/>
-    <col min="13317" max="13318" width="4.140625" style="213" customWidth="1"/>
-    <col min="13319" max="13319" width="11.42578125" style="213"/>
-    <col min="13320" max="13320" width="19.140625" style="213" customWidth="1"/>
-    <col min="13321" max="13322" width="11.42578125" style="213"/>
-    <col min="13323" max="13324" width="4.85546875" style="213" customWidth="1"/>
-    <col min="13325" max="13325" width="10.85546875" style="213" customWidth="1"/>
-    <col min="13326" max="13326" width="11.42578125" style="213"/>
+    <col min="13313" max="13313" width="4.44140625" style="213" customWidth="1"/>
+    <col min="13314" max="13314" width="20.88671875" style="213" customWidth="1"/>
+    <col min="13315" max="13316" width="11.44140625" style="213"/>
+    <col min="13317" max="13318" width="4.109375" style="213" customWidth="1"/>
+    <col min="13319" max="13319" width="11.44140625" style="213"/>
+    <col min="13320" max="13320" width="19.109375" style="213" customWidth="1"/>
+    <col min="13321" max="13322" width="11.44140625" style="213"/>
+    <col min="13323" max="13324" width="4.88671875" style="213" customWidth="1"/>
+    <col min="13325" max="13325" width="10.88671875" style="213" customWidth="1"/>
+    <col min="13326" max="13326" width="11.44140625" style="213"/>
     <col min="13327" max="13327" width="22" style="213" customWidth="1"/>
-    <col min="13328" max="13329" width="11.42578125" style="213"/>
+    <col min="13328" max="13329" width="11.44140625" style="213"/>
     <col min="13330" max="13331" width="6" style="213" customWidth="1"/>
-    <col min="13332" max="13562" width="11.42578125" style="213"/>
+    <col min="13332" max="13562" width="11.44140625" style="213"/>
     <col min="13563" max="13564" width="20" style="213" customWidth="1"/>
-    <col min="13565" max="13565" width="11.42578125" style="213"/>
-    <col min="13566" max="13567" width="6.140625" style="213" customWidth="1"/>
+    <col min="13565" max="13565" width="11.44140625" style="213"/>
+    <col min="13566" max="13567" width="6.109375" style="213" customWidth="1"/>
     <col min="13568" max="13568" width="14" style="213" customWidth="1"/>
-    <col min="13569" max="13569" width="4.42578125" style="213" customWidth="1"/>
-    <col min="13570" max="13570" width="20.85546875" style="213" customWidth="1"/>
-    <col min="13571" max="13572" width="11.42578125" style="213"/>
-    <col min="13573" max="13574" width="4.140625" style="213" customWidth="1"/>
-    <col min="13575" max="13575" width="11.42578125" style="213"/>
-    <col min="13576" max="13576" width="19.140625" style="213" customWidth="1"/>
-    <col min="13577" max="13578" width="11.42578125" style="213"/>
-    <col min="13579" max="13580" width="4.85546875" style="213" customWidth="1"/>
-    <col min="13581" max="13581" width="10.85546875" style="213" customWidth="1"/>
-    <col min="13582" max="13582" width="11.42578125" style="213"/>
+    <col min="13569" max="13569" width="4.44140625" style="213" customWidth="1"/>
+    <col min="13570" max="13570" width="20.88671875" style="213" customWidth="1"/>
+    <col min="13571" max="13572" width="11.44140625" style="213"/>
+    <col min="13573" max="13574" width="4.109375" style="213" customWidth="1"/>
+    <col min="13575" max="13575" width="11.44140625" style="213"/>
+    <col min="13576" max="13576" width="19.109375" style="213" customWidth="1"/>
+    <col min="13577" max="13578" width="11.44140625" style="213"/>
+    <col min="13579" max="13580" width="4.88671875" style="213" customWidth="1"/>
+    <col min="13581" max="13581" width="10.88671875" style="213" customWidth="1"/>
+    <col min="13582" max="13582" width="11.44140625" style="213"/>
     <col min="13583" max="13583" width="22" style="213" customWidth="1"/>
-    <col min="13584" max="13585" width="11.42578125" style="213"/>
+    <col min="13584" max="13585" width="11.44140625" style="213"/>
     <col min="13586" max="13587" width="6" style="213" customWidth="1"/>
-    <col min="13588" max="13818" width="11.42578125" style="213"/>
+    <col min="13588" max="13818" width="11.44140625" style="213"/>
     <col min="13819" max="13820" width="20" style="213" customWidth="1"/>
-    <col min="13821" max="13821" width="11.42578125" style="213"/>
-    <col min="13822" max="13823" width="6.140625" style="213" customWidth="1"/>
+    <col min="13821" max="13821" width="11.44140625" style="213"/>
+    <col min="13822" max="13823" width="6.109375" style="213" customWidth="1"/>
     <col min="13824" max="13824" width="14" style="213" customWidth="1"/>
-    <col min="13825" max="13825" width="4.42578125" style="213" customWidth="1"/>
-    <col min="13826" max="13826" width="20.85546875" style="213" customWidth="1"/>
-    <col min="13827" max="13828" width="11.42578125" style="213"/>
-    <col min="13829" max="13830" width="4.140625" style="213" customWidth="1"/>
-    <col min="13831" max="13831" width="11.42578125" style="213"/>
-    <col min="13832" max="13832" width="19.140625" style="213" customWidth="1"/>
-    <col min="13833" max="13834" width="11.42578125" style="213"/>
-    <col min="13835" max="13836" width="4.85546875" style="213" customWidth="1"/>
-    <col min="13837" max="13837" width="10.85546875" style="213" customWidth="1"/>
-    <col min="13838" max="13838" width="11.42578125" style="213"/>
+    <col min="13825" max="13825" width="4.44140625" style="213" customWidth="1"/>
+    <col min="13826" max="13826" width="20.88671875" style="213" customWidth="1"/>
+    <col min="13827" max="13828" width="11.44140625" style="213"/>
+    <col min="13829" max="13830" width="4.109375" style="213" customWidth="1"/>
+    <col min="13831" max="13831" width="11.44140625" style="213"/>
+    <col min="13832" max="13832" width="19.109375" style="213" customWidth="1"/>
+    <col min="13833" max="13834" width="11.44140625" style="213"/>
+    <col min="13835" max="13836" width="4.88671875" style="213" customWidth="1"/>
+    <col min="13837" max="13837" width="10.88671875" style="213" customWidth="1"/>
+    <col min="13838" max="13838" width="11.44140625" style="213"/>
     <col min="13839" max="13839" width="22" style="213" customWidth="1"/>
-    <col min="13840" max="13841" width="11.42578125" style="213"/>
+    <col min="13840" max="13841" width="11.44140625" style="213"/>
     <col min="13842" max="13843" width="6" style="213" customWidth="1"/>
-    <col min="13844" max="14074" width="11.42578125" style="213"/>
+    <col min="13844" max="14074" width="11.44140625" style="213"/>
     <col min="14075" max="14076" width="20" style="213" customWidth="1"/>
-    <col min="14077" max="14077" width="11.42578125" style="213"/>
-    <col min="14078" max="14079" width="6.140625" style="213" customWidth="1"/>
+    <col min="14077" max="14077" width="11.44140625" style="213"/>
+    <col min="14078" max="14079" width="6.109375" style="213" customWidth="1"/>
     <col min="14080" max="14080" width="14" style="213" customWidth="1"/>
-    <col min="14081" max="14081" width="4.42578125" style="213" customWidth="1"/>
-    <col min="14082" max="14082" width="20.85546875" style="213" customWidth="1"/>
-    <col min="14083" max="14084" width="11.42578125" style="213"/>
-    <col min="14085" max="14086" width="4.140625" style="213" customWidth="1"/>
-    <col min="14087" max="14087" width="11.42578125" style="213"/>
-    <col min="14088" max="14088" width="19.140625" style="213" customWidth="1"/>
-    <col min="14089" max="14090" width="11.42578125" style="213"/>
-    <col min="14091" max="14092" width="4.85546875" style="213" customWidth="1"/>
-    <col min="14093" max="14093" width="10.85546875" style="213" customWidth="1"/>
-    <col min="14094" max="14094" width="11.42578125" style="213"/>
+    <col min="14081" max="14081" width="4.44140625" style="213" customWidth="1"/>
+    <col min="14082" max="14082" width="20.88671875" style="213" customWidth="1"/>
+    <col min="14083" max="14084" width="11.44140625" style="213"/>
+    <col min="14085" max="14086" width="4.109375" style="213" customWidth="1"/>
+    <col min="14087" max="14087" width="11.44140625" style="213"/>
+    <col min="14088" max="14088" width="19.109375" style="213" customWidth="1"/>
+    <col min="14089" max="14090" width="11.44140625" style="213"/>
+    <col min="14091" max="14092" width="4.88671875" style="213" customWidth="1"/>
+    <col min="14093" max="14093" width="10.88671875" style="213" customWidth="1"/>
+    <col min="14094" max="14094" width="11.44140625" style="213"/>
     <col min="14095" max="14095" width="22" style="213" customWidth="1"/>
-    <col min="14096" max="14097" width="11.42578125" style="213"/>
+    <col min="14096" max="14097" width="11.44140625" style="213"/>
     <col min="14098" max="14099" width="6" style="213" customWidth="1"/>
-    <col min="14100" max="14330" width="11.42578125" style="213"/>
+    <col min="14100" max="14330" width="11.44140625" style="213"/>
     <col min="14331" max="14332" width="20" style="213" customWidth="1"/>
-    <col min="14333" max="14333" width="11.42578125" style="213"/>
-    <col min="14334" max="14335" width="6.140625" style="213" customWidth="1"/>
+    <col min="14333" max="14333" width="11.44140625" style="213"/>
+    <col min="14334" max="14335" width="6.109375" style="213" customWidth="1"/>
     <col min="14336" max="14336" width="14" style="213" customWidth="1"/>
-    <col min="14337" max="14337" width="4.42578125" style="213" customWidth="1"/>
-    <col min="14338" max="14338" width="20.85546875" style="213" customWidth="1"/>
-    <col min="14339" max="14340" width="11.42578125" style="213"/>
-    <col min="14341" max="14342" width="4.140625" style="213" customWidth="1"/>
-    <col min="14343" max="14343" width="11.42578125" style="213"/>
-    <col min="14344" max="14344" width="19.140625" style="213" customWidth="1"/>
-    <col min="14345" max="14346" width="11.42578125" style="213"/>
-    <col min="14347" max="14348" width="4.85546875" style="213" customWidth="1"/>
-    <col min="14349" max="14349" width="10.85546875" style="213" customWidth="1"/>
-    <col min="14350" max="14350" width="11.42578125" style="213"/>
+    <col min="14337" max="14337" width="4.44140625" style="213" customWidth="1"/>
+    <col min="14338" max="14338" width="20.88671875" style="213" customWidth="1"/>
+    <col min="14339" max="14340" width="11.44140625" style="213"/>
+    <col min="14341" max="14342" width="4.109375" style="213" customWidth="1"/>
+    <col min="14343" max="14343" width="11.44140625" style="213"/>
+    <col min="14344" max="14344" width="19.109375" style="213" customWidth="1"/>
+    <col min="14345" max="14346" width="11.44140625" style="213"/>
+    <col min="14347" max="14348" width="4.88671875" style="213" customWidth="1"/>
+    <col min="14349" max="14349" width="10.88671875" style="213" customWidth="1"/>
+    <col min="14350" max="14350" width="11.44140625" style="213"/>
     <col min="14351" max="14351" width="22" style="213" customWidth="1"/>
-    <col min="14352" max="14353" width="11.42578125" style="213"/>
+    <col min="14352" max="14353" width="11.44140625" style="213"/>
     <col min="14354" max="14355" width="6" style="213" customWidth="1"/>
-    <col min="14356" max="14586" width="11.42578125" style="213"/>
+    <col min="14356" max="14586" width="11.44140625" style="213"/>
     <col min="14587" max="14588" width="20" style="213" customWidth="1"/>
-    <col min="14589" max="14589" width="11.42578125" style="213"/>
-    <col min="14590" max="14591" width="6.140625" style="213" customWidth="1"/>
+    <col min="14589" max="14589" width="11.44140625" style="213"/>
+    <col min="14590" max="14591" width="6.109375" style="213" customWidth="1"/>
     <col min="14592" max="14592" width="14" style="213" customWidth="1"/>
-    <col min="14593" max="14593" width="4.42578125" style="213" customWidth="1"/>
-    <col min="14594" max="14594" width="20.85546875" style="213" customWidth="1"/>
-    <col min="14595" max="14596" width="11.42578125" style="213"/>
-    <col min="14597" max="14598" width="4.140625" style="213" customWidth="1"/>
-    <col min="14599" max="14599" width="11.42578125" style="213"/>
-    <col min="14600" max="14600" width="19.140625" style="213" customWidth="1"/>
-    <col min="14601" max="14602" width="11.42578125" style="213"/>
-    <col min="14603" max="14604" width="4.85546875" style="213" customWidth="1"/>
-    <col min="14605" max="14605" width="10.85546875" style="213" customWidth="1"/>
-    <col min="14606" max="14606" width="11.42578125" style="213"/>
+    <col min="14593" max="14593" width="4.44140625" style="213" customWidth="1"/>
+    <col min="14594" max="14594" width="20.88671875" style="213" customWidth="1"/>
+    <col min="14595" max="14596" width="11.44140625" style="213"/>
+    <col min="14597" max="14598" width="4.109375" style="213" customWidth="1"/>
+    <col min="14599" max="14599" width="11.44140625" style="213"/>
+    <col min="14600" max="14600" width="19.109375" style="213" customWidth="1"/>
+    <col min="14601" max="14602" width="11.44140625" style="213"/>
+    <col min="14603" max="14604" width="4.88671875" style="213" customWidth="1"/>
+    <col min="14605" max="14605" width="10.88671875" style="213" customWidth="1"/>
+    <col min="14606" max="14606" width="11.44140625" style="213"/>
     <col min="14607" max="14607" width="22" style="213" customWidth="1"/>
-    <col min="14608" max="14609" width="11.42578125" style="213"/>
+    <col min="14608" max="14609" width="11.44140625" style="213"/>
     <col min="14610" max="14611" width="6" style="213" customWidth="1"/>
-    <col min="14612" max="14842" width="11.42578125" style="213"/>
+    <col min="14612" max="14842" width="11.44140625" style="213"/>
     <col min="14843" max="14844" width="20" style="213" customWidth="1"/>
-    <col min="14845" max="14845" width="11.42578125" style="213"/>
-    <col min="14846" max="14847" width="6.140625" style="213" customWidth="1"/>
+    <col min="14845" max="14845" width="11.44140625" style="213"/>
+    <col min="14846" max="14847" width="6.109375" style="213" customWidth="1"/>
     <col min="14848" max="14848" width="14" style="213" customWidth="1"/>
-    <col min="14849" max="14849" width="4.42578125" style="213" customWidth="1"/>
-    <col min="14850" max="14850" width="20.85546875" style="213" customWidth="1"/>
-    <col min="14851" max="14852" width="11.42578125" style="213"/>
-    <col min="14853" max="14854" width="4.140625" style="213" customWidth="1"/>
-    <col min="14855" max="14855" width="11.42578125" style="213"/>
-    <col min="14856" max="14856" width="19.140625" style="213" customWidth="1"/>
-    <col min="14857" max="14858" width="11.42578125" style="213"/>
-    <col min="14859" max="14860" width="4.85546875" style="213" customWidth="1"/>
-    <col min="14861" max="14861" width="10.85546875" style="213" customWidth="1"/>
-    <col min="14862" max="14862" width="11.42578125" style="213"/>
+    <col min="14849" max="14849" width="4.44140625" style="213" customWidth="1"/>
+    <col min="14850" max="14850" width="20.88671875" style="213" customWidth="1"/>
+    <col min="14851" max="14852" width="11.44140625" style="213"/>
+    <col min="14853" max="14854" width="4.109375" style="213" customWidth="1"/>
+    <col min="14855" max="14855" width="11.44140625" style="213"/>
+    <col min="14856" max="14856" width="19.109375" style="213" customWidth="1"/>
+    <col min="14857" max="14858" width="11.44140625" style="213"/>
+    <col min="14859" max="14860" width="4.88671875" style="213" customWidth="1"/>
+    <col min="14861" max="14861" width="10.88671875" style="213" customWidth="1"/>
+    <col min="14862" max="14862" width="11.44140625" style="213"/>
     <col min="14863" max="14863" width="22" style="213" customWidth="1"/>
-    <col min="14864" max="14865" width="11.42578125" style="213"/>
+    <col min="14864" max="14865" width="11.44140625" style="213"/>
     <col min="14866" max="14867" width="6" style="213" customWidth="1"/>
-    <col min="14868" max="15098" width="11.42578125" style="213"/>
+    <col min="14868" max="15098" width="11.44140625" style="213"/>
     <col min="15099" max="15100" width="20" style="213" customWidth="1"/>
-    <col min="15101" max="15101" width="11.42578125" style="213"/>
-    <col min="15102" max="15103" width="6.140625" style="213" customWidth="1"/>
+    <col min="15101" max="15101" width="11.44140625" style="213"/>
+    <col min="15102" max="15103" width="6.109375" style="213" customWidth="1"/>
     <col min="15104" max="15104" width="14" style="213" customWidth="1"/>
-    <col min="15105" max="15105" width="4.42578125" style="213" customWidth="1"/>
-    <col min="15106" max="15106" width="20.85546875" style="213" customWidth="1"/>
-    <col min="15107" max="15108" width="11.42578125" style="213"/>
-    <col min="15109" max="15110" width="4.140625" style="213" customWidth="1"/>
-    <col min="15111" max="15111" width="11.42578125" style="213"/>
-    <col min="15112" max="15112" width="19.140625" style="213" customWidth="1"/>
-    <col min="15113" max="15114" width="11.42578125" style="213"/>
-    <col min="15115" max="15116" width="4.85546875" style="213" customWidth="1"/>
-    <col min="15117" max="15117" width="10.85546875" style="213" customWidth="1"/>
-    <col min="15118" max="15118" width="11.42578125" style="213"/>
+    <col min="15105" max="15105" width="4.44140625" style="213" customWidth="1"/>
+    <col min="15106" max="15106" width="20.88671875" style="213" customWidth="1"/>
+    <col min="15107" max="15108" width="11.44140625" style="213"/>
+    <col min="15109" max="15110" width="4.109375" style="213" customWidth="1"/>
+    <col min="15111" max="15111" width="11.44140625" style="213"/>
+    <col min="15112" max="15112" width="19.109375" style="213" customWidth="1"/>
+    <col min="15113" max="15114" width="11.44140625" style="213"/>
+    <col min="15115" max="15116" width="4.88671875" style="213" customWidth="1"/>
+    <col min="15117" max="15117" width="10.88671875" style="213" customWidth="1"/>
+    <col min="15118" max="15118" width="11.44140625" style="213"/>
     <col min="15119" max="15119" width="22" style="213" customWidth="1"/>
-    <col min="15120" max="15121" width="11.42578125" style="213"/>
+    <col min="15120" max="15121" width="11.44140625" style="213"/>
     <col min="15122" max="15123" width="6" style="213" customWidth="1"/>
-    <col min="15124" max="15354" width="11.42578125" style="213"/>
+    <col min="15124" max="15354" width="11.44140625" style="213"/>
     <col min="15355" max="15356" width="20" style="213" customWidth="1"/>
-    <col min="15357" max="15357" width="11.42578125" style="213"/>
-    <col min="15358" max="15359" width="6.140625" style="213" customWidth="1"/>
+    <col min="15357" max="15357" width="11.44140625" style="213"/>
+    <col min="15358" max="15359" width="6.109375" style="213" customWidth="1"/>
     <col min="15360" max="15360" width="14" style="213" customWidth="1"/>
-    <col min="15361" max="15361" width="4.42578125" style="213" customWidth="1"/>
-    <col min="15362" max="15362" width="20.85546875" style="213" customWidth="1"/>
-    <col min="15363" max="15364" width="11.42578125" style="213"/>
-    <col min="15365" max="15366" width="4.140625" style="213" customWidth="1"/>
-    <col min="15367" max="15367" width="11.42578125" style="213"/>
-    <col min="15368" max="15368" width="19.140625" style="213" customWidth="1"/>
-    <col min="15369" max="15370" width="11.42578125" style="213"/>
-    <col min="15371" max="15372" width="4.85546875" style="213" customWidth="1"/>
-    <col min="15373" max="15373" width="10.85546875" style="213" customWidth="1"/>
-    <col min="15374" max="15374" width="11.42578125" style="213"/>
+    <col min="15361" max="15361" width="4.44140625" style="213" customWidth="1"/>
+    <col min="15362" max="15362" width="20.88671875" style="213" customWidth="1"/>
+    <col min="15363" max="15364" width="11.44140625" style="213"/>
+    <col min="15365" max="15366" width="4.109375" style="213" customWidth="1"/>
+    <col min="15367" max="15367" width="11.44140625" style="213"/>
+    <col min="15368" max="15368" width="19.109375" style="213" customWidth="1"/>
+    <col min="15369" max="15370" width="11.44140625" style="213"/>
+    <col min="15371" max="15372" width="4.88671875" style="213" customWidth="1"/>
+    <col min="15373" max="15373" width="10.88671875" style="213" customWidth="1"/>
+    <col min="15374" max="15374" width="11.44140625" style="213"/>
     <col min="15375" max="15375" width="22" style="213" customWidth="1"/>
-    <col min="15376" max="15377" width="11.42578125" style="213"/>
+    <col min="15376" max="15377" width="11.44140625" style="213"/>
     <col min="15378" max="15379" width="6" style="213" customWidth="1"/>
-    <col min="15380" max="15610" width="11.42578125" style="213"/>
+    <col min="15380" max="15610" width="11.44140625" style="213"/>
     <col min="15611" max="15612" width="20" style="213" customWidth="1"/>
-    <col min="15613" max="15613" width="11.42578125" style="213"/>
-    <col min="15614" max="15615" width="6.140625" style="213" customWidth="1"/>
+    <col min="15613" max="15613" width="11.44140625" style="213"/>
+    <col min="15614" max="15615" width="6.109375" style="213" customWidth="1"/>
     <col min="15616" max="15616" width="14" style="213" customWidth="1"/>
-    <col min="15617" max="15617" width="4.42578125" style="213" customWidth="1"/>
-    <col min="15618" max="15618" width="20.85546875" style="213" customWidth="1"/>
-    <col min="15619" max="15620" width="11.42578125" style="213"/>
-    <col min="15621" max="15622" width="4.140625" style="213" customWidth="1"/>
-    <col min="15623" max="15623" width="11.42578125" style="213"/>
-    <col min="15624" max="15624" width="19.140625" style="213" customWidth="1"/>
-    <col min="15625" max="15626" width="11.42578125" style="213"/>
-    <col min="15627" max="15628" width="4.85546875" style="213" customWidth="1"/>
-    <col min="15629" max="15629" width="10.85546875" style="213" customWidth="1"/>
-    <col min="15630" max="15630" width="11.42578125" style="213"/>
+    <col min="15617" max="15617" width="4.44140625" style="213" customWidth="1"/>
+    <col min="15618" max="15618" width="20.88671875" style="213" customWidth="1"/>
+    <col min="15619" max="15620" width="11.44140625" style="213"/>
+    <col min="15621" max="15622" width="4.109375" style="213" customWidth="1"/>
+    <col min="15623" max="15623" width="11.44140625" style="213"/>
+    <col min="15624" max="15624" width="19.109375" style="213" customWidth="1"/>
+    <col min="15625" max="15626" width="11.44140625" style="213"/>
+    <col min="15627" max="15628" width="4.88671875" style="213" customWidth="1"/>
+    <col min="15629" max="15629" width="10.88671875" style="213" customWidth="1"/>
+    <col min="15630" max="15630" width="11.44140625" style="213"/>
     <col min="15631" max="15631" width="22" style="213" customWidth="1"/>
-    <col min="15632" max="15633" width="11.42578125" style="213"/>
+    <col min="15632" max="15633" width="11.44140625" style="213"/>
     <col min="15634" max="15635" width="6" style="213" customWidth="1"/>
-    <col min="15636" max="15866" width="11.42578125" style="213"/>
+    <col min="15636" max="15866" width="11.44140625" style="213"/>
     <col min="15867" max="15868" width="20" style="213" customWidth="1"/>
-    <col min="15869" max="15869" width="11.42578125" style="213"/>
-    <col min="15870" max="15871" width="6.140625" style="213" customWidth="1"/>
+    <col min="15869" max="15869" width="11.44140625" style="213"/>
+    <col min="15870" max="15871" width="6.109375" style="213" customWidth="1"/>
     <col min="15872" max="15872" width="14" style="213" customWidth="1"/>
-    <col min="15873" max="15873" width="4.42578125" style="213" customWidth="1"/>
-    <col min="15874" max="15874" width="20.85546875" style="213" customWidth="1"/>
-    <col min="15875" max="15876" width="11.42578125" style="213"/>
-    <col min="15877" max="15878" width="4.140625" style="213" customWidth="1"/>
-    <col min="15879" max="15879" width="11.42578125" style="213"/>
-    <col min="15880" max="15880" width="19.140625" style="213" customWidth="1"/>
-    <col min="15881" max="15882" width="11.42578125" style="213"/>
-    <col min="15883" max="15884" width="4.85546875" style="213" customWidth="1"/>
-    <col min="15885" max="15885" width="10.85546875" style="213" customWidth="1"/>
-    <col min="15886" max="15886" width="11.42578125" style="213"/>
+    <col min="15873" max="15873" width="4.44140625" style="213" customWidth="1"/>
+    <col min="15874" max="15874" width="20.88671875" style="213" customWidth="1"/>
+    <col min="15875" max="15876" width="11.44140625" style="213"/>
+    <col min="15877" max="15878" width="4.109375" style="213" customWidth="1"/>
+    <col min="15879" max="15879" width="11.44140625" style="213"/>
+    <col min="15880" max="15880" width="19.109375" style="213" customWidth="1"/>
+    <col min="15881" max="15882" width="11.44140625" style="213"/>
+    <col min="15883" max="15884" width="4.88671875" style="213" customWidth="1"/>
+    <col min="15885" max="15885" width="10.88671875" style="213" customWidth="1"/>
+    <col min="15886" max="15886" width="11.44140625" style="213"/>
     <col min="15887" max="15887" width="22" style="213" customWidth="1"/>
-    <col min="15888" max="15889" width="11.42578125" style="213"/>
+    <col min="15888" max="15889" width="11.44140625" style="213"/>
     <col min="15890" max="15891" width="6" style="213" customWidth="1"/>
-    <col min="15892" max="16122" width="11.42578125" style="213"/>
+    <col min="15892" max="16122" width="11.44140625" style="213"/>
     <col min="16123" max="16124" width="20" style="213" customWidth="1"/>
-    <col min="16125" max="16125" width="11.42578125" style="213"/>
-    <col min="16126" max="16127" width="6.140625" style="213" customWidth="1"/>
+    <col min="16125" max="16125" width="11.44140625" style="213"/>
+    <col min="16126" max="16127" width="6.109375" style="213" customWidth="1"/>
     <col min="16128" max="16128" width="14" style="213" customWidth="1"/>
-    <col min="16129" max="16129" width="4.42578125" style="213" customWidth="1"/>
-    <col min="16130" max="16130" width="20.85546875" style="213" customWidth="1"/>
-    <col min="16131" max="16132" width="11.42578125" style="213"/>
-    <col min="16133" max="16134" width="4.140625" style="213" customWidth="1"/>
-    <col min="16135" max="16135" width="11.42578125" style="213"/>
-    <col min="16136" max="16136" width="19.140625" style="213" customWidth="1"/>
-    <col min="16137" max="16138" width="11.42578125" style="213"/>
-    <col min="16139" max="16140" width="4.85546875" style="213" customWidth="1"/>
-    <col min="16141" max="16141" width="10.85546875" style="213" customWidth="1"/>
-    <col min="16142" max="16142" width="11.42578125" style="213"/>
+    <col min="16129" max="16129" width="4.44140625" style="213" customWidth="1"/>
+    <col min="16130" max="16130" width="20.88671875" style="213" customWidth="1"/>
+    <col min="16131" max="16132" width="11.44140625" style="213"/>
+    <col min="16133" max="16134" width="4.109375" style="213" customWidth="1"/>
+    <col min="16135" max="16135" width="11.44140625" style="213"/>
+    <col min="16136" max="16136" width="19.109375" style="213" customWidth="1"/>
+    <col min="16137" max="16138" width="11.44140625" style="213"/>
+    <col min="16139" max="16140" width="4.88671875" style="213" customWidth="1"/>
+    <col min="16141" max="16141" width="10.88671875" style="213" customWidth="1"/>
+    <col min="16142" max="16142" width="11.44140625" style="213"/>
     <col min="16143" max="16143" width="22" style="213" customWidth="1"/>
-    <col min="16144" max="16145" width="11.42578125" style="213"/>
+    <col min="16144" max="16145" width="11.44140625" style="213"/>
     <col min="16146" max="16147" width="6" style="213" customWidth="1"/>
-    <col min="16148" max="16384" width="11.42578125" style="213"/>
+    <col min="16148" max="16384" width="11.44140625" style="213"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="214"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="215" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="213" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B5" s="230">
         <v>46161</v>
@@ -14641,30 +14647,30 @@
       <c r="B6" s="216"/>
     </row>
     <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="461" t="s">
+      <c r="A7" s="463" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="463"/>
+      <c r="C7" s="463"/>
+      <c r="D7" s="463"/>
+      <c r="F7" s="463" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="461"/>
-      <c r="C7" s="461"/>
-      <c r="D7" s="461"/>
-      <c r="F7" s="461" t="s">
+      <c r="G7" s="463"/>
+      <c r="H7" s="463"/>
+      <c r="I7" s="463"/>
+      <c r="K7" s="463" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="461"/>
-      <c r="H7" s="461"/>
-      <c r="I7" s="461"/>
-      <c r="K7" s="461" t="s">
+      <c r="L7" s="463"/>
+      <c r="M7" s="463"/>
+      <c r="N7" s="463"/>
+      <c r="P7" s="463" t="s">
         <v>122</v>
       </c>
-      <c r="L7" s="461"/>
-      <c r="M7" s="461"/>
-      <c r="N7" s="461"/>
-      <c r="P7" s="461" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q7" s="461"/>
-      <c r="R7" s="461"/>
-      <c r="S7" s="461"/>
+      <c r="Q7" s="463"/>
+      <c r="R7" s="463"/>
+      <c r="S7" s="463"/>
     </row>
     <row r="8" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="218"/>
@@ -14686,575 +14692,575 @@
     </row>
     <row r="9" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="B9" s="460" t="e">
+        <v>123</v>
+      </c>
+      <c r="B9" s="462" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="C9" s="460"/>
-      <c r="D9" s="460"/>
+      <c r="C9" s="462"/>
+      <c r="D9" s="462"/>
       <c r="F9" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="G9" s="460" t="e">
+        <v>123</v>
+      </c>
+      <c r="G9" s="462" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H9" s="460"/>
-      <c r="I9" s="460"/>
+      <c r="H9" s="462"/>
+      <c r="I9" s="462"/>
       <c r="K9" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="L9" s="460" t="e">
+        <v>123</v>
+      </c>
+      <c r="L9" s="462" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M9" s="460"/>
-      <c r="N9" s="460"/>
+      <c r="M9" s="462"/>
+      <c r="N9" s="462"/>
       <c r="P9" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q9" s="462" t="e">
+        <v>123</v>
+      </c>
+      <c r="Q9" s="464" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="R9" s="463"/>
-      <c r="S9" s="464"/>
+      <c r="R9" s="465"/>
+      <c r="S9" s="466"/>
     </row>
     <row r="10" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="219" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="460" t="e">
+        <v>124</v>
+      </c>
+      <c r="B10" s="462" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="460"/>
-      <c r="D10" s="460"/>
+      <c r="C10" s="462"/>
+      <c r="D10" s="462"/>
       <c r="F10" s="219" t="s">
-        <v>125</v>
-      </c>
-      <c r="G10" s="460" t="e">
+        <v>124</v>
+      </c>
+      <c r="G10" s="462" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="H10" s="460"/>
-      <c r="I10" s="460"/>
+      <c r="H10" s="462"/>
+      <c r="I10" s="462"/>
       <c r="K10" s="219" t="s">
-        <v>125</v>
-      </c>
-      <c r="L10" s="460" t="e">
+        <v>124</v>
+      </c>
+      <c r="L10" s="462" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="M10" s="460"/>
-      <c r="N10" s="460"/>
+      <c r="M10" s="462"/>
+      <c r="N10" s="462"/>
       <c r="P10" s="219" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q10" s="462" t="e">
+        <v>124</v>
+      </c>
+      <c r="Q10" s="464" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="R10" s="463"/>
-      <c r="S10" s="464"/>
+      <c r="R10" s="465"/>
+      <c r="S10" s="466"/>
     </row>
     <row r="11" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="219" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="460" t="e">
+        <v>125</v>
+      </c>
+      <c r="B11" s="462" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="460"/>
-      <c r="D11" s="460"/>
+      <c r="C11" s="462"/>
+      <c r="D11" s="462"/>
       <c r="F11" s="219" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" s="460" t="e">
+        <v>125</v>
+      </c>
+      <c r="G11" s="462" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H11" s="460"/>
-      <c r="I11" s="460"/>
+      <c r="H11" s="462"/>
+      <c r="I11" s="462"/>
       <c r="K11" s="219" t="s">
-        <v>126</v>
-      </c>
-      <c r="L11" s="460" t="e">
+        <v>125</v>
+      </c>
+      <c r="L11" s="462" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="M11" s="460"/>
-      <c r="N11" s="460"/>
+      <c r="M11" s="462"/>
+      <c r="N11" s="462"/>
       <c r="P11" s="219" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q11" s="462" t="e">
+        <v>125</v>
+      </c>
+      <c r="Q11" s="464" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R11" s="463"/>
-      <c r="S11" s="464"/>
+      <c r="R11" s="465"/>
+      <c r="S11" s="466"/>
     </row>
     <row r="12" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="219" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="460" t="e">
+        <v>126</v>
+      </c>
+      <c r="B12" s="462" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
       <c r="F12" s="219" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="460" t="e">
+        <v>126</v>
+      </c>
+      <c r="G12" s="462" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="H12" s="460"/>
-      <c r="I12" s="460"/>
+      <c r="H12" s="462"/>
+      <c r="I12" s="462"/>
       <c r="K12" s="219" t="s">
-        <v>127</v>
-      </c>
-      <c r="L12" s="460" t="e">
+        <v>126</v>
+      </c>
+      <c r="L12" s="462" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="M12" s="460"/>
-      <c r="N12" s="460"/>
+      <c r="M12" s="462"/>
+      <c r="N12" s="462"/>
       <c r="P12" s="219" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q12" s="462" t="e">
+        <v>126</v>
+      </c>
+      <c r="Q12" s="464" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="R12" s="463"/>
-      <c r="S12" s="464"/>
+      <c r="R12" s="465"/>
+      <c r="S12" s="466"/>
     </row>
     <row r="13" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="219" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="454" t="e">
+        <v>127</v>
+      </c>
+      <c r="B13" s="456" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="454"/>
-      <c r="D13" s="454"/>
+      <c r="C13" s="456"/>
+      <c r="D13" s="456"/>
       <c r="F13" s="219" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="454" t="e">
+        <v>127</v>
+      </c>
+      <c r="G13" s="456" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H13" s="454"/>
-      <c r="I13" s="454"/>
+      <c r="H13" s="456"/>
+      <c r="I13" s="456"/>
       <c r="K13" s="219" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="454" t="e">
+        <v>127</v>
+      </c>
+      <c r="L13" s="456" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="M13" s="454"/>
-      <c r="N13" s="454"/>
+      <c r="M13" s="456"/>
+      <c r="N13" s="456"/>
       <c r="P13" s="219" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q13" s="456" t="e">
+        <v>127</v>
+      </c>
+      <c r="Q13" s="458" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R13" s="457"/>
-      <c r="S13" s="458"/>
+      <c r="R13" s="459"/>
+      <c r="S13" s="460"/>
     </row>
     <row r="14" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="217" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="454" t="e">
+        <v>128</v>
+      </c>
+      <c r="B14" s="456" t="e">
         <f>ABS((B13/(B11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="C14" s="454"/>
-      <c r="D14" s="454"/>
+      <c r="C14" s="456"/>
+      <c r="D14" s="456"/>
       <c r="F14" s="217" t="s">
-        <v>129</v>
-      </c>
-      <c r="G14" s="454" t="e">
+        <v>128</v>
+      </c>
+      <c r="G14" s="456" t="e">
         <f>ABS((G13/(G11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="H14" s="454"/>
-      <c r="I14" s="454"/>
+      <c r="H14" s="456"/>
+      <c r="I14" s="456"/>
       <c r="K14" s="217" t="s">
-        <v>129</v>
-      </c>
-      <c r="L14" s="454" t="e">
+        <v>128</v>
+      </c>
+      <c r="L14" s="456" t="e">
         <f>ABS((L13/(L11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="M14" s="454"/>
-      <c r="N14" s="454"/>
+      <c r="M14" s="456"/>
+      <c r="N14" s="456"/>
       <c r="P14" s="217" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q14" s="456" t="e">
+        <v>128</v>
+      </c>
+      <c r="Q14" s="458" t="e">
         <f>ABS((Q13/(Q11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="R14" s="457"/>
-      <c r="S14" s="458"/>
+      <c r="R14" s="459"/>
+      <c r="S14" s="460"/>
     </row>
     <row r="15" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="217" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="454" t="e">
+        <v>129</v>
+      </c>
+      <c r="B15" s="456" t="e">
         <f>ABS((((B10*B11-(B9^2))/(B11*(#REF!-1)))-(B14))*((B11*(#REF!-1))/((B11^2)-B12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="C15" s="454"/>
-      <c r="D15" s="454"/>
+      <c r="C15" s="456"/>
+      <c r="D15" s="456"/>
       <c r="F15" s="217" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="454" t="e">
+        <v>129</v>
+      </c>
+      <c r="G15" s="456" t="e">
         <f>ABS((((G10*G11-(G9^2))/(G11*(#REF!-1)))-(G14))*((G11*(#REF!-1))/((G11^2)-G12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="454"/>
-      <c r="I15" s="454"/>
+      <c r="H15" s="456"/>
+      <c r="I15" s="456"/>
       <c r="K15" s="217" t="s">
-        <v>130</v>
-      </c>
-      <c r="L15" s="454" t="e">
+        <v>129</v>
+      </c>
+      <c r="L15" s="456" t="e">
         <f>ABS((((L10*L11-(L9^2))/(L11*(#REF!-1)))-(L14))*((L11*(#REF!-1))/((L11^2)-L12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="M15" s="454"/>
-      <c r="N15" s="454"/>
+      <c r="M15" s="456"/>
+      <c r="N15" s="456"/>
       <c r="P15" s="217" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q15" s="454" t="e">
+        <v>129</v>
+      </c>
+      <c r="Q15" s="456" t="e">
         <f>ABS((((Q10*Q11-(Q9^2))/(Q11*(#REF!-1)))-(Q14))*((Q11*(#REF!-1))/((Q11^2)-Q12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="R15" s="454"/>
-      <c r="S15" s="454"/>
+      <c r="R15" s="456"/>
+      <c r="S15" s="456"/>
     </row>
     <row r="16" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="217" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="454" t="e">
+        <v>130</v>
+      </c>
+      <c r="B16" s="456" t="e">
         <f>(B14+B15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="C16" s="454"/>
-      <c r="D16" s="454"/>
+      <c r="C16" s="456"/>
+      <c r="D16" s="456"/>
       <c r="F16" s="217" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="454" t="e">
+        <v>130</v>
+      </c>
+      <c r="G16" s="456" t="e">
         <f>(G14+G15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="H16" s="454"/>
-      <c r="I16" s="454"/>
+      <c r="H16" s="456"/>
+      <c r="I16" s="456"/>
       <c r="K16" s="217" t="s">
-        <v>131</v>
-      </c>
-      <c r="L16" s="454" t="e">
+        <v>130</v>
+      </c>
+      <c r="L16" s="456" t="e">
         <f>(L14+L15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="M16" s="454"/>
-      <c r="N16" s="454"/>
+      <c r="M16" s="456"/>
+      <c r="N16" s="456"/>
       <c r="P16" s="217" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q16" s="456" t="e">
+        <v>130</v>
+      </c>
+      <c r="Q16" s="458" t="e">
         <f>(Q14+Q15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="R16" s="457"/>
-      <c r="S16" s="458"/>
+      <c r="R16" s="459"/>
+      <c r="S16" s="460"/>
     </row>
     <row r="17" spans="1:25" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="217" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="454" t="e">
+        <v>131</v>
+      </c>
+      <c r="B17" s="456" t="e">
         <f>SQRT(B14)</f>
         <v>#REF!</v>
       </c>
-      <c r="C17" s="454"/>
-      <c r="D17" s="454"/>
+      <c r="C17" s="456"/>
+      <c r="D17" s="456"/>
       <c r="F17" s="217" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="454" t="e">
+        <v>131</v>
+      </c>
+      <c r="G17" s="456" t="e">
         <f>SQRT(G14)</f>
         <v>#REF!</v>
       </c>
-      <c r="H17" s="454"/>
-      <c r="I17" s="454"/>
+      <c r="H17" s="456"/>
+      <c r="I17" s="456"/>
       <c r="K17" s="217" t="s">
-        <v>132</v>
-      </c>
-      <c r="L17" s="454" t="e">
+        <v>131</v>
+      </c>
+      <c r="L17" s="456" t="e">
         <f>SQRT(L14)</f>
         <v>#REF!</v>
       </c>
-      <c r="M17" s="454"/>
-      <c r="N17" s="454"/>
+      <c r="M17" s="456"/>
+      <c r="N17" s="456"/>
       <c r="P17" s="217" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q17" s="456" t="e">
+        <v>131</v>
+      </c>
+      <c r="Q17" s="458" t="e">
         <f>SQRT(Q14)</f>
         <v>#REF!</v>
       </c>
-      <c r="R17" s="457"/>
-      <c r="S17" s="458"/>
-      <c r="V17" s="455"/>
-      <c r="W17" s="455"/>
-      <c r="X17" s="455"/>
-      <c r="Y17" s="455"/>
+      <c r="R17" s="459"/>
+      <c r="S17" s="460"/>
+      <c r="V17" s="457"/>
+      <c r="W17" s="457"/>
+      <c r="X17" s="457"/>
+      <c r="Y17" s="457"/>
     </row>
     <row r="18" spans="1:25" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="217" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="454" t="e">
+        <v>132</v>
+      </c>
+      <c r="B18" s="456" t="e">
         <f>+SQRT(B14+B15)</f>
         <v>#REF!</v>
       </c>
-      <c r="C18" s="454"/>
-      <c r="D18" s="454"/>
+      <c r="C18" s="456"/>
+      <c r="D18" s="456"/>
       <c r="F18" s="217" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="454" t="e">
+        <v>132</v>
+      </c>
+      <c r="G18" s="456" t="e">
         <f>+SQRT(G14+G15)</f>
         <v>#REF!</v>
       </c>
-      <c r="H18" s="454"/>
-      <c r="I18" s="454"/>
+      <c r="H18" s="456"/>
+      <c r="I18" s="456"/>
       <c r="K18" s="217" t="s">
-        <v>133</v>
-      </c>
-      <c r="L18" s="454" t="e">
+        <v>132</v>
+      </c>
+      <c r="L18" s="456" t="e">
         <f>+SQRT(L14+L15)</f>
         <v>#REF!</v>
       </c>
-      <c r="M18" s="454"/>
-      <c r="N18" s="454"/>
+      <c r="M18" s="456"/>
+      <c r="N18" s="456"/>
       <c r="P18" s="217" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q18" s="456" t="e">
+        <v>132</v>
+      </c>
+      <c r="Q18" s="458" t="e">
         <f>+SQRT(Q14+Q15)</f>
         <v>#REF!</v>
       </c>
-      <c r="R18" s="457"/>
-      <c r="S18" s="458"/>
-      <c r="V18" s="455"/>
-      <c r="W18" s="455"/>
-      <c r="X18" s="455"/>
-      <c r="Y18" s="455"/>
-    </row>
-    <row r="19" spans="1:25" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="R18" s="459"/>
+      <c r="S18" s="460"/>
+      <c r="V18" s="457"/>
+      <c r="W18" s="457"/>
+      <c r="X18" s="457"/>
+      <c r="Y18" s="457"/>
+    </row>
+    <row r="19" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="379" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="459">
+        <v>213</v>
+      </c>
+      <c r="B19" s="461">
         <v>7.6899555698759737E-3</v>
       </c>
-      <c r="C19" s="459"/>
-      <c r="D19" s="459"/>
+      <c r="C19" s="461"/>
+      <c r="D19" s="461"/>
       <c r="E19" s="380"/>
       <c r="F19" s="379" t="s">
-        <v>214</v>
-      </c>
-      <c r="G19" s="459">
+        <v>213</v>
+      </c>
+      <c r="G19" s="461">
         <v>6.454972243679062E-3</v>
       </c>
-      <c r="H19" s="459"/>
-      <c r="I19" s="459"/>
+      <c r="H19" s="461"/>
+      <c r="I19" s="461"/>
       <c r="J19" s="380"/>
       <c r="K19" s="379" t="s">
-        <v>214</v>
-      </c>
-      <c r="L19" s="459">
+        <v>213</v>
+      </c>
+      <c r="L19" s="461">
         <v>6.4718943646096755E-3</v>
       </c>
-      <c r="M19" s="459"/>
-      <c r="N19" s="459"/>
+      <c r="M19" s="461"/>
+      <c r="N19" s="461"/>
       <c r="O19" s="380"/>
       <c r="P19" s="379" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q19" s="461">
+        <v>9.1503642914731384E-2</v>
+      </c>
+      <c r="R19" s="461"/>
+      <c r="S19" s="461"/>
+      <c r="V19" s="457"/>
+      <c r="W19" s="457"/>
+      <c r="X19" s="457"/>
+      <c r="Y19" s="457"/>
+    </row>
+    <row r="20" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="379" t="s">
         <v>214</v>
       </c>
-      <c r="Q19" s="459">
-        <v>9.1503642914731384E-2</v>
-      </c>
-      <c r="R19" s="459"/>
-      <c r="S19" s="459"/>
-      <c r="V19" s="455"/>
-      <c r="W19" s="455"/>
-      <c r="X19" s="455"/>
-      <c r="Y19" s="455"/>
-    </row>
-    <row r="20" spans="1:25" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="379" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="459">
+      <c r="B20" s="461">
         <v>7.734845547824153E-3</v>
       </c>
-      <c r="C20" s="459"/>
-      <c r="D20" s="459"/>
+      <c r="C20" s="461"/>
+      <c r="D20" s="461"/>
       <c r="E20" s="380"/>
       <c r="F20" s="379" t="s">
-        <v>215</v>
-      </c>
-      <c r="G20" s="459">
+        <v>214</v>
+      </c>
+      <c r="G20" s="461">
         <v>6.6157779978408861E-3</v>
       </c>
-      <c r="H20" s="459"/>
-      <c r="I20" s="459"/>
+      <c r="H20" s="461"/>
+      <c r="I20" s="461"/>
       <c r="J20" s="380"/>
       <c r="K20" s="379" t="s">
-        <v>215</v>
-      </c>
-      <c r="L20" s="459">
+        <v>214</v>
+      </c>
+      <c r="L20" s="461">
         <v>6.5331464330420554E-3</v>
       </c>
-      <c r="M20" s="459"/>
-      <c r="N20" s="459"/>
+      <c r="M20" s="461"/>
+      <c r="N20" s="461"/>
       <c r="O20" s="380"/>
       <c r="P20" s="379" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q20" s="459">
+        <v>214</v>
+      </c>
+      <c r="Q20" s="461">
         <v>0.1067108740857599</v>
       </c>
-      <c r="R20" s="459"/>
-      <c r="S20" s="459"/>
-      <c r="V20" s="455"/>
-      <c r="W20" s="455"/>
-      <c r="X20" s="455"/>
-      <c r="Y20" s="455"/>
+      <c r="R20" s="461"/>
+      <c r="S20" s="461"/>
+      <c r="V20" s="457"/>
+      <c r="W20" s="457"/>
+      <c r="X20" s="457"/>
+      <c r="Y20" s="457"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V21" s="455"/>
-      <c r="W21" s="455"/>
-      <c r="X21" s="455"/>
-      <c r="Y21" s="455"/>
+      <c r="V21" s="457"/>
+      <c r="W21" s="457"/>
+      <c r="X21" s="457"/>
+      <c r="Y21" s="457"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V22" s="455"/>
-      <c r="W22" s="455"/>
-      <c r="X22" s="455"/>
-      <c r="Y22" s="455"/>
+      <c r="V22" s="457"/>
+      <c r="W22" s="457"/>
+      <c r="X22" s="457"/>
+      <c r="Y22" s="457"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V23" s="455"/>
-      <c r="W23" s="455"/>
-      <c r="X23" s="455"/>
-      <c r="Y23" s="455"/>
+      <c r="V23" s="457"/>
+      <c r="W23" s="457"/>
+      <c r="X23" s="457"/>
+      <c r="Y23" s="457"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V24" s="455"/>
-      <c r="W24" s="455"/>
-      <c r="X24" s="455"/>
-      <c r="Y24" s="455"/>
+      <c r="V24" s="457"/>
+      <c r="W24" s="457"/>
+      <c r="X24" s="457"/>
+      <c r="Y24" s="457"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V25" s="455"/>
-      <c r="W25" s="455"/>
-      <c r="X25" s="455"/>
-      <c r="Y25" s="455"/>
+      <c r="V25" s="457"/>
+      <c r="W25" s="457"/>
+      <c r="X25" s="457"/>
+      <c r="Y25" s="457"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V26" s="455"/>
-      <c r="W26" s="455"/>
-      <c r="X26" s="455"/>
-      <c r="Y26" s="455"/>
+      <c r="V26" s="457"/>
+      <c r="W26" s="457"/>
+      <c r="X26" s="457"/>
+      <c r="Y26" s="457"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V27" s="455"/>
-      <c r="W27" s="455"/>
-      <c r="X27" s="455"/>
-      <c r="Y27" s="455"/>
+      <c r="V27" s="457"/>
+      <c r="W27" s="457"/>
+      <c r="X27" s="457"/>
+      <c r="Y27" s="457"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V28" s="455"/>
-      <c r="W28" s="455"/>
-      <c r="X28" s="455"/>
-      <c r="Y28" s="455"/>
+      <c r="V28" s="457"/>
+      <c r="W28" s="457"/>
+      <c r="X28" s="457"/>
+      <c r="Y28" s="457"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V29" s="455"/>
-      <c r="W29" s="455"/>
-      <c r="X29" s="455"/>
-      <c r="Y29" s="455"/>
+      <c r="V29" s="457"/>
+      <c r="W29" s="457"/>
+      <c r="X29" s="457"/>
+      <c r="Y29" s="457"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V30" s="455"/>
-      <c r="W30" s="455"/>
-      <c r="X30" s="455"/>
-      <c r="Y30" s="455"/>
+      <c r="V30" s="457"/>
+      <c r="W30" s="457"/>
+      <c r="X30" s="457"/>
+      <c r="Y30" s="457"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V31" s="455"/>
-      <c r="W31" s="455"/>
-      <c r="X31" s="455"/>
-      <c r="Y31" s="455"/>
+      <c r="V31" s="457"/>
+      <c r="W31" s="457"/>
+      <c r="X31" s="457"/>
+      <c r="Y31" s="457"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V32" s="455"/>
-      <c r="W32" s="455"/>
-      <c r="X32" s="455"/>
-      <c r="Y32" s="455"/>
+      <c r="V32" s="457"/>
+      <c r="W32" s="457"/>
+      <c r="X32" s="457"/>
+      <c r="Y32" s="457"/>
     </row>
     <row r="33" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V33" s="455"/>
-      <c r="W33" s="455"/>
-      <c r="X33" s="455"/>
-      <c r="Y33" s="455"/>
+      <c r="V33" s="457"/>
+      <c r="W33" s="457"/>
+      <c r="X33" s="457"/>
+      <c r="Y33" s="457"/>
     </row>
     <row r="34" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V34" s="455"/>
-      <c r="W34" s="455"/>
-      <c r="X34" s="455"/>
-      <c r="Y34" s="455"/>
+      <c r="V34" s="457"/>
+      <c r="W34" s="457"/>
+      <c r="X34" s="457"/>
+      <c r="Y34" s="457"/>
     </row>
     <row r="35" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V35" s="455"/>
-      <c r="W35" s="455"/>
-      <c r="X35" s="455"/>
-      <c r="Y35" s="455"/>
+      <c r="V35" s="457"/>
+      <c r="W35" s="457"/>
+      <c r="X35" s="457"/>
+      <c r="Y35" s="457"/>
     </row>
     <row r="36" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V36" s="455"/>
-      <c r="W36" s="455"/>
-      <c r="X36" s="455"/>
-      <c r="Y36" s="455"/>
+      <c r="V36" s="457"/>
+      <c r="W36" s="457"/>
+      <c r="X36" s="457"/>
+      <c r="Y36" s="457"/>
     </row>
     <row r="37" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V37" s="455"/>
-      <c r="W37" s="455"/>
-      <c r="X37" s="455"/>
-      <c r="Y37" s="455"/>
+      <c r="V37" s="457"/>
+      <c r="W37" s="457"/>
+      <c r="X37" s="457"/>
+      <c r="Y37" s="457"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F7BNTbSy/WaNWXDdT6W94NKCeKyHLn/2tkk/4quJIvd3p+J7bDJlNkQREHsu55RDSjMZ5YiRTRqr/fG8D9Qggw==" saltValue="uAZ5OYTao9E+LNIA/ZL2vQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -15322,57 +15328,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A2:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="1" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="465" t="s">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="467" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="467"/>
+      <c r="C2" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="465"/>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>4400</v>
       </c>
@@ -15385,7 +15391,7 @@
         <v>4400-4401</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E3" s="7">
         <v>350</v>
@@ -15418,7 +15424,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="str">
@@ -15455,7 +15461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f>+B3+1</f>
         <v>4402</v>
@@ -15498,7 +15504,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="str">
@@ -15535,7 +15541,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f>+B5+1</f>
         <v>4404</v>
@@ -15578,7 +15584,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="str">
@@ -15615,7 +15621,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>

--- a/app/templates/informes/Informes agregado/P.fino/1-INF.-N-000-26-AG18-P.E.-FINO-V10.xlsx
+++ b/app/templates/informes/Informes agregado/P.fino/1-INF.-N-000-26-AG18-P.E.-FINO-V10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\Informes agregado\P.fino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B5AAA4-C81B-4A94-BEFD-405087880263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ED8A36-22C7-4203-8D34-21C17F039DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="96" r:id="rId1"/>
@@ -3543,24 +3543,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -3625,6 +3607,53 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3649,40 +3678,11 @@
     <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3699,30 +3699,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="37" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3785,38 +3761,62 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="171" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8022,34 +8022,34 @@
       <c r="M6" s="371"/>
     </row>
     <row r="7" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="389" t="s">
+      <c r="A7" s="384" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="389"/>
-      <c r="C7" s="389"/>
-      <c r="D7" s="389"/>
-      <c r="E7" s="389"/>
-      <c r="F7" s="389"/>
-      <c r="G7" s="389"/>
-      <c r="H7" s="389"/>
-      <c r="I7" s="389"/>
+      <c r="B7" s="384"/>
+      <c r="C7" s="384"/>
+      <c r="D7" s="384"/>
+      <c r="E7" s="384"/>
+      <c r="F7" s="384"/>
+      <c r="G7" s="384"/>
+      <c r="H7" s="384"/>
+      <c r="I7" s="384"/>
       <c r="L7" s="42" t="s">
         <v>153</v>
       </c>
       <c r="M7" s="371"/>
     </row>
     <row r="8" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="390" t="s">
+      <c r="A8" s="385" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="390"/>
-      <c r="C8" s="390"/>
-      <c r="D8" s="390"/>
-      <c r="E8" s="390"/>
-      <c r="F8" s="390"/>
-      <c r="G8" s="390"/>
-      <c r="H8" s="390"/>
-      <c r="I8" s="390"/>
+      <c r="B8" s="385"/>
+      <c r="C8" s="385"/>
+      <c r="D8" s="385"/>
+      <c r="E8" s="385"/>
+      <c r="F8" s="385"/>
+      <c r="G8" s="385"/>
+      <c r="H8" s="385"/>
+      <c r="I8" s="385"/>
       <c r="L8" s="42" t="s">
         <v>202</v>
       </c>
@@ -8080,10 +8080,10 @@
       <c r="E10" s="320" t="s">
         <v>177</v>
       </c>
-      <c r="F10" s="391" t="s">
+      <c r="F10" s="386" t="s">
         <v>178</v>
       </c>
-      <c r="G10" s="391"/>
+      <c r="G10" s="386"/>
       <c r="H10" s="321"/>
       <c r="I10" s="321"/>
       <c r="J10" s="322"/>
@@ -8122,17 +8122,17 @@
       <c r="M12" s="372"/>
     </row>
     <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="392" t="s">
+      <c r="A13" s="387" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="393"/>
-      <c r="C13" s="393"/>
-      <c r="D13" s="393"/>
-      <c r="E13" s="393"/>
-      <c r="F13" s="393"/>
-      <c r="G13" s="393"/>
-      <c r="H13" s="393"/>
-      <c r="I13" s="394"/>
+      <c r="B13" s="388"/>
+      <c r="C13" s="388"/>
+      <c r="D13" s="388"/>
+      <c r="E13" s="388"/>
+      <c r="F13" s="388"/>
+      <c r="G13" s="388"/>
+      <c r="H13" s="388"/>
+      <c r="I13" s="389"/>
       <c r="J13" s="322"/>
       <c r="L13" s="42" t="s">
         <v>17</v>
@@ -8140,17 +8140,17 @@
       <c r="M13" s="372"/>
     </row>
     <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="395" t="s">
+      <c r="A14" s="390" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="396"/>
-      <c r="C14" s="396"/>
-      <c r="D14" s="396"/>
-      <c r="E14" s="396"/>
-      <c r="F14" s="396"/>
-      <c r="G14" s="396"/>
-      <c r="H14" s="396"/>
-      <c r="I14" s="397"/>
+      <c r="B14" s="391"/>
+      <c r="C14" s="391"/>
+      <c r="D14" s="391"/>
+      <c r="E14" s="391"/>
+      <c r="F14" s="391"/>
+      <c r="G14" s="391"/>
+      <c r="H14" s="391"/>
+      <c r="I14" s="392"/>
       <c r="J14" s="322"/>
       <c r="L14" s="370"/>
       <c r="M14" s="371"/>
@@ -8184,8 +8184,8 @@
         <v>181</v>
       </c>
       <c r="F16" s="330"/>
-      <c r="G16" s="398"/>
-      <c r="H16" s="399"/>
+      <c r="G16" s="393"/>
+      <c r="H16" s="394"/>
       <c r="I16" s="332"/>
       <c r="J16" s="322"/>
       <c r="L16" s="42" t="s">
@@ -8203,8 +8203,8 @@
       <c r="E17" s="329" t="s">
         <v>183</v>
       </c>
-      <c r="G17" s="398"/>
-      <c r="H17" s="399"/>
+      <c r="G17" s="393"/>
+      <c r="H17" s="394"/>
       <c r="I17" s="332"/>
       <c r="J17" s="322"/>
       <c r="L17" s="42" t="s">
@@ -8223,8 +8223,8 @@
         <v>185</v>
       </c>
       <c r="F18" s="330"/>
-      <c r="G18" s="398"/>
-      <c r="H18" s="399"/>
+      <c r="G18" s="393"/>
+      <c r="H18" s="394"/>
       <c r="I18" s="334"/>
       <c r="J18" s="322"/>
     </row>
@@ -8237,8 +8237,8 @@
         <v>186</v>
       </c>
       <c r="F19" s="329"/>
-      <c r="G19" s="398"/>
-      <c r="H19" s="399"/>
+      <c r="G19" s="393"/>
+      <c r="H19" s="394"/>
       <c r="I19" s="334"/>
       <c r="J19" s="322"/>
     </row>
@@ -8272,19 +8272,19 @@
     </row>
     <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="333"/>
-      <c r="B22" s="400" t="s">
+      <c r="B22" s="395" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="400"/>
-      <c r="D22" s="400"/>
-      <c r="E22" s="401"/>
+      <c r="C22" s="395"/>
+      <c r="D22" s="395"/>
+      <c r="E22" s="396"/>
       <c r="F22" s="336" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="400" t="s">
+      <c r="G22" s="395" t="s">
         <v>189</v>
       </c>
-      <c r="H22" s="400"/>
+      <c r="H22" s="395"/>
       <c r="I22" s="334"/>
       <c r="J22" s="322"/>
     </row>
@@ -8355,8 +8355,8 @@
       <c r="F26" s="287" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="402"/>
-      <c r="H26" s="403"/>
+      <c r="G26" s="397"/>
+      <c r="H26" s="398"/>
       <c r="I26" s="339"/>
       <c r="J26" s="322"/>
     </row>
@@ -8553,58 +8553,58 @@
       <c r="D40" s="356" t="s">
         <v>191</v>
       </c>
-      <c r="E40" s="387" t="s">
+      <c r="E40" s="382" t="s">
         <v>192</v>
       </c>
-      <c r="F40" s="388"/>
+      <c r="F40" s="383"/>
       <c r="J40" s="322"/>
     </row>
     <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="357" t="s">
         <v>193</v>
       </c>
-      <c r="E41" s="384"/>
-      <c r="F41" s="385"/>
+      <c r="E41" s="401"/>
+      <c r="F41" s="402"/>
       <c r="J41" s="322"/>
     </row>
     <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="357" t="s">
         <v>194</v>
       </c>
-      <c r="E42" s="384"/>
-      <c r="F42" s="385"/>
+      <c r="E42" s="401"/>
+      <c r="F42" s="402"/>
       <c r="J42" s="322"/>
     </row>
     <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="357" t="s">
         <v>195</v>
       </c>
-      <c r="E43" s="384"/>
-      <c r="F43" s="385"/>
+      <c r="E43" s="401"/>
+      <c r="F43" s="402"/>
       <c r="J43" s="322"/>
     </row>
     <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="357" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="384"/>
-      <c r="F44" s="385"/>
+      <c r="E44" s="401"/>
+      <c r="F44" s="402"/>
       <c r="J44" s="322"/>
     </row>
     <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="357" t="s">
         <v>196</v>
       </c>
-      <c r="E45" s="384"/>
-      <c r="F45" s="385"/>
+      <c r="E45" s="401"/>
+      <c r="F45" s="402"/>
       <c r="J45" s="322"/>
     </row>
     <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="357" t="s">
         <v>197</v>
       </c>
-      <c r="E46" s="384"/>
-      <c r="F46" s="385"/>
+      <c r="E46" s="401"/>
+      <c r="F46" s="402"/>
       <c r="J46" s="322"/>
     </row>
     <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8665,11 +8665,11 @@
       <c r="J52" s="322"/>
     </row>
     <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="386"/>
-      <c r="D53" s="386"/>
-      <c r="E53" s="386"/>
-      <c r="F53" s="386"/>
-      <c r="G53" s="386"/>
+      <c r="C53" s="403"/>
+      <c r="D53" s="403"/>
+      <c r="E53" s="403"/>
+      <c r="F53" s="403"/>
+      <c r="G53" s="403"/>
       <c r="H53" s="361"/>
       <c r="I53" s="361"/>
       <c r="J53" s="322"/>
@@ -8694,39 +8694,49 @@
       </c>
       <c r="B55" s="362"/>
       <c r="C55" s="352"/>
-      <c r="D55" s="382" t="s">
+      <c r="D55" s="399" t="s">
         <v>200</v>
       </c>
-      <c r="E55" s="382"/>
-      <c r="F55" s="382"/>
-      <c r="G55" s="382"/>
-      <c r="H55" s="382"/>
-      <c r="I55" s="382"/>
+      <c r="E55" s="399"/>
+      <c r="F55" s="399"/>
+      <c r="G55" s="399"/>
+      <c r="H55" s="399"/>
+      <c r="I55" s="399"/>
       <c r="J55" s="322"/>
     </row>
     <row r="56" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="383" t="s">
+      <c r="A57" s="400" t="s">
         <v>201</v>
       </c>
-      <c r="B57" s="383"/>
-      <c r="C57" s="383"/>
-      <c r="D57" s="383"/>
-      <c r="E57" s="383"/>
-      <c r="F57" s="383"/>
-      <c r="G57" s="383"/>
-      <c r="H57" s="383"/>
-      <c r="I57" s="383"/>
+      <c r="B57" s="400"/>
+      <c r="C57" s="400"/>
+      <c r="D57" s="400"/>
+      <c r="E57" s="400"/>
+      <c r="F57" s="400"/>
+      <c r="G57" s="400"/>
+      <c r="H57" s="400"/>
+      <c r="I57" s="400"/>
     </row>
     <row r="58" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:10" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="k0t1kVffZgNYMVxA0ywRe7TqZPd2p4MZI3FSA+92LP6kJR5oXI7CFm7m2vxq5O9PVMfV7Ar2tJhLAraSe6djrw==" saltValue="udAdfuHeRp6eIwE20i9ocA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <protectedRanges>
     <protectedRange sqref="C12" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E11 C53 C10" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="23">
+    <mergeCell ref="D55:I55"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="E43:F43"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A8:I8"/>
@@ -8740,16 +8750,6 @@
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="D55:I55"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="E43:F43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0.78740157480314965" bottom="0" header="0" footer="0"/>
@@ -8820,36 +8820,36 @@
       <c r="L3" s="39"/>
     </row>
     <row r="4" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="404" t="s">
+      <c r="A4" s="413" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="404"/>
-      <c r="C4" s="404"/>
-      <c r="D4" s="404"/>
-      <c r="E4" s="404"/>
-      <c r="F4" s="404"/>
-      <c r="G4" s="404"/>
-      <c r="H4" s="404"/>
-      <c r="I4" s="404"/>
-      <c r="J4" s="404"/>
-      <c r="K4" s="404"/>
-      <c r="L4" s="404"/>
+      <c r="B4" s="413"/>
+      <c r="C4" s="413"/>
+      <c r="D4" s="413"/>
+      <c r="E4" s="413"/>
+      <c r="F4" s="413"/>
+      <c r="G4" s="413"/>
+      <c r="H4" s="413"/>
+      <c r="I4" s="413"/>
+      <c r="J4" s="413"/>
+      <c r="K4" s="413"/>
+      <c r="L4" s="413"/>
     </row>
     <row r="5" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="411">
+      <c r="A5" s="420">
         <v>0</v>
       </c>
-      <c r="B5" s="411"/>
-      <c r="C5" s="411"/>
-      <c r="D5" s="411"/>
-      <c r="E5" s="411"/>
-      <c r="F5" s="411"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="411"/>
-      <c r="J5" s="411"/>
-      <c r="K5" s="411"/>
-      <c r="L5" s="411"/>
+      <c r="B5" s="420"/>
+      <c r="C5" s="420"/>
+      <c r="D5" s="420"/>
+      <c r="E5" s="420"/>
+      <c r="F5" s="420"/>
+      <c r="G5" s="420"/>
+      <c r="H5" s="420"/>
+      <c r="I5" s="420"/>
+      <c r="J5" s="420"/>
+      <c r="K5" s="420"/>
+      <c r="L5" s="420"/>
     </row>
     <row r="6" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8859,16 +8859,16 @@
       <c r="B7" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="415">
+      <c r="C7" s="421">
         <f>+FORMATO!M2</f>
         <v>0</v>
       </c>
-      <c r="D7" s="415"/>
-      <c r="E7" s="415"/>
-      <c r="F7" s="415"/>
-      <c r="G7" s="415"/>
-      <c r="H7" s="415"/>
-      <c r="I7" s="415"/>
+      <c r="D7" s="421"/>
+      <c r="E7" s="421"/>
+      <c r="F7" s="421"/>
+      <c r="G7" s="421"/>
+      <c r="H7" s="421"/>
+      <c r="I7" s="421"/>
       <c r="J7" s="42" t="s">
         <v>3</v>
       </c>
@@ -8886,16 +8886,16 @@
       <c r="B8" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="415">
+      <c r="C8" s="421">
         <f>+FORMATO!M3</f>
         <v>0</v>
       </c>
-      <c r="D8" s="415"/>
-      <c r="E8" s="415"/>
-      <c r="F8" s="415"/>
-      <c r="G8" s="415"/>
-      <c r="H8" s="415"/>
-      <c r="I8" s="415"/>
+      <c r="D8" s="421"/>
+      <c r="E8" s="421"/>
+      <c r="F8" s="421"/>
+      <c r="G8" s="421"/>
+      <c r="H8" s="421"/>
+      <c r="I8" s="421"/>
       <c r="J8" s="42" t="s">
         <v>153</v>
       </c>
@@ -8915,16 +8915,16 @@
       <c r="B9" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="415">
+      <c r="C9" s="421">
         <f>+FORMATO!M4</f>
         <v>0</v>
       </c>
-      <c r="D9" s="415"/>
-      <c r="E9" s="415"/>
-      <c r="F9" s="415"/>
-      <c r="G9" s="415"/>
-      <c r="H9" s="415"/>
-      <c r="I9" s="415"/>
+      <c r="D9" s="421"/>
+      <c r="E9" s="421"/>
+      <c r="F9" s="421"/>
+      <c r="G9" s="421"/>
+      <c r="H9" s="421"/>
+      <c r="I9" s="421"/>
       <c r="J9" s="42" t="s">
         <v>203</v>
       </c>
@@ -8944,16 +8944,16 @@
       <c r="B10" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="415">
+      <c r="C10" s="421">
         <f>+FORMATO!M5</f>
         <v>0</v>
       </c>
-      <c r="D10" s="415"/>
-      <c r="E10" s="415"/>
-      <c r="F10" s="415"/>
-      <c r="G10" s="415"/>
-      <c r="H10" s="415"/>
-      <c r="I10" s="415"/>
+      <c r="D10" s="421"/>
+      <c r="E10" s="421"/>
+      <c r="F10" s="421"/>
+      <c r="G10" s="421"/>
+      <c r="H10" s="421"/>
+      <c r="I10" s="421"/>
       <c r="J10" s="381" t="s">
         <v>7</v>
       </c>
@@ -8999,37 +8999,37 @@
       <c r="M12" s="28"/>
     </row>
     <row r="13" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="405" t="s">
+      <c r="A13" s="414" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="406"/>
-      <c r="C13" s="406"/>
-      <c r="D13" s="406"/>
-      <c r="E13" s="406"/>
-      <c r="F13" s="406"/>
-      <c r="G13" s="406"/>
-      <c r="H13" s="406"/>
-      <c r="I13" s="406"/>
-      <c r="J13" s="406"/>
-      <c r="K13" s="406"/>
-      <c r="L13" s="407"/>
+      <c r="B13" s="415"/>
+      <c r="C13" s="415"/>
+      <c r="D13" s="415"/>
+      <c r="E13" s="415"/>
+      <c r="F13" s="415"/>
+      <c r="G13" s="415"/>
+      <c r="H13" s="415"/>
+      <c r="I13" s="415"/>
+      <c r="J13" s="415"/>
+      <c r="K13" s="415"/>
+      <c r="L13" s="416"/>
       <c r="M13" s="28"/>
     </row>
     <row r="14" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="408" t="s">
+      <c r="A14" s="417" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="409"/>
-      <c r="C14" s="409"/>
-      <c r="D14" s="409"/>
-      <c r="E14" s="409"/>
-      <c r="F14" s="409"/>
-      <c r="G14" s="409"/>
-      <c r="H14" s="409"/>
-      <c r="I14" s="409"/>
-      <c r="J14" s="409"/>
-      <c r="K14" s="409"/>
-      <c r="L14" s="410"/>
+      <c r="B14" s="418"/>
+      <c r="C14" s="418"/>
+      <c r="D14" s="418"/>
+      <c r="E14" s="418"/>
+      <c r="F14" s="418"/>
+      <c r="G14" s="418"/>
+      <c r="H14" s="418"/>
+      <c r="I14" s="418"/>
+      <c r="J14" s="418"/>
+      <c r="K14" s="418"/>
+      <c r="L14" s="419"/>
       <c r="M14" s="28"/>
     </row>
     <row r="15" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9146,11 +9146,11 @@
         <f>+FORMATO!M13</f>
         <v>0</v>
       </c>
-      <c r="M19" s="416">
+      <c r="M19" s="404">
         <f>+FORMATO!E11</f>
         <v>0</v>
       </c>
-      <c r="N19" s="417"/>
+      <c r="N19" s="405"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
@@ -9189,15 +9189,15 @@
     </row>
     <row r="22" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60"/>
-      <c r="B22" s="412" t="s">
+      <c r="B22" s="407" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="413"/>
-      <c r="D22" s="413"/>
-      <c r="E22" s="413"/>
-      <c r="F22" s="413"/>
-      <c r="G22" s="413"/>
-      <c r="H22" s="414"/>
+      <c r="C22" s="408"/>
+      <c r="D22" s="408"/>
+      <c r="E22" s="408"/>
+      <c r="F22" s="408"/>
+      <c r="G22" s="408"/>
+      <c r="H22" s="409"/>
       <c r="I22" s="182" t="s">
         <v>20</v>
       </c>
@@ -9300,10 +9300,10 @@
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
       <c r="D27" s="91"/>
-      <c r="E27" s="420"/>
-      <c r="F27" s="420"/>
-      <c r="G27" s="420"/>
-      <c r="H27" s="420"/>
+      <c r="E27" s="411"/>
+      <c r="F27" s="411"/>
+      <c r="G27" s="411"/>
+      <c r="H27" s="411"/>
       <c r="I27" s="38"/>
       <c r="J27" s="61"/>
       <c r="K27" s="61"/>
@@ -9312,17 +9312,17 @@
     </row>
     <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60"/>
-      <c r="B28" s="412" t="s">
+      <c r="B28" s="407" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="413"/>
-      <c r="D28" s="413"/>
-      <c r="E28" s="413"/>
-      <c r="F28" s="413"/>
-      <c r="G28" s="413"/>
-      <c r="H28" s="413"/>
-      <c r="I28" s="413"/>
-      <c r="J28" s="414"/>
+      <c r="C28" s="408"/>
+      <c r="D28" s="408"/>
+      <c r="E28" s="408"/>
+      <c r="F28" s="408"/>
+      <c r="G28" s="408"/>
+      <c r="H28" s="408"/>
+      <c r="I28" s="408"/>
+      <c r="J28" s="409"/>
       <c r="K28" s="61"/>
       <c r="L28" s="62"/>
       <c r="M28" s="32"/>
@@ -9497,88 +9497,88 @@
       <c r="M37" s="28"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="421" t="s">
+      <c r="A38" s="412" t="s">
         <v>217</v>
       </c>
-      <c r="B38" s="421"/>
-      <c r="C38" s="421"/>
-      <c r="D38" s="421"/>
-      <c r="E38" s="421"/>
-      <c r="F38" s="421"/>
-      <c r="G38" s="421"/>
-      <c r="H38" s="421"/>
-      <c r="I38" s="421"/>
-      <c r="J38" s="421"/>
-      <c r="K38" s="421"/>
-      <c r="L38" s="421"/>
+      <c r="B38" s="412"/>
+      <c r="C38" s="412"/>
+      <c r="D38" s="412"/>
+      <c r="E38" s="412"/>
+      <c r="F38" s="412"/>
+      <c r="G38" s="412"/>
+      <c r="H38" s="412"/>
+      <c r="I38" s="412"/>
+      <c r="J38" s="412"/>
+      <c r="K38" s="412"/>
+      <c r="L38" s="412"/>
       <c r="M38" s="28"/>
     </row>
     <row r="39" spans="1:15" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="419" t="s">
+      <c r="A39" s="410" t="s">
         <v>218</v>
       </c>
-      <c r="B39" s="419"/>
-      <c r="C39" s="419"/>
-      <c r="D39" s="419"/>
-      <c r="E39" s="419"/>
-      <c r="F39" s="419"/>
-      <c r="G39" s="419"/>
-      <c r="H39" s="419"/>
-      <c r="I39" s="419"/>
-      <c r="J39" s="419"/>
-      <c r="K39" s="419"/>
-      <c r="L39" s="419"/>
+      <c r="B39" s="410"/>
+      <c r="C39" s="410"/>
+      <c r="D39" s="410"/>
+      <c r="E39" s="410"/>
+      <c r="F39" s="410"/>
+      <c r="G39" s="410"/>
+      <c r="H39" s="410"/>
+      <c r="I39" s="410"/>
+      <c r="J39" s="410"/>
+      <c r="K39" s="410"/>
+      <c r="L39" s="410"/>
       <c r="M39" s="28"/>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="419" t="s">
+      <c r="A40" s="410" t="s">
         <v>219</v>
       </c>
-      <c r="B40" s="419"/>
-      <c r="C40" s="419"/>
-      <c r="D40" s="419"/>
-      <c r="E40" s="419"/>
-      <c r="F40" s="419"/>
-      <c r="G40" s="419"/>
-      <c r="H40" s="419"/>
-      <c r="I40" s="419"/>
-      <c r="J40" s="419"/>
-      <c r="K40" s="419"/>
-      <c r="L40" s="419"/>
+      <c r="B40" s="410"/>
+      <c r="C40" s="410"/>
+      <c r="D40" s="410"/>
+      <c r="E40" s="410"/>
+      <c r="F40" s="410"/>
+      <c r="G40" s="410"/>
+      <c r="H40" s="410"/>
+      <c r="I40" s="410"/>
+      <c r="J40" s="410"/>
+      <c r="K40" s="410"/>
+      <c r="L40" s="410"/>
       <c r="M40" s="28"/>
     </row>
     <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="419" t="s">
+      <c r="A41" s="410" t="s">
         <v>220</v>
       </c>
-      <c r="B41" s="419"/>
-      <c r="C41" s="419"/>
-      <c r="D41" s="419"/>
-      <c r="E41" s="419"/>
-      <c r="F41" s="419"/>
-      <c r="G41" s="419"/>
-      <c r="H41" s="419"/>
-      <c r="I41" s="419"/>
-      <c r="J41" s="419"/>
-      <c r="K41" s="419"/>
-      <c r="L41" s="419"/>
+      <c r="B41" s="410"/>
+      <c r="C41" s="410"/>
+      <c r="D41" s="410"/>
+      <c r="E41" s="410"/>
+      <c r="F41" s="410"/>
+      <c r="G41" s="410"/>
+      <c r="H41" s="410"/>
+      <c r="I41" s="410"/>
+      <c r="J41" s="410"/>
+      <c r="K41" s="410"/>
+      <c r="L41" s="410"/>
       <c r="M41" s="28"/>
     </row>
     <row r="42" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="418" t="s">
+      <c r="A42" s="406" t="s">
         <v>221</v>
       </c>
-      <c r="B42" s="418"/>
-      <c r="C42" s="418"/>
-      <c r="D42" s="418"/>
-      <c r="E42" s="418"/>
-      <c r="F42" s="418"/>
-      <c r="G42" s="418"/>
-      <c r="H42" s="418"/>
-      <c r="I42" s="418"/>
-      <c r="J42" s="418"/>
-      <c r="K42" s="418"/>
-      <c r="L42" s="418"/>
+      <c r="B42" s="406"/>
+      <c r="C42" s="406"/>
+      <c r="D42" s="406"/>
+      <c r="E42" s="406"/>
+      <c r="F42" s="406"/>
+      <c r="G42" s="406"/>
+      <c r="H42" s="406"/>
+      <c r="I42" s="406"/>
+      <c r="J42" s="406"/>
+      <c r="K42" s="406"/>
+      <c r="L42" s="406"/>
       <c r="M42" s="28"/>
     </row>
     <row r="43" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9702,14 +9702,6 @@
     <protectedRange sqref="E10:I10" name="Rango3_3_1_1_1_1_1_1_1_1_1_1_1_2_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="17">
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A38:L38"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -9719,6 +9711,14 @@
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="C10:I10"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A38:L38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.98425196850393704" bottom="0" header="0.11811023622047245" footer="0"/>
@@ -9901,15 +9901,15 @@
       <c r="O10" s="86"/>
     </row>
     <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="412" t="s">
+      <c r="B11" s="407" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="413"/>
-      <c r="D11" s="413"/>
-      <c r="E11" s="413"/>
-      <c r="F11" s="413"/>
-      <c r="G11" s="413"/>
-      <c r="H11" s="414"/>
+      <c r="C11" s="408"/>
+      <c r="D11" s="408"/>
+      <c r="E11" s="408"/>
+      <c r="F11" s="408"/>
+      <c r="G11" s="408"/>
+      <c r="H11" s="409"/>
       <c r="I11" s="169" t="s">
         <v>44</v>
       </c>
@@ -10300,16 +10300,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="436"/>
-      <c r="B1" s="439" t="s">
+      <c r="A1" s="428"/>
+      <c r="B1" s="431" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
-      <c r="E1" s="440"/>
-      <c r="F1" s="440"/>
-      <c r="G1" s="440"/>
-      <c r="H1" s="441"/>
+      <c r="C1" s="432"/>
+      <c r="D1" s="432"/>
+      <c r="E1" s="432"/>
+      <c r="F1" s="432"/>
+      <c r="G1" s="432"/>
+      <c r="H1" s="433"/>
       <c r="I1" s="103" t="s">
         <v>51</v>
       </c>
@@ -10318,14 +10318,14 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="437"/>
-      <c r="B2" s="442"/>
-      <c r="C2" s="443"/>
-      <c r="D2" s="443"/>
-      <c r="E2" s="443"/>
-      <c r="F2" s="443"/>
-      <c r="G2" s="443"/>
-      <c r="H2" s="444"/>
+      <c r="A2" s="429"/>
+      <c r="B2" s="434"/>
+      <c r="C2" s="435"/>
+      <c r="D2" s="435"/>
+      <c r="E2" s="435"/>
+      <c r="F2" s="435"/>
+      <c r="G2" s="435"/>
+      <c r="H2" s="436"/>
       <c r="I2" s="103" t="s">
         <v>53</v>
       </c>
@@ -10334,14 +10334,14 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="437"/>
-      <c r="B3" s="442"/>
-      <c r="C3" s="443"/>
-      <c r="D3" s="443"/>
-      <c r="E3" s="443"/>
-      <c r="F3" s="443"/>
-      <c r="G3" s="443"/>
-      <c r="H3" s="444"/>
+      <c r="A3" s="429"/>
+      <c r="B3" s="434"/>
+      <c r="C3" s="435"/>
+      <c r="D3" s="435"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="436"/>
       <c r="I3" s="103" t="s">
         <v>54</v>
       </c>
@@ -10350,14 +10350,14 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="438"/>
-      <c r="B4" s="445"/>
-      <c r="C4" s="446"/>
-      <c r="D4" s="446"/>
-      <c r="E4" s="446"/>
-      <c r="F4" s="446"/>
-      <c r="G4" s="446"/>
-      <c r="H4" s="447"/>
+      <c r="A4" s="430"/>
+      <c r="B4" s="437"/>
+      <c r="C4" s="438"/>
+      <c r="D4" s="438"/>
+      <c r="E4" s="438"/>
+      <c r="F4" s="438"/>
+      <c r="G4" s="438"/>
+      <c r="H4" s="439"/>
       <c r="I4" s="103" t="s">
         <v>55</v>
       </c>
@@ -10490,13 +10490,13 @@
       <c r="M17" s="237"/>
     </row>
     <row r="18" spans="1:21" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="450" t="s">
+      <c r="A18" s="442" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="450"/>
-      <c r="C18" s="450"/>
-      <c r="D18" s="450"/>
-      <c r="E18" s="450"/>
+      <c r="B18" s="442"/>
+      <c r="C18" s="442"/>
+      <c r="D18" s="442"/>
+      <c r="E18" s="442"/>
     </row>
     <row r="19" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F19" s="237"/>
@@ -10753,16 +10753,16 @@
       <c r="J38" s="107"/>
     </row>
     <row r="39" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="453" t="s">
+      <c r="A39" s="445" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="454"/>
-      <c r="C39" s="454"/>
-      <c r="D39" s="454"/>
-      <c r="E39" s="454"/>
-      <c r="F39" s="454"/>
-      <c r="G39" s="454"/>
-      <c r="H39" s="455"/>
+      <c r="B39" s="446"/>
+      <c r="C39" s="446"/>
+      <c r="D39" s="446"/>
+      <c r="E39" s="446"/>
+      <c r="F39" s="446"/>
+      <c r="G39" s="446"/>
+      <c r="H39" s="447"/>
       <c r="I39" s="107"/>
       <c r="J39" s="107"/>
     </row>
@@ -10898,10 +10898,10 @@
         <v>80</v>
       </c>
       <c r="I44" s="107"/>
-      <c r="J44" s="448" t="s">
+      <c r="J44" s="440" t="s">
         <v>85</v>
       </c>
-      <c r="K44" s="449"/>
+      <c r="K44" s="441"/>
       <c r="L44" s="101" t="s">
         <v>72</v>
       </c>
@@ -11490,10 +11490,10 @@
       <c r="I64" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="J64" s="448" t="s">
+      <c r="J64" s="440" t="s">
         <v>85</v>
       </c>
-      <c r="K64" s="449"/>
+      <c r="K64" s="441"/>
       <c r="L64" s="101" t="s">
         <v>72</v>
       </c>
@@ -11692,8 +11692,8 @@
         <v>80</v>
       </c>
       <c r="I69" s="107"/>
-      <c r="J69" s="451"/>
-      <c r="K69" s="452"/>
+      <c r="J69" s="443"/>
+      <c r="K69" s="444"/>
       <c r="L69" s="158" t="e">
         <f>SUM(L65:L68)</f>
         <v>#DIV/0!</v>
@@ -12164,10 +12164,10 @@
         <v>80</v>
       </c>
       <c r="I84" s="107"/>
-      <c r="J84" s="448" t="s">
+      <c r="J84" s="440" t="s">
         <v>85</v>
       </c>
-      <c r="K84" s="449"/>
+      <c r="K84" s="441"/>
       <c r="L84" s="101" t="s">
         <v>72</v>
       </c>
@@ -12660,10 +12660,10 @@
       <c r="F99" s="147"/>
       <c r="G99" s="148"/>
       <c r="H99" s="149"/>
-      <c r="J99" s="448" t="s">
+      <c r="J99" s="440" t="s">
         <v>85</v>
       </c>
-      <c r="K99" s="449"/>
+      <c r="K99" s="441"/>
       <c r="L99" s="101" t="s">
         <v>72</v>
       </c>
@@ -13086,19 +13086,19 @@
       <c r="A113" s="376" t="s">
         <v>205</v>
       </c>
-      <c r="B113" s="428" t="s">
+      <c r="B113" s="448" t="s">
         <v>206</v>
       </c>
-      <c r="C113" s="429"/>
+      <c r="C113" s="449"/>
       <c r="D113" s="377"/>
-      <c r="E113" s="430" t="s">
+      <c r="E113" s="450" t="s">
         <v>207</v>
       </c>
-      <c r="F113" s="430"/>
-      <c r="G113" s="431" t="s">
+      <c r="F113" s="450"/>
+      <c r="G113" s="451" t="s">
         <v>208</v>
       </c>
-      <c r="H113" s="432"/>
+      <c r="H113" s="452"/>
       <c r="K113" s="107"/>
       <c r="N113" s="107"/>
       <c r="O113" s="107"/>
@@ -13120,18 +13120,18 @@
       <c r="A115" s="378" t="s">
         <v>209</v>
       </c>
-      <c r="B115" s="433">
+      <c r="B115" s="453">
         <v>44869</v>
       </c>
-      <c r="C115" s="434"/>
-      <c r="E115" s="435" t="s">
+      <c r="C115" s="454"/>
+      <c r="E115" s="455" t="s">
         <v>210</v>
       </c>
-      <c r="F115" s="435"/>
-      <c r="G115" s="433">
+      <c r="F115" s="455"/>
+      <c r="G115" s="453">
         <v>44870</v>
       </c>
-      <c r="H115" s="434"/>
+      <c r="H115" s="454"/>
       <c r="K115" s="107"/>
       <c r="L115" s="107"/>
       <c r="M115" s="107"/>
@@ -13144,6 +13144,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="LUQM9/1cugGgjBSOa13V00Az19LtI0GISkl2s+B+CeDs9vqTu/qxaIsAvmj7bFfIvwPel1aJQ6UdLU47/0TEFw==" saltValue="pC5w/U1I+NFtBwsHIESvAA==" spinCount="100000" sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="G115:H115"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:H4"/>
     <mergeCell ref="J84:K84"/>
@@ -13153,12 +13159,6 @@
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="J44:K44"/>
     <mergeCell ref="J64:K64"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="G113:H113"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="G115:H115"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -13463,7 +13463,7 @@
       <c r="D30" s="283"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dQSKWnNiZlBwFGkj3dO+DeQJhyBtijhSV3+UD/c/PfT0FCKsLovvZuOtwl2SEMNZ5gZXqgKfTNaVpMbAtrXUDQ==" saltValue="KWF49AnRoPgaYQ3QjZtviw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -14647,30 +14647,30 @@
       <c r="B6" s="216"/>
     </row>
     <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="463" t="s">
+      <c r="A7" s="464" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="463"/>
-      <c r="C7" s="463"/>
-      <c r="D7" s="463"/>
-      <c r="F7" s="463" t="s">
+      <c r="B7" s="464"/>
+      <c r="C7" s="464"/>
+      <c r="D7" s="464"/>
+      <c r="F7" s="464" t="s">
         <v>120</v>
       </c>
-      <c r="G7" s="463"/>
-      <c r="H7" s="463"/>
-      <c r="I7" s="463"/>
-      <c r="K7" s="463" t="s">
+      <c r="G7" s="464"/>
+      <c r="H7" s="464"/>
+      <c r="I7" s="464"/>
+      <c r="K7" s="464" t="s">
         <v>121</v>
       </c>
-      <c r="L7" s="463"/>
-      <c r="M7" s="463"/>
-      <c r="N7" s="463"/>
-      <c r="P7" s="463" t="s">
+      <c r="L7" s="464"/>
+      <c r="M7" s="464"/>
+      <c r="N7" s="464"/>
+      <c r="P7" s="464" t="s">
         <v>122</v>
       </c>
-      <c r="Q7" s="463"/>
-      <c r="R7" s="463"/>
-      <c r="S7" s="463"/>
+      <c r="Q7" s="464"/>
+      <c r="R7" s="464"/>
+      <c r="S7" s="464"/>
     </row>
     <row r="8" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="218"/>
@@ -14694,585 +14694,606 @@
       <c r="A9" s="219" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="462" t="e">
+      <c r="B9" s="465" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="C9" s="462"/>
-      <c r="D9" s="462"/>
+      <c r="C9" s="465"/>
+      <c r="D9" s="465"/>
       <c r="F9" s="219" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="462" t="e">
+      <c r="G9" s="465" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H9" s="462"/>
-      <c r="I9" s="462"/>
+      <c r="H9" s="465"/>
+      <c r="I9" s="465"/>
       <c r="K9" s="219" t="s">
         <v>123</v>
       </c>
-      <c r="L9" s="462" t="e">
+      <c r="L9" s="465" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M9" s="462"/>
-      <c r="N9" s="462"/>
+      <c r="M9" s="465"/>
+      <c r="N9" s="465"/>
       <c r="P9" s="219" t="s">
         <v>123</v>
       </c>
-      <c r="Q9" s="464" t="e">
+      <c r="Q9" s="457" t="e">
         <f>+#REF!*#REF!+#REF!*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="R9" s="465"/>
-      <c r="S9" s="466"/>
+      <c r="R9" s="458"/>
+      <c r="S9" s="459"/>
     </row>
     <row r="10" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="219" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="462" t="e">
+      <c r="B10" s="465" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="462"/>
-      <c r="D10" s="462"/>
+      <c r="C10" s="465"/>
+      <c r="D10" s="465"/>
       <c r="F10" s="219" t="s">
         <v>124</v>
       </c>
-      <c r="G10" s="462" t="e">
+      <c r="G10" s="465" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="H10" s="462"/>
-      <c r="I10" s="462"/>
+      <c r="H10" s="465"/>
+      <c r="I10" s="465"/>
       <c r="K10" s="219" t="s">
         <v>124</v>
       </c>
-      <c r="L10" s="462" t="e">
+      <c r="L10" s="465" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="M10" s="462"/>
-      <c r="N10" s="462"/>
+      <c r="M10" s="465"/>
+      <c r="N10" s="465"/>
       <c r="P10" s="219" t="s">
         <v>124</v>
       </c>
-      <c r="Q10" s="464" t="e">
+      <c r="Q10" s="457" t="e">
         <f>+#REF!*POWER(#REF!,2)+#REF!*POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="R10" s="465"/>
-      <c r="S10" s="466"/>
+      <c r="R10" s="458"/>
+      <c r="S10" s="459"/>
     </row>
     <row r="11" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="462" t="e">
+      <c r="B11" s="465" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="462"/>
-      <c r="D11" s="462"/>
+      <c r="C11" s="465"/>
+      <c r="D11" s="465"/>
       <c r="F11" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="462" t="e">
+      <c r="G11" s="465" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H11" s="462"/>
-      <c r="I11" s="462"/>
+      <c r="H11" s="465"/>
+      <c r="I11" s="465"/>
       <c r="K11" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="L11" s="462" t="e">
+      <c r="L11" s="465" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="M11" s="462"/>
-      <c r="N11" s="462"/>
+      <c r="M11" s="465"/>
+      <c r="N11" s="465"/>
       <c r="P11" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="Q11" s="464" t="e">
+      <c r="Q11" s="457" t="e">
         <f>+SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R11" s="465"/>
-      <c r="S11" s="466"/>
+      <c r="R11" s="458"/>
+      <c r="S11" s="459"/>
     </row>
     <row r="12" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="219" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="462" t="e">
+      <c r="B12" s="465" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
+      <c r="C12" s="465"/>
+      <c r="D12" s="465"/>
       <c r="F12" s="219" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="462" t="e">
+      <c r="G12" s="465" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="H12" s="462"/>
-      <c r="I12" s="462"/>
+      <c r="H12" s="465"/>
+      <c r="I12" s="465"/>
       <c r="K12" s="219" t="s">
         <v>126</v>
       </c>
-      <c r="L12" s="462" t="e">
+      <c r="L12" s="465" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="M12" s="462"/>
-      <c r="N12" s="462"/>
+      <c r="M12" s="465"/>
+      <c r="N12" s="465"/>
       <c r="P12" s="219" t="s">
         <v>126</v>
       </c>
-      <c r="Q12" s="464" t="e">
+      <c r="Q12" s="457" t="e">
         <f>+POWER(#REF!,2)+POWER(#REF!,2)</f>
         <v>#REF!</v>
       </c>
-      <c r="R12" s="465"/>
-      <c r="S12" s="466"/>
+      <c r="R12" s="458"/>
+      <c r="S12" s="459"/>
     </row>
     <row r="13" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="219" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="456" t="e">
+      <c r="B13" s="463" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="456"/>
-      <c r="D13" s="456"/>
+      <c r="C13" s="463"/>
+      <c r="D13" s="463"/>
       <c r="F13" s="219" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="456" t="e">
+      <c r="G13" s="463" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="H13" s="456"/>
-      <c r="I13" s="456"/>
+      <c r="H13" s="463"/>
+      <c r="I13" s="463"/>
       <c r="K13" s="219" t="s">
         <v>127</v>
       </c>
-      <c r="L13" s="456" t="e">
+      <c r="L13" s="463" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="M13" s="456"/>
-      <c r="N13" s="456"/>
+      <c r="M13" s="463"/>
+      <c r="N13" s="463"/>
       <c r="P13" s="219" t="s">
         <v>127</v>
       </c>
-      <c r="Q13" s="458" t="e">
+      <c r="Q13" s="460" t="e">
         <f>(#REF!-1)*SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R13" s="459"/>
-      <c r="S13" s="460"/>
+      <c r="R13" s="461"/>
+      <c r="S13" s="462"/>
     </row>
     <row r="14" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="456" t="e">
+      <c r="B14" s="463" t="e">
         <f>ABS((B13/(B11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="C14" s="456"/>
-      <c r="D14" s="456"/>
+      <c r="C14" s="463"/>
+      <c r="D14" s="463"/>
       <c r="F14" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="G14" s="456" t="e">
+      <c r="G14" s="463" t="e">
         <f>ABS((G13/(G11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="H14" s="456"/>
-      <c r="I14" s="456"/>
+      <c r="H14" s="463"/>
+      <c r="I14" s="463"/>
       <c r="K14" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="L14" s="456" t="e">
+      <c r="L14" s="463" t="e">
         <f>ABS((L13/(L11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="M14" s="456"/>
-      <c r="N14" s="456"/>
+      <c r="M14" s="463"/>
+      <c r="N14" s="463"/>
       <c r="P14" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="Q14" s="458" t="e">
+      <c r="Q14" s="460" t="e">
         <f>ABS((Q13/(Q11-#REF!)))</f>
         <v>#REF!</v>
       </c>
-      <c r="R14" s="459"/>
-      <c r="S14" s="460"/>
+      <c r="R14" s="461"/>
+      <c r="S14" s="462"/>
     </row>
     <row r="15" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="456" t="e">
+      <c r="B15" s="463" t="e">
         <f>ABS((((B10*B11-(B9^2))/(B11*(#REF!-1)))-(B14))*((B11*(#REF!-1))/((B11^2)-B12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="C15" s="456"/>
-      <c r="D15" s="456"/>
+      <c r="C15" s="463"/>
+      <c r="D15" s="463"/>
       <c r="F15" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="456" t="e">
+      <c r="G15" s="463" t="e">
         <f>ABS((((G10*G11-(G9^2))/(G11*(#REF!-1)))-(G14))*((G11*(#REF!-1))/((G11^2)-G12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="456"/>
-      <c r="I15" s="456"/>
+      <c r="H15" s="463"/>
+      <c r="I15" s="463"/>
       <c r="K15" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="L15" s="456" t="e">
+      <c r="L15" s="463" t="e">
         <f>ABS((((L10*L11-(L9^2))/(L11*(#REF!-1)))-(L14))*((L11*(#REF!-1))/((L11^2)-L12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="M15" s="456"/>
-      <c r="N15" s="456"/>
+      <c r="M15" s="463"/>
+      <c r="N15" s="463"/>
       <c r="P15" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="Q15" s="456" t="e">
+      <c r="Q15" s="463" t="e">
         <f>ABS((((Q10*Q11-(Q9^2))/(Q11*(#REF!-1)))-(Q14))*((Q11*(#REF!-1))/((Q11^2)-Q12)))</f>
         <v>#REF!</v>
       </c>
-      <c r="R15" s="456"/>
-      <c r="S15" s="456"/>
+      <c r="R15" s="463"/>
+      <c r="S15" s="463"/>
     </row>
     <row r="16" spans="1:19" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="456" t="e">
+      <c r="B16" s="463" t="e">
         <f>(B14+B15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="C16" s="456"/>
-      <c r="D16" s="456"/>
+      <c r="C16" s="463"/>
+      <c r="D16" s="463"/>
       <c r="F16" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="456" t="e">
+      <c r="G16" s="463" t="e">
         <f>(G14+G15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="H16" s="456"/>
-      <c r="I16" s="456"/>
+      <c r="H16" s="463"/>
+      <c r="I16" s="463"/>
       <c r="K16" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="456" t="e">
+      <c r="L16" s="463" t="e">
         <f>(L14+L15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="M16" s="456"/>
-      <c r="N16" s="456"/>
+      <c r="M16" s="463"/>
+      <c r="N16" s="463"/>
       <c r="P16" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="Q16" s="458" t="e">
+      <c r="Q16" s="460" t="e">
         <f>(Q14+Q15)/1000000</f>
         <v>#REF!</v>
       </c>
-      <c r="R16" s="459"/>
-      <c r="S16" s="460"/>
+      <c r="R16" s="461"/>
+      <c r="S16" s="462"/>
     </row>
     <row r="17" spans="1:25" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="217" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="456" t="e">
+      <c r="B17" s="463" t="e">
         <f>SQRT(B14)</f>
         <v>#REF!</v>
       </c>
-      <c r="C17" s="456"/>
-      <c r="D17" s="456"/>
+      <c r="C17" s="463"/>
+      <c r="D17" s="463"/>
       <c r="F17" s="217" t="s">
         <v>131</v>
       </c>
-      <c r="G17" s="456" t="e">
+      <c r="G17" s="463" t="e">
         <f>SQRT(G14)</f>
         <v>#REF!</v>
       </c>
-      <c r="H17" s="456"/>
-      <c r="I17" s="456"/>
+      <c r="H17" s="463"/>
+      <c r="I17" s="463"/>
       <c r="K17" s="217" t="s">
         <v>131</v>
       </c>
-      <c r="L17" s="456" t="e">
+      <c r="L17" s="463" t="e">
         <f>SQRT(L14)</f>
         <v>#REF!</v>
       </c>
-      <c r="M17" s="456"/>
-      <c r="N17" s="456"/>
+      <c r="M17" s="463"/>
+      <c r="N17" s="463"/>
       <c r="P17" s="217" t="s">
         <v>131</v>
       </c>
-      <c r="Q17" s="458" t="e">
+      <c r="Q17" s="460" t="e">
         <f>SQRT(Q14)</f>
         <v>#REF!</v>
       </c>
-      <c r="R17" s="459"/>
-      <c r="S17" s="460"/>
-      <c r="V17" s="457"/>
-      <c r="W17" s="457"/>
-      <c r="X17" s="457"/>
-      <c r="Y17" s="457"/>
+      <c r="R17" s="461"/>
+      <c r="S17" s="462"/>
+      <c r="V17" s="466"/>
+      <c r="W17" s="466"/>
+      <c r="X17" s="466"/>
+      <c r="Y17" s="466"/>
     </row>
     <row r="18" spans="1:25" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="217" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="456" t="e">
+      <c r="B18" s="463" t="e">
         <f>+SQRT(B14+B15)</f>
         <v>#REF!</v>
       </c>
-      <c r="C18" s="456"/>
-      <c r="D18" s="456"/>
+      <c r="C18" s="463"/>
+      <c r="D18" s="463"/>
       <c r="F18" s="217" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="456" t="e">
+      <c r="G18" s="463" t="e">
         <f>+SQRT(G14+G15)</f>
         <v>#REF!</v>
       </c>
-      <c r="H18" s="456"/>
-      <c r="I18" s="456"/>
+      <c r="H18" s="463"/>
+      <c r="I18" s="463"/>
       <c r="K18" s="217" t="s">
         <v>132</v>
       </c>
-      <c r="L18" s="456" t="e">
+      <c r="L18" s="463" t="e">
         <f>+SQRT(L14+L15)</f>
         <v>#REF!</v>
       </c>
-      <c r="M18" s="456"/>
-      <c r="N18" s="456"/>
+      <c r="M18" s="463"/>
+      <c r="N18" s="463"/>
       <c r="P18" s="217" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="458" t="e">
+      <c r="Q18" s="460" t="e">
         <f>+SQRT(Q14+Q15)</f>
         <v>#REF!</v>
       </c>
-      <c r="R18" s="459"/>
-      <c r="S18" s="460"/>
-      <c r="V18" s="457"/>
-      <c r="W18" s="457"/>
-      <c r="X18" s="457"/>
-      <c r="Y18" s="457"/>
+      <c r="R18" s="461"/>
+      <c r="S18" s="462"/>
+      <c r="V18" s="466"/>
+      <c r="W18" s="466"/>
+      <c r="X18" s="466"/>
+      <c r="Y18" s="466"/>
     </row>
     <row r="19" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="379" t="s">
         <v>213</v>
       </c>
-      <c r="B19" s="461">
+      <c r="B19" s="456">
         <v>7.6899555698759737E-3</v>
       </c>
-      <c r="C19" s="461"/>
-      <c r="D19" s="461"/>
+      <c r="C19" s="456"/>
+      <c r="D19" s="456"/>
       <c r="E19" s="380"/>
       <c r="F19" s="379" t="s">
         <v>213</v>
       </c>
-      <c r="G19" s="461">
+      <c r="G19" s="456">
         <v>6.454972243679062E-3</v>
       </c>
-      <c r="H19" s="461"/>
-      <c r="I19" s="461"/>
+      <c r="H19" s="456"/>
+      <c r="I19" s="456"/>
       <c r="J19" s="380"/>
       <c r="K19" s="379" t="s">
         <v>213</v>
       </c>
-      <c r="L19" s="461">
+      <c r="L19" s="456">
         <v>6.4718943646096755E-3</v>
       </c>
-      <c r="M19" s="461"/>
-      <c r="N19" s="461"/>
+      <c r="M19" s="456"/>
+      <c r="N19" s="456"/>
       <c r="O19" s="380"/>
       <c r="P19" s="379" t="s">
         <v>213</v>
       </c>
-      <c r="Q19" s="461">
+      <c r="Q19" s="456">
         <v>9.1503642914731384E-2</v>
       </c>
-      <c r="R19" s="461"/>
-      <c r="S19" s="461"/>
-      <c r="V19" s="457"/>
-      <c r="W19" s="457"/>
-      <c r="X19" s="457"/>
-      <c r="Y19" s="457"/>
+      <c r="R19" s="456"/>
+      <c r="S19" s="456"/>
+      <c r="V19" s="466"/>
+      <c r="W19" s="466"/>
+      <c r="X19" s="466"/>
+      <c r="Y19" s="466"/>
     </row>
     <row r="20" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="379" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="461">
+      <c r="B20" s="456">
         <v>7.734845547824153E-3</v>
       </c>
-      <c r="C20" s="461"/>
-      <c r="D20" s="461"/>
+      <c r="C20" s="456"/>
+      <c r="D20" s="456"/>
       <c r="E20" s="380"/>
       <c r="F20" s="379" t="s">
         <v>214</v>
       </c>
-      <c r="G20" s="461">
+      <c r="G20" s="456">
         <v>6.6157779978408861E-3</v>
       </c>
-      <c r="H20" s="461"/>
-      <c r="I20" s="461"/>
+      <c r="H20" s="456"/>
+      <c r="I20" s="456"/>
       <c r="J20" s="380"/>
       <c r="K20" s="379" t="s">
         <v>214</v>
       </c>
-      <c r="L20" s="461">
+      <c r="L20" s="456">
         <v>6.5331464330420554E-3</v>
       </c>
-      <c r="M20" s="461"/>
-      <c r="N20" s="461"/>
+      <c r="M20" s="456"/>
+      <c r="N20" s="456"/>
       <c r="O20" s="380"/>
       <c r="P20" s="379" t="s">
         <v>214</v>
       </c>
-      <c r="Q20" s="461">
+      <c r="Q20" s="456">
         <v>0.1067108740857599</v>
       </c>
-      <c r="R20" s="461"/>
-      <c r="S20" s="461"/>
-      <c r="V20" s="457"/>
-      <c r="W20" s="457"/>
-      <c r="X20" s="457"/>
-      <c r="Y20" s="457"/>
+      <c r="R20" s="456"/>
+      <c r="S20" s="456"/>
+      <c r="V20" s="466"/>
+      <c r="W20" s="466"/>
+      <c r="X20" s="466"/>
+      <c r="Y20" s="466"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V21" s="457"/>
-      <c r="W21" s="457"/>
-      <c r="X21" s="457"/>
-      <c r="Y21" s="457"/>
+      <c r="V21" s="466"/>
+      <c r="W21" s="466"/>
+      <c r="X21" s="466"/>
+      <c r="Y21" s="466"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V22" s="457"/>
-      <c r="W22" s="457"/>
-      <c r="X22" s="457"/>
-      <c r="Y22" s="457"/>
+      <c r="V22" s="466"/>
+      <c r="W22" s="466"/>
+      <c r="X22" s="466"/>
+      <c r="Y22" s="466"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V23" s="457"/>
-      <c r="W23" s="457"/>
-      <c r="X23" s="457"/>
-      <c r="Y23" s="457"/>
+      <c r="V23" s="466"/>
+      <c r="W23" s="466"/>
+      <c r="X23" s="466"/>
+      <c r="Y23" s="466"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V24" s="457"/>
-      <c r="W24" s="457"/>
-      <c r="X24" s="457"/>
-      <c r="Y24" s="457"/>
+      <c r="V24" s="466"/>
+      <c r="W24" s="466"/>
+      <c r="X24" s="466"/>
+      <c r="Y24" s="466"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V25" s="457"/>
-      <c r="W25" s="457"/>
-      <c r="X25" s="457"/>
-      <c r="Y25" s="457"/>
+      <c r="V25" s="466"/>
+      <c r="W25" s="466"/>
+      <c r="X25" s="466"/>
+      <c r="Y25" s="466"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V26" s="457"/>
-      <c r="W26" s="457"/>
-      <c r="X26" s="457"/>
-      <c r="Y26" s="457"/>
+      <c r="V26" s="466"/>
+      <c r="W26" s="466"/>
+      <c r="X26" s="466"/>
+      <c r="Y26" s="466"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V27" s="457"/>
-      <c r="W27" s="457"/>
-      <c r="X27" s="457"/>
-      <c r="Y27" s="457"/>
+      <c r="V27" s="466"/>
+      <c r="W27" s="466"/>
+      <c r="X27" s="466"/>
+      <c r="Y27" s="466"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V28" s="457"/>
-      <c r="W28" s="457"/>
-      <c r="X28" s="457"/>
-      <c r="Y28" s="457"/>
+      <c r="V28" s="466"/>
+      <c r="W28" s="466"/>
+      <c r="X28" s="466"/>
+      <c r="Y28" s="466"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V29" s="457"/>
-      <c r="W29" s="457"/>
-      <c r="X29" s="457"/>
-      <c r="Y29" s="457"/>
+      <c r="V29" s="466"/>
+      <c r="W29" s="466"/>
+      <c r="X29" s="466"/>
+      <c r="Y29" s="466"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V30" s="457"/>
-      <c r="W30" s="457"/>
-      <c r="X30" s="457"/>
-      <c r="Y30" s="457"/>
+      <c r="V30" s="466"/>
+      <c r="W30" s="466"/>
+      <c r="X30" s="466"/>
+      <c r="Y30" s="466"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V31" s="457"/>
-      <c r="W31" s="457"/>
-      <c r="X31" s="457"/>
-      <c r="Y31" s="457"/>
+      <c r="V31" s="466"/>
+      <c r="W31" s="466"/>
+      <c r="X31" s="466"/>
+      <c r="Y31" s="466"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="V32" s="457"/>
-      <c r="W32" s="457"/>
-      <c r="X32" s="457"/>
-      <c r="Y32" s="457"/>
+      <c r="V32" s="466"/>
+      <c r="W32" s="466"/>
+      <c r="X32" s="466"/>
+      <c r="Y32" s="466"/>
     </row>
     <row r="33" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V33" s="457"/>
-      <c r="W33" s="457"/>
-      <c r="X33" s="457"/>
-      <c r="Y33" s="457"/>
+      <c r="V33" s="466"/>
+      <c r="W33" s="466"/>
+      <c r="X33" s="466"/>
+      <c r="Y33" s="466"/>
     </row>
     <row r="34" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V34" s="457"/>
-      <c r="W34" s="457"/>
-      <c r="X34" s="457"/>
-      <c r="Y34" s="457"/>
+      <c r="V34" s="466"/>
+      <c r="W34" s="466"/>
+      <c r="X34" s="466"/>
+      <c r="Y34" s="466"/>
     </row>
     <row r="35" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V35" s="457"/>
-      <c r="W35" s="457"/>
-      <c r="X35" s="457"/>
-      <c r="Y35" s="457"/>
+      <c r="V35" s="466"/>
+      <c r="W35" s="466"/>
+      <c r="X35" s="466"/>
+      <c r="Y35" s="466"/>
     </row>
     <row r="36" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V36" s="457"/>
-      <c r="W36" s="457"/>
-      <c r="X36" s="457"/>
-      <c r="Y36" s="457"/>
+      <c r="V36" s="466"/>
+      <c r="W36" s="466"/>
+      <c r="X36" s="466"/>
+      <c r="Y36" s="466"/>
     </row>
     <row r="37" spans="22:25" x14ac:dyDescent="0.2">
-      <c r="V37" s="457"/>
-      <c r="W37" s="457"/>
-      <c r="X37" s="457"/>
-      <c r="Y37" s="457"/>
+      <c r="V37" s="466"/>
+      <c r="W37" s="466"/>
+      <c r="X37" s="466"/>
+      <c r="Y37" s="466"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F7BNTbSy/WaNWXDdT6W94NKCeKyHLn/2tkk/4quJIvd3p+J7bDJlNkQREHsu55RDSjMZ5YiRTRqr/fG8D9Qggw==" saltValue="uAZ5OYTao9E+LNIA/ZL2vQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="53">
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="V17:Y37"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="L14:N14"/>
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="B15:D15"/>
@@ -15289,35 +15310,14 @@
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="V17:Y37"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="Q16:S16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
